--- a/Materials/Расписание 2026-2027/Расписание_V34_для_завуча.xlsx
+++ b/Materials/Расписание 2026-2027/Расписание_V34_для_завуча.xlsx
@@ -230,10 +230,10 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -874,7 +874,7 @@
       <c r="R3" s="7" t="inlineStr">
         <is>
           <t>КиЛ
-Дюсембаева А.К., каб. английского языка (№27)</t>
+Власова А.К., каб. английского языка (№27)</t>
         </is>
       </c>
       <c r="S3" s="7" t="inlineStr">
@@ -928,7 +928,7 @@
       <c r="F4" s="7" t="inlineStr">
         <is>
           <t>Казахский язык
-Дюсембаева А.К., нач. класс 1Б (№8)</t>
+Власова А.К., нач. класс 1Б (№8)</t>
         </is>
       </c>
       <c r="G4" s="7" t="inlineStr">
@@ -1075,7 +1075,7 @@
       <c r="H5" s="7" t="inlineStr">
         <is>
           <t>Казахский язык
-Дюсембаева А.К., нач. класс 3А (№7)</t>
+Власова А.К., нач. класс 3А (№7)</t>
         </is>
       </c>
       <c r="I5" s="7" t="inlineStr">
@@ -1117,14 +1117,14 @@
       <c r="O5" s="8" t="inlineStr">
         <is>
           <t>Русский язык
-Темерканова О.В., каб. технологии (мальчики) (№39)
+Темерканова О.В., каб. математики (№25)
 вместе с 6В</t>
         </is>
       </c>
       <c r="P5" s="8" t="inlineStr">
         <is>
           <t>Русский язык
-Темерканова О.В., каб. технологии (мальчики) (№39)
+Темерканова О.В., каб. математики (№25)
 вместе с 6Б</t>
         </is>
       </c>
@@ -1246,7 +1246,7 @@
       <c r="N6" s="7" t="inlineStr">
         <is>
           <t>Русская лит.
-Ажикенова М.А., каб. робототехники (№15)</t>
+Ажикенова М.А., каб. мультимедийный (№18)</t>
         </is>
       </c>
       <c r="O6" s="7" t="inlineStr">
@@ -1421,7 +1421,7 @@
       <c r="L8" s="7" t="inlineStr">
         <is>
           <t>Каз. литература
-Дюсембаева А.К., каб. НВП (№28)</t>
+Власова А.К., каб. НВП (№28)</t>
         </is>
       </c>
       <c r="M8" s="7" t="inlineStr">
@@ -1774,7 +1774,7 @@
       <c r="Q12" s="7" t="inlineStr">
         <is>
           <t>КиЛ
-Дюсембаева А.К., каб. физики (№16)</t>
+Власова А.К., каб. физики (№16)</t>
         </is>
       </c>
       <c r="R12" s="7" t="inlineStr">
@@ -1877,7 +1877,7 @@
       <c r="L13" s="7" t="inlineStr">
         <is>
           <t>Казахский язык
-Дюсембаева А.К., каб. физики (№16)</t>
+Власова А.К., каб. физики (№16)</t>
         </is>
       </c>
       <c r="M13" s="7" t="inlineStr">
@@ -2047,7 +2047,7 @@
       <c r="R14" s="7" t="inlineStr">
         <is>
           <t>КиЛ
-Дюсембаева А.К., каб. физики (№16)</t>
+Власова А.К., каб. физики (№16)</t>
         </is>
       </c>
       <c r="S14" s="7" t="inlineStr">
@@ -2135,14 +2135,14 @@
       <c r="O15" s="8" t="inlineStr">
         <is>
           <t>Русская лит.
-Темерканова О.В., каб. технологии (мальчики) (№39)
+Темерканова О.В., каб. английского языка (№27)
 вместе с 6В</t>
         </is>
       </c>
       <c r="P15" s="8" t="inlineStr">
         <is>
           <t>Чтение и разв. речи
-Темерканова О.В., каб. технологии (мальчики) (№39)
+Темерканова О.В., каб. английского языка (№27)
 вместе с 6Б</t>
         </is>
       </c>
@@ -2705,14 +2705,14 @@
       <c r="O21" s="8" t="inlineStr">
         <is>
           <t>Русский язык
-Темерканова О.В., каб. технологии (мальчики) (№39)
+Темерканова О.В., каб. биологии (№19)
 вместе с 6В</t>
         </is>
       </c>
       <c r="P21" s="8" t="inlineStr">
         <is>
           <t>Русский язык
-Темерканова О.В., каб. технологии (мальчики) (№39)
+Темерканова О.В., каб. биологии (№19)
 вместе с 6Б</t>
         </is>
       </c>
@@ -2725,7 +2725,7 @@
       <c r="R21" s="7" t="inlineStr">
         <is>
           <t>КиЛ
-Дюсембаева А.К., каб. английского языка (№27)</t>
+Власова А.К., каб. английского языка (№27)</t>
         </is>
       </c>
       <c r="S21" s="7" t="inlineStr">
@@ -2776,7 +2776,7 @@
       <c r="D22" s="7" t="inlineStr">
         <is>
           <t>Казахский язык
-Жекеева Н.А., каб. технологии (девочки) (№29)</t>
+Жекеева Н.А., нач. класс 2А/4А (№42)</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
@@ -2848,12 +2848,10 @@
         </is>
       </c>
       <c r="P22" s="7" t="n"/>
-      <c r="Q22" s="10" t="inlineStr">
-        <is>
-          <t>Девочки: Худ.труд
-Жукова И.М., каб. технологии (девочки) (№29)
-Мальчики: Худ.труд
-Жантимиров А.К., каб. технологии (мальчики) (№39)</t>
+      <c r="Q22" s="7" t="inlineStr">
+        <is>
+          <t>Физкультура
+Ольков Г.В., спортзал (№01)</t>
         </is>
       </c>
       <c r="R22" s="7" t="inlineStr">
@@ -2962,7 +2960,7 @@
       <c r="Q23" s="7" t="inlineStr">
         <is>
           <t>КиЛ
-Дюсембаева А.К., каб. английского языка (№27)</t>
+Власова А.К., каб. английского языка (№27)</t>
         </is>
       </c>
       <c r="R23" s="7" t="inlineStr">
@@ -3030,7 +3028,7 @@
       <c r="L24" s="7" t="inlineStr">
         <is>
           <t>Каз. литература
-Дюсембаева А.К., каб. английского языка (№27)</t>
+Власова А.К., каб. английского языка (№27)</t>
         </is>
       </c>
       <c r="M24" s="7" t="inlineStr">
@@ -3051,8 +3049,8 @@
       <c r="P24" s="7" t="n"/>
       <c r="Q24" s="7" t="inlineStr">
         <is>
-          <t>Физкультура
-Ольков Г.В., спортзал (№01)</t>
+          <t>Физика
+Русина Н.В., каб. физики (№16)</t>
         </is>
       </c>
       <c r="R24" s="7" t="inlineStr">
@@ -3112,12 +3110,7 @@
       <c r="N25" s="7" t="n"/>
       <c r="O25" s="7" t="n"/>
       <c r="P25" s="7" t="n"/>
-      <c r="Q25" s="7" t="inlineStr">
-        <is>
-          <t>Физика
-Русина Н.В., каб. физики (№16)</t>
-        </is>
-      </c>
+      <c r="Q25" s="7" t="n"/>
       <c r="R25" s="7" t="n"/>
       <c r="S25" s="7" t="inlineStr">
         <is>
@@ -3235,7 +3228,7 @@
       <c r="L27" s="7" t="inlineStr">
         <is>
           <t>Казахский язык
-Дюсембаева А.К., каб. НВП (№28)</t>
+Власова А.К., каб. НВП (№28)</t>
         </is>
       </c>
       <c r="M27" s="7" t="inlineStr">
@@ -3397,7 +3390,7 @@
       <c r="Q28" s="7" t="inlineStr">
         <is>
           <t>КиЛ
-Дюсембаева А.К., каб. НВП (№28)</t>
+Власова А.К., каб. НВП (№28)</t>
         </is>
       </c>
       <c r="R28" s="7" t="inlineStr">
@@ -3464,7 +3457,7 @@
       <c r="F29" s="7" t="inlineStr">
         <is>
           <t>Казахский язык
-Дюсембаева А.К., нач. класс 1Б (№8)</t>
+Власова А.К., нач. класс 1Б (№8)</t>
         </is>
       </c>
       <c r="G29" s="7" t="inlineStr">
@@ -3604,7 +3597,7 @@
       <c r="H30" s="7" t="inlineStr">
         <is>
           <t>Казахский язык
-Дюсембаева А.К., нач. класс 3А (№7)</t>
+Власова А.К., нач. класс 3А (№7)</t>
         </is>
       </c>
       <c r="I30" s="7" t="inlineStr">
@@ -3646,14 +3639,14 @@
       <c r="O30" s="8" t="inlineStr">
         <is>
           <t>Русская лит.
-Темерканова О.В., каб. технологии (мальчики) (№39)
+Темерканова О.В., каб. истории (№14)
 вместе с 6В</t>
         </is>
       </c>
       <c r="P30" s="8" t="inlineStr">
         <is>
           <t>Чтение и разв. речи
-Темерканова О.В., каб. технологии (мальчики) (№39)
+Темерканова О.В., каб. истории (№14)
 вместе с 6Б</t>
         </is>
       </c>
@@ -3735,8 +3728,8 @@
       </c>
       <c r="L31" s="7" t="inlineStr">
         <is>
-          <t>Геометрия
-Ізбасты М.Ж., каб. робототехники (№15)</t>
+          <t>Всем.история
+Досаева М.Х., каб. истории (№14)</t>
         </is>
       </c>
       <c r="M31" s="7" t="inlineStr">
@@ -3756,7 +3749,7 @@
       <c r="O31" s="7" t="inlineStr">
         <is>
           <t>История Каз.
-Мельникова Л.Р., каб. истории (№14)</t>
+Мельникова Л.Р., каб. робототехники (№15)</t>
         </is>
       </c>
       <c r="P31" s="7" t="n"/>
@@ -3769,7 +3762,7 @@
       <c r="R31" s="7" t="inlineStr">
         <is>
           <t>КиЛ
-Дюсембаева А.К., каб. английского языка (№27)</t>
+Власова А.К., каб. английского языка (№27)</t>
         </is>
       </c>
       <c r="S31" s="7" t="inlineStr">
@@ -3820,8 +3813,8 @@
       <c r="K32" s="7" t="n"/>
       <c r="L32" s="7" t="inlineStr">
         <is>
-          <t>Всем.история
-Досаева М.Х., каб. истории (№14)</t>
+          <t>Геометрия
+Ізбасты М.Ж., каб. истории (№14)</t>
         </is>
       </c>
       <c r="M32" s="7" t="inlineStr">
@@ -4040,8 +4033,8 @@
       </c>
       <c r="L35" s="7" t="inlineStr">
         <is>
-          <t>Каз. литература
-Дюсембаева А.К., каб. английского языка (№27)</t>
+          <t>Казахский язык
+Власова А.К., каб. английского языка (№27)</t>
         </is>
       </c>
       <c r="M35" s="7" t="inlineStr">
@@ -4070,10 +4063,12 @@
 вместе с 6Б</t>
         </is>
       </c>
-      <c r="Q35" s="7" t="inlineStr">
-        <is>
-          <t>Физика
-Русина Н.В., каб. физики (№16)</t>
+      <c r="Q35" s="10" t="inlineStr">
+        <is>
+          <t>Девочки: Худ.труд
+Жукова И.М., каб. технологии (девочки) (№29)
+Мальчики: Худ.труд
+Жантимиров А.К., каб. технологии (мальчики) (№39)</t>
         </is>
       </c>
       <c r="R35" s="7" t="inlineStr">
@@ -4203,7 +4198,7 @@
       <c r="Q36" s="7" t="inlineStr">
         <is>
           <t>КиЛ
-Дюсембаева А.К., каб. английского языка (№27)</t>
+Власова А.К., каб. английского языка (№27)</t>
         </is>
       </c>
       <c r="R36" s="7" t="inlineStr">
@@ -4461,14 +4456,14 @@
       <c r="O38" s="8" t="inlineStr">
         <is>
           <t>Русский язык
-Темерканова О.В., каб. технологии (мальчики) (№39)
+Темерканова О.В., каб. английского языка (№27)
 вместе с 6В</t>
         </is>
       </c>
       <c r="P38" s="8" t="inlineStr">
         <is>
           <t>Русский язык
-Темерканова О.В., каб. технологии (мальчики) (№39)
+Темерканова О.В., каб. английского языка (№27)
 вместе с 6Б</t>
         </is>
       </c>
@@ -4642,7 +4637,7 @@
       <c r="H40" s="7" t="inlineStr">
         <is>
           <t>Казахский язык
-Дюсембаева А.К., нач. класс 3А (№7)</t>
+Власова А.К., нач. класс 3А (№7)</t>
         </is>
       </c>
       <c r="I40" s="7" t="n"/>
@@ -4682,7 +4677,12 @@
         </is>
       </c>
       <c r="P40" s="7" t="n"/>
-      <c r="Q40" s="7" t="n"/>
+      <c r="Q40" s="7" t="inlineStr">
+        <is>
+          <t>Физика
+Русина Н.В., каб. физики (№16)</t>
+        </is>
+      </c>
       <c r="R40" s="7" t="inlineStr">
         <is>
           <t>Физкультура
@@ -4874,12 +4874,12 @@
       <c r="D51" s="17" t="n">
         <v>21</v>
       </c>
-      <c r="E51" s="17" t="n">
-        <v>0</v>
+      <c r="E51" s="18" t="n">
+        <v>1</v>
       </c>
       <c r="F51" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Чт 5</t>
         </is>
       </c>
       <c r="G51" s="17" t="inlineStr"/>
@@ -5286,76 +5286,76 @@
     <row r="65">
       <c r="C65" s="17" t="inlineStr">
         <is>
-          <t>Дмитриев Евгений Владимирович</t>
+          <t>Власова Айгуль Каирбековна</t>
         </is>
       </c>
       <c r="D65" s="17" t="n">
-        <v>24</v>
-      </c>
-      <c r="E65" s="17" t="n">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="E65" s="18" t="n">
+        <v>6</v>
       </c>
       <c r="F65" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Пн 4, Пн 5, Ср 4, Пт 3, Пт 4, Пт 5</t>
         </is>
       </c>
       <c r="G65" s="17" t="inlineStr"/>
       <c r="H65" s="17" t="inlineStr">
         <is>
-          <t>Пн 1–5, 8 ур.; Вт 1–5, 7–8 ур.; Ср весь день; Чт 1–5, 8 ур.; Пт 1–4, 7–8 ур.</t>
+          <t>без ограничений</t>
         </is>
       </c>
       <c r="I65" s="17" t="inlineStr">
         <is>
-          <t>5 / 4 / 6 / 5 / 4</t>
+          <t>4 / 3 / 3 / 5 / 3</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="C66" s="17" t="inlineStr">
         <is>
-          <t>Досаева Мадина Хайрулловна</t>
+          <t>Дмитриев Евгений Владимирович</t>
         </is>
       </c>
       <c r="D66" s="17" t="n">
         <v>24</v>
       </c>
-      <c r="E66" s="18" t="n">
-        <v>7</v>
+      <c r="E66" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F66" s="17" t="inlineStr">
         <is>
-          <t>Пн 2, Вт 3, Ср 5, Чт 4, Чт 5, Пт 2, Пт 3</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G66" s="17" t="inlineStr"/>
       <c r="H66" s="17" t="inlineStr">
         <is>
-          <t>без ограничений</t>
+          <t>Пн 1–5, 8 ур.; Вт 1–5, 7–8 ур.; Ср весь день; Чт 1–5, 8 ур.; Пт 1–4, 7–8 ур.</t>
         </is>
       </c>
       <c r="I66" s="17" t="inlineStr">
         <is>
-          <t>5 / 6 / 5 / 4 / 4</t>
+          <t>5 / 4 / 6 / 5 / 4</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="C67" s="17" t="inlineStr">
         <is>
-          <t>Дюсембаева Айгуль Каирбековна</t>
+          <t>Досаева Мадина Хайрулловна</t>
         </is>
       </c>
       <c r="D67" s="17" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E67" s="18" t="n">
         <v>6</v>
       </c>
       <c r="F67" s="17" t="inlineStr">
         <is>
-          <t>Пн 4, Пн 5, Ср 4, Пт 3, Пт 4, Пт 5</t>
+          <t>Пн 2, Вт 3, Ср 5, Чт 4, Пт 2, Пт 3</t>
         </is>
       </c>
       <c r="G67" s="17" t="inlineStr"/>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="I67" s="17" t="inlineStr">
         <is>
-          <t>4 / 3 / 3 / 5 / 3</t>
+          <t>5 / 6 / 5 / 4 / 4</t>
         </is>
       </c>
     </row>
@@ -5399,7 +5399,7 @@
       </c>
       <c r="I68" s="17" t="inlineStr">
         <is>
-          <t>0 / 0 / 4 / 3 / 5</t>
+          <t>0 / 0 / 3 / 3 / 6</t>
         </is>
       </c>
     </row>
@@ -5475,22 +5475,22 @@
         <v>10</v>
       </c>
       <c r="E71" s="18" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F71" s="17" t="inlineStr">
         <is>
-          <t>Чт 6, Пт 4</t>
+          <t>Ср 3, Ср 4, Ср 5, Чт 6, Пт 4</t>
         </is>
       </c>
       <c r="G71" s="17" t="inlineStr"/>
       <c r="H71" s="17" t="inlineStr">
         <is>
-          <t>Пн 1, 3–8 ур.; Вт 2, 4–8 ур.; Ср 2, 6–8 ур.; Чт 2–8 ур.; Пт весь день</t>
+          <t>Пн 1, 3–8 ур.; Вт 2, 4–8 ур.; Ср 2–8 ур.; Чт 2, 5–8 ур.; Пт весь день</t>
         </is>
       </c>
       <c r="I71" s="17" t="inlineStr">
         <is>
-          <t>0 / 0 / 3 / 2 / 5</t>
+          <t>0 / 0 / 2 / 2 / 6</t>
         </is>
       </c>
     </row>
@@ -5715,7 +5715,7 @@
       </c>
       <c r="F79" s="17" t="inlineStr">
         <is>
-          <t>Пн 5, Вт 5, Ср 2, Ср 3, Ср 4, Чт 2, Чт 3, Чт 4, Чт 5, Пт 5</t>
+          <t>Пн 5, Вт 5, Ср 2, Ср 3, Ср 6, Чт 2, Чт 3, Чт 4, Чт 5, Пт 5</t>
         </is>
       </c>
       <c r="G79" s="17" t="inlineStr"/>
@@ -5798,11 +5798,11 @@
         <v>13</v>
       </c>
       <c r="E82" s="18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F82" s="17" t="inlineStr">
         <is>
-          <t>Ср 5, Ср 6, Пт 2</t>
+          <t>Ср 5</t>
         </is>
       </c>
       <c r="G82" s="17" t="inlineStr"/>
@@ -6082,9 +6082,9 @@
       </c>
       <c r="E94" s="17" t="inlineStr">
         <is>
-          <t>Ср: 4 ур. 1А Труд. обучение; 4 ур. 7А/Мальчики Худ.труд; 5 ур. 5А,6А,8Ә Худ.труд; 6 ур. 6Б/Мальчики Худ.труд
+          <t>Ср: 4 ур. 1А Труд. обучение; 5 ур. 5А,6А,8Ә Худ.труд; 6 ур. 6Б/Мальчики Худ.труд
 Чт: 2 ур. 1А ИЗО; 5 ур. 5Б/Мальчики Худ.труд; 7 ур. 8А/Мальчики Худ.труд
-Пт: 2 ур. 6Б/Мальчики Худ.труд; 3 ур. 5А,6А Худ.труд; 5 ур. 5Б/Мальчики Худ.труд; 6 ур. 8Б/Мальчики Худ.труд; 7 ур. 9Б/Мальчики Худ.труд</t>
+Пт: 1 ур. 7А/Мальчики Худ.труд; 2 ур. 6Б/Мальчики Худ.труд; 3 ур. 5А,6А Худ.труд; 5 ур. 5Б/Мальчики Худ.труд; 6 ур. 8Б/Мальчики Худ.труд; 7 ур. 9Б/Мальчики Худ.труд</t>
         </is>
       </c>
       <c r="F94" s="17" t="n">
@@ -6759,17 +6759,17 @@
       </c>
       <c r="F116" s="17" t="inlineStr">
         <is>
+          <t>6 (1–6)</t>
+        </is>
+      </c>
+      <c r="G116" s="17" t="inlineStr">
+        <is>
           <t>7 (1–7)</t>
         </is>
       </c>
-      <c r="G116" s="17" t="inlineStr">
-        <is>
-          <t>7 (1–7)</t>
-        </is>
-      </c>
       <c r="H116" s="17" t="inlineStr">
         <is>
-          <t>5 (1–5)</t>
+          <t>6 (1–6)</t>
         </is>
       </c>
       <c r="I116" s="17" t="n">
@@ -7390,13 +7390,17 @@
 каб. робототехники (№15)</t>
         </is>
       </c>
-      <c r="AD3" s="22" t="inlineStr">
+      <c r="AD3" s="23" t="inlineStr">
+        <is>
+          <t>окно</t>
+        </is>
+      </c>
+      <c r="AE3" s="22" t="inlineStr">
         <is>
           <t>8Ә
-каб. робототехники (№15)</t>
-        </is>
-      </c>
-      <c r="AE3" s="22" t="n"/>
+каб. истории (№14)</t>
+        </is>
+      </c>
       <c r="AF3" s="22" t="n"/>
       <c r="AG3" s="22" t="n"/>
       <c r="AH3" s="22" t="inlineStr">
@@ -7431,7 +7435,7 @@
         <v>21</v>
       </c>
       <c r="AQ3" s="21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
@@ -7446,7 +7450,7 @@
 нач. класс 1Б (№8)</t>
         </is>
       </c>
-      <c r="C4" s="23" t="n"/>
+      <c r="C4" s="24" t="n"/>
       <c r="D4" s="22" t="inlineStr">
         <is>
           <t>1Б
@@ -7456,7 +7460,7 @@
       <c r="E4" s="22" t="inlineStr">
         <is>
           <t>5Б
-каб. робототехники (№15)</t>
+каб. мультимедийный (№18)</t>
         </is>
       </c>
       <c r="F4" s="22" t="n"/>
@@ -7492,7 +7496,7 @@
 нач. класс 1Б (№8)</t>
         </is>
       </c>
-      <c r="S4" s="23" t="n"/>
+      <c r="S4" s="24" t="n"/>
       <c r="T4" s="22" t="inlineStr">
         <is>
           <t>1Б
@@ -7543,7 +7547,7 @@
 нач. класс 1Б (№8)</t>
         </is>
       </c>
-      <c r="AI4" s="23" t="n"/>
+      <c r="AI4" s="24" t="n"/>
       <c r="AJ4" s="22" t="inlineStr">
         <is>
           <t>1Б
@@ -7630,10 +7634,10 @@
 каб. английского языка (№27)</t>
         </is>
       </c>
-      <c r="N5" s="23" t="n"/>
-      <c r="O5" s="23" t="n"/>
-      <c r="P5" s="23" t="n"/>
-      <c r="Q5" s="23" t="n"/>
+      <c r="N5" s="24" t="n"/>
+      <c r="O5" s="24" t="n"/>
+      <c r="P5" s="24" t="n"/>
+      <c r="Q5" s="24" t="n"/>
       <c r="R5" s="22" t="inlineStr">
         <is>
           <t>4А
@@ -7646,7 +7650,7 @@
 каб. английского языка (№27)</t>
         </is>
       </c>
-      <c r="T5" s="24" t="inlineStr">
+      <c r="T5" s="23" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -7700,7 +7704,7 @@
 нач. класс 4Б (№9)</t>
         </is>
       </c>
-      <c r="AD5" s="24" t="inlineStr">
+      <c r="AD5" s="23" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -7732,7 +7736,7 @@
 нач. класс 3А (№7)</t>
         </is>
       </c>
-      <c r="AL5" s="24" t="inlineStr">
+      <c r="AL5" s="23" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -7770,7 +7774,7 @@
 нач. класс 2А/4А (№42)</t>
         </is>
       </c>
-      <c r="D6" s="24" t="inlineStr">
+      <c r="D6" s="23" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -7814,7 +7818,7 @@
 нач. класс 2А/4А (№42)</t>
         </is>
       </c>
-      <c r="S6" s="24" t="inlineStr">
+      <c r="S6" s="23" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -7886,7 +7890,7 @@
 нач. класс 2А/4А (№42)</t>
         </is>
       </c>
-      <c r="AK6" s="24" t="inlineStr">
+      <c r="AK6" s="23" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -7985,7 +7989,7 @@
 каб. казахского языка и литературы (№23)</t>
         </is>
       </c>
-      <c r="S7" s="24" t="inlineStr">
+      <c r="S7" s="23" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -8002,7 +8006,7 @@
 каб. казахского языка (№24)</t>
         </is>
       </c>
-      <c r="V7" s="24" t="inlineStr">
+      <c r="V7" s="23" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -8039,7 +8043,7 @@
 каб. казахского языка (№24)</t>
         </is>
       </c>
-      <c r="AD7" s="24" t="inlineStr">
+      <c r="AD7" s="23" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -8075,7 +8079,7 @@
 каб. казахского языка (№24)</t>
         </is>
       </c>
-      <c r="AK7" s="24" t="inlineStr">
+      <c r="AK7" s="23" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -8120,7 +8124,7 @@
 нач. класс 2Б (№6)</t>
         </is>
       </c>
-      <c r="E8" s="24" t="inlineStr">
+      <c r="E8" s="23" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -8206,7 +8210,7 @@
 каб. казахского языка (№24)</t>
         </is>
       </c>
-      <c r="AA8" s="23" t="n"/>
+      <c r="AA8" s="24" t="n"/>
       <c r="AB8" s="22" t="inlineStr">
         <is>
           <t>8Б
@@ -8274,22 +8278,22 @@
           <t>Аятова А.Ж.</t>
         </is>
       </c>
-      <c r="B9" s="23" t="n"/>
-      <c r="C9" s="23" t="n"/>
-      <c r="D9" s="23" t="n"/>
-      <c r="E9" s="23" t="n"/>
-      <c r="F9" s="23" t="n"/>
-      <c r="G9" s="23" t="n"/>
-      <c r="H9" s="23" t="n"/>
-      <c r="I9" s="23" t="n"/>
-      <c r="J9" s="23" t="n"/>
-      <c r="K9" s="23" t="n"/>
-      <c r="L9" s="23" t="n"/>
-      <c r="M9" s="23" t="n"/>
-      <c r="N9" s="23" t="n"/>
-      <c r="O9" s="23" t="n"/>
-      <c r="P9" s="23" t="n"/>
-      <c r="Q9" s="23" t="n"/>
+      <c r="B9" s="24" t="n"/>
+      <c r="C9" s="24" t="n"/>
+      <c r="D9" s="24" t="n"/>
+      <c r="E9" s="24" t="n"/>
+      <c r="F9" s="24" t="n"/>
+      <c r="G9" s="24" t="n"/>
+      <c r="H9" s="24" t="n"/>
+      <c r="I9" s="24" t="n"/>
+      <c r="J9" s="24" t="n"/>
+      <c r="K9" s="24" t="n"/>
+      <c r="L9" s="24" t="n"/>
+      <c r="M9" s="24" t="n"/>
+      <c r="N9" s="24" t="n"/>
+      <c r="O9" s="24" t="n"/>
+      <c r="P9" s="24" t="n"/>
+      <c r="Q9" s="24" t="n"/>
       <c r="R9" s="22" t="inlineStr">
         <is>
           <t>8Ә
@@ -8318,22 +8322,22 @@
       <c r="W9" s="22" t="n"/>
       <c r="X9" s="22" t="n"/>
       <c r="Y9" s="22" t="n"/>
-      <c r="Z9" s="23" t="n"/>
-      <c r="AA9" s="23" t="n"/>
-      <c r="AB9" s="23" t="n"/>
-      <c r="AC9" s="23" t="n"/>
-      <c r="AD9" s="23" t="n"/>
-      <c r="AE9" s="23" t="n"/>
-      <c r="AF9" s="23" t="n"/>
-      <c r="AG9" s="23" t="n"/>
-      <c r="AH9" s="23" t="n"/>
-      <c r="AI9" s="23" t="n"/>
-      <c r="AJ9" s="23" t="n"/>
-      <c r="AK9" s="23" t="n"/>
-      <c r="AL9" s="23" t="n"/>
-      <c r="AM9" s="23" t="n"/>
-      <c r="AN9" s="23" t="n"/>
-      <c r="AO9" s="23" t="n"/>
+      <c r="Z9" s="24" t="n"/>
+      <c r="AA9" s="24" t="n"/>
+      <c r="AB9" s="24" t="n"/>
+      <c r="AC9" s="24" t="n"/>
+      <c r="AD9" s="24" t="n"/>
+      <c r="AE9" s="24" t="n"/>
+      <c r="AF9" s="24" t="n"/>
+      <c r="AG9" s="24" t="n"/>
+      <c r="AH9" s="24" t="n"/>
+      <c r="AI9" s="24" t="n"/>
+      <c r="AJ9" s="24" t="n"/>
+      <c r="AK9" s="24" t="n"/>
+      <c r="AL9" s="24" t="n"/>
+      <c r="AM9" s="24" t="n"/>
+      <c r="AN9" s="24" t="n"/>
+      <c r="AO9" s="24" t="n"/>
       <c r="AP9" s="21" t="n">
         <v>4</v>
       </c>
@@ -8393,7 +8397,7 @@
 каб. химии (№17)</t>
         </is>
       </c>
-      <c r="M10" s="24" t="inlineStr">
+      <c r="M10" s="23" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -8419,7 +8423,7 @@
 каб. биологии (№19)</t>
         </is>
       </c>
-      <c r="T10" s="24" t="inlineStr">
+      <c r="T10" s="23" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -8451,7 +8455,7 @@
 каб. химии (№17)</t>
         </is>
       </c>
-      <c r="AB10" s="24" t="inlineStr">
+      <c r="AB10" s="23" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -8517,17 +8521,17 @@
           <t>Байгазиева А.Д.</t>
         </is>
       </c>
-      <c r="B11" s="23" t="n"/>
-      <c r="C11" s="23" t="n"/>
-      <c r="D11" s="23" t="n"/>
-      <c r="E11" s="23" t="n"/>
-      <c r="F11" s="23" t="n"/>
-      <c r="G11" s="23" t="n"/>
-      <c r="H11" s="23" t="n"/>
-      <c r="I11" s="23" t="n"/>
-      <c r="J11" s="23" t="n"/>
-      <c r="K11" s="23" t="n"/>
-      <c r="L11" s="23" t="n"/>
+      <c r="B11" s="24" t="n"/>
+      <c r="C11" s="24" t="n"/>
+      <c r="D11" s="24" t="n"/>
+      <c r="E11" s="24" t="n"/>
+      <c r="F11" s="24" t="n"/>
+      <c r="G11" s="24" t="n"/>
+      <c r="H11" s="24" t="n"/>
+      <c r="I11" s="24" t="n"/>
+      <c r="J11" s="24" t="n"/>
+      <c r="K11" s="24" t="n"/>
+      <c r="L11" s="24" t="n"/>
       <c r="M11" s="22" t="inlineStr">
         <is>
           <t>8Ә
@@ -8540,20 +8544,20 @@
 каб. биологии (№19)</t>
         </is>
       </c>
-      <c r="O11" s="23" t="n"/>
-      <c r="P11" s="23" t="n"/>
-      <c r="Q11" s="23" t="n"/>
-      <c r="R11" s="23" t="n"/>
-      <c r="S11" s="23" t="n"/>
-      <c r="T11" s="23" t="n"/>
-      <c r="U11" s="23" t="n"/>
-      <c r="V11" s="23" t="n"/>
-      <c r="W11" s="23" t="n"/>
-      <c r="X11" s="23" t="n"/>
-      <c r="Y11" s="23" t="n"/>
-      <c r="Z11" s="23" t="n"/>
-      <c r="AA11" s="23" t="n"/>
-      <c r="AB11" s="23" t="n"/>
+      <c r="O11" s="24" t="n"/>
+      <c r="P11" s="24" t="n"/>
+      <c r="Q11" s="24" t="n"/>
+      <c r="R11" s="24" t="n"/>
+      <c r="S11" s="24" t="n"/>
+      <c r="T11" s="24" t="n"/>
+      <c r="U11" s="24" t="n"/>
+      <c r="V11" s="24" t="n"/>
+      <c r="W11" s="24" t="n"/>
+      <c r="X11" s="24" t="n"/>
+      <c r="Y11" s="24" t="n"/>
+      <c r="Z11" s="24" t="n"/>
+      <c r="AA11" s="24" t="n"/>
+      <c r="AB11" s="24" t="n"/>
       <c r="AC11" s="22" t="inlineStr">
         <is>
           <t>8Ә
@@ -8566,17 +8570,17 @@
 каб. биологии (№19)</t>
         </is>
       </c>
-      <c r="AE11" s="23" t="n"/>
-      <c r="AF11" s="23" t="n"/>
-      <c r="AG11" s="23" t="n"/>
-      <c r="AH11" s="23" t="n"/>
-      <c r="AI11" s="23" t="n"/>
-      <c r="AJ11" s="23" t="n"/>
-      <c r="AK11" s="23" t="n"/>
-      <c r="AL11" s="23" t="n"/>
-      <c r="AM11" s="23" t="n"/>
-      <c r="AN11" s="23" t="n"/>
-      <c r="AO11" s="23" t="n"/>
+      <c r="AE11" s="24" t="n"/>
+      <c r="AF11" s="24" t="n"/>
+      <c r="AG11" s="24" t="n"/>
+      <c r="AH11" s="24" t="n"/>
+      <c r="AI11" s="24" t="n"/>
+      <c r="AJ11" s="24" t="n"/>
+      <c r="AK11" s="24" t="n"/>
+      <c r="AL11" s="24" t="n"/>
+      <c r="AM11" s="24" t="n"/>
+      <c r="AN11" s="24" t="n"/>
+      <c r="AO11" s="24" t="n"/>
       <c r="AP11" s="21" t="n">
         <v>4</v>
       </c>
@@ -8680,7 +8684,7 @@
 каб. казахского языка и литературы (№23)</t>
         </is>
       </c>
-      <c r="V12" s="24" t="inlineStr">
+      <c r="V12" s="23" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -8732,12 +8736,12 @@
 каб. казахского языка и литературы (№23)</t>
         </is>
       </c>
-      <c r="AI12" s="24" t="inlineStr">
+      <c r="AI12" s="23" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
       </c>
-      <c r="AJ12" s="24" t="inlineStr">
+      <c r="AJ12" s="23" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -8775,8 +8779,8 @@
           <t>Балташева З.Т.</t>
         </is>
       </c>
-      <c r="B13" s="23" t="n"/>
-      <c r="C13" s="23" t="n"/>
+      <c r="B13" s="24" t="n"/>
+      <c r="C13" s="24" t="n"/>
       <c r="D13" s="22" t="inlineStr">
         <is>
           <t>8Ә
@@ -8803,38 +8807,38 @@
       </c>
       <c r="H13" s="22" t="n"/>
       <c r="I13" s="22" t="n"/>
-      <c r="J13" s="23" t="n"/>
-      <c r="K13" s="23" t="n"/>
-      <c r="L13" s="23" t="n"/>
-      <c r="M13" s="23" t="n"/>
-      <c r="N13" s="23" t="n"/>
-      <c r="O13" s="23" t="n"/>
-      <c r="P13" s="23" t="n"/>
-      <c r="Q13" s="23" t="n"/>
-      <c r="R13" s="23" t="n"/>
-      <c r="S13" s="23" t="n"/>
-      <c r="T13" s="23" t="n"/>
-      <c r="U13" s="23" t="n"/>
-      <c r="V13" s="23" t="n"/>
-      <c r="W13" s="23" t="n"/>
-      <c r="X13" s="23" t="n"/>
-      <c r="Y13" s="23" t="n"/>
-      <c r="Z13" s="23" t="n"/>
-      <c r="AA13" s="23" t="n"/>
-      <c r="AB13" s="23" t="n"/>
-      <c r="AC13" s="23" t="n"/>
-      <c r="AD13" s="23" t="n"/>
-      <c r="AE13" s="23" t="n"/>
-      <c r="AF13" s="23" t="n"/>
-      <c r="AG13" s="23" t="n"/>
-      <c r="AH13" s="23" t="n"/>
-      <c r="AI13" s="23" t="n"/>
-      <c r="AJ13" s="23" t="n"/>
-      <c r="AK13" s="23" t="n"/>
-      <c r="AL13" s="23" t="n"/>
-      <c r="AM13" s="23" t="n"/>
-      <c r="AN13" s="23" t="n"/>
-      <c r="AO13" s="23" t="n"/>
+      <c r="J13" s="24" t="n"/>
+      <c r="K13" s="24" t="n"/>
+      <c r="L13" s="24" t="n"/>
+      <c r="M13" s="24" t="n"/>
+      <c r="N13" s="24" t="n"/>
+      <c r="O13" s="24" t="n"/>
+      <c r="P13" s="24" t="n"/>
+      <c r="Q13" s="24" t="n"/>
+      <c r="R13" s="24" t="n"/>
+      <c r="S13" s="24" t="n"/>
+      <c r="T13" s="24" t="n"/>
+      <c r="U13" s="24" t="n"/>
+      <c r="V13" s="24" t="n"/>
+      <c r="W13" s="24" t="n"/>
+      <c r="X13" s="24" t="n"/>
+      <c r="Y13" s="24" t="n"/>
+      <c r="Z13" s="24" t="n"/>
+      <c r="AA13" s="24" t="n"/>
+      <c r="AB13" s="24" t="n"/>
+      <c r="AC13" s="24" t="n"/>
+      <c r="AD13" s="24" t="n"/>
+      <c r="AE13" s="24" t="n"/>
+      <c r="AF13" s="24" t="n"/>
+      <c r="AG13" s="24" t="n"/>
+      <c r="AH13" s="24" t="n"/>
+      <c r="AI13" s="24" t="n"/>
+      <c r="AJ13" s="24" t="n"/>
+      <c r="AK13" s="24" t="n"/>
+      <c r="AL13" s="24" t="n"/>
+      <c r="AM13" s="24" t="n"/>
+      <c r="AN13" s="24" t="n"/>
+      <c r="AO13" s="24" t="n"/>
       <c r="AP13" s="21" t="n">
         <v>4</v>
       </c>
@@ -8866,7 +8870,7 @@
 каб. информатики (№26)</t>
         </is>
       </c>
-      <c r="E14" s="24" t="inlineStr">
+      <c r="E14" s="23" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -8897,7 +8901,7 @@
 каб. информатики (№26)</t>
         </is>
       </c>
-      <c r="L14" s="24" t="inlineStr">
+      <c r="L14" s="23" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -8908,7 +8912,7 @@
 каб. информатики (№26)</t>
         </is>
       </c>
-      <c r="N14" s="24" t="inlineStr">
+      <c r="N14" s="23" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -8982,18 +8986,18 @@
 каб. информатики (№26)</t>
         </is>
       </c>
-      <c r="AC14" s="23" t="n"/>
-      <c r="AD14" s="23" t="n"/>
-      <c r="AE14" s="23" t="n"/>
-      <c r="AF14" s="23" t="n"/>
-      <c r="AG14" s="23" t="n"/>
+      <c r="AC14" s="24" t="n"/>
+      <c r="AD14" s="24" t="n"/>
+      <c r="AE14" s="24" t="n"/>
+      <c r="AF14" s="24" t="n"/>
+      <c r="AG14" s="24" t="n"/>
       <c r="AH14" s="22" t="inlineStr">
         <is>
           <t>5Б
 каб. информатики (№26)</t>
         </is>
       </c>
-      <c r="AI14" s="24" t="inlineStr">
+      <c r="AI14" s="23" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -9004,7 +9008,7 @@
 каб. информатики (№26)</t>
         </is>
       </c>
-      <c r="AK14" s="24" t="inlineStr">
+      <c r="AK14" s="23" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -9113,7 +9117,7 @@
 каб. робототехники (№15)</t>
         </is>
       </c>
-      <c r="F16" s="24" t="inlineStr">
+      <c r="F16" s="23" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -9208,497 +9212,492 @@
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="21" t="inlineStr">
         <is>
-          <t>Дмитриев Е.В.</t>
+          <t>Власова А.К.</t>
         </is>
       </c>
       <c r="B17" s="22" t="inlineStr">
         <is>
-          <t>9Б
-каб. русского языка (№20)</t>
+          <t>8А
+каб. английского языка (№27)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
         <is>
-          <t>11Б
-каб. русского языка (№20)</t>
+          <t>1Б
+нач. класс 1Б (№8)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
         <is>
-          <t>8А
-каб. русского языка (№20)</t>
-        </is>
-      </c>
-      <c r="E17" s="22" t="inlineStr">
-        <is>
-          <t>8Б
-каб. русского языка (№20)</t>
-        </is>
-      </c>
-      <c r="F17" s="22" t="inlineStr">
-        <is>
-          <t>10А
-каб. русского языка (№20)</t>
-        </is>
-      </c>
-      <c r="G17" s="23" t="n"/>
-      <c r="H17" s="23" t="n"/>
+          <t>3А
+нач. класс 3А (№7)</t>
+        </is>
+      </c>
+      <c r="E17" s="23" t="inlineStr">
+        <is>
+          <t>окно</t>
+        </is>
+      </c>
+      <c r="F17" s="23" t="inlineStr">
+        <is>
+          <t>окно</t>
+        </is>
+      </c>
+      <c r="G17" s="22" t="inlineStr">
+        <is>
+          <t>8Ә
+каб. НВП (№28)</t>
+        </is>
+      </c>
+      <c r="H17" s="22" t="n"/>
       <c r="I17" s="22" t="n"/>
       <c r="J17" s="22" t="n"/>
-      <c r="K17" s="22" t="n"/>
+      <c r="K17" s="22" t="inlineStr">
+        <is>
+          <t>7А
+каб. физики (№16)</t>
+        </is>
+      </c>
       <c r="L17" s="22" t="inlineStr">
         <is>
+          <t>8Ә
+каб. физики (№16)</t>
+        </is>
+      </c>
+      <c r="M17" s="22" t="inlineStr">
+        <is>
+          <t>8А
+каб. физики (№16)</t>
+        </is>
+      </c>
+      <c r="N17" s="22" t="n"/>
+      <c r="O17" s="22" t="n"/>
+      <c r="P17" s="22" t="n"/>
+      <c r="Q17" s="22" t="n"/>
+      <c r="R17" s="22" t="n"/>
+      <c r="S17" s="22" t="n"/>
+      <c r="T17" s="22" t="inlineStr">
+        <is>
+          <t>8А
+каб. английского языка (№27)</t>
+        </is>
+      </c>
+      <c r="U17" s="23" t="inlineStr">
+        <is>
+          <t>окно</t>
+        </is>
+      </c>
+      <c r="V17" s="22" t="inlineStr">
+        <is>
           <t>7А
-каб. русского языка (№20)</t>
-        </is>
-      </c>
-      <c r="M17" s="22" t="inlineStr">
-        <is>
-          <t>9Б
-каб. русского языка (№20)</t>
-        </is>
-      </c>
-      <c r="N17" s="22" t="inlineStr">
-        <is>
-          <t>8Б
-каб. русского языка (№20)</t>
-        </is>
-      </c>
-      <c r="O17" s="23" t="n"/>
-      <c r="P17" s="22" t="inlineStr">
-        <is>
-          <t>8А
-каб. русского языка (№20)</t>
-        </is>
-      </c>
-      <c r="Q17" s="22" t="n"/>
-      <c r="R17" s="22" t="inlineStr">
-        <is>
-          <t>8А
-каб. русского языка (№20)</t>
-        </is>
-      </c>
-      <c r="S17" s="22" t="inlineStr">
-        <is>
-          <t>7А
-каб. русского языка (№20)</t>
-        </is>
-      </c>
-      <c r="T17" s="22" t="inlineStr">
-        <is>
-          <t>9Б
-каб. русского языка (№20)</t>
-        </is>
-      </c>
-      <c r="U17" s="22" t="inlineStr">
-        <is>
-          <t>11Б
-каб. русского языка (№20)</t>
-        </is>
-      </c>
-      <c r="V17" s="22" t="inlineStr">
-        <is>
-          <t>10А
-каб. русского языка (№20)</t>
+каб. английского языка (№27)</t>
         </is>
       </c>
       <c r="W17" s="22" t="inlineStr">
         <is>
-          <t>8Б
-каб. русского языка (№20)</t>
+          <t>8Ә
+каб. английского языка (№27)</t>
         </is>
       </c>
       <c r="X17" s="22" t="n"/>
       <c r="Y17" s="22" t="n"/>
       <c r="Z17" s="22" t="inlineStr">
         <is>
-          <t>8Б
-каб. русского языка (№20)</t>
+          <t>8Ә
+каб. НВП (№28)</t>
         </is>
       </c>
       <c r="AA17" s="22" t="inlineStr">
         <is>
-          <t>9Б
-каб. русского языка (№20)</t>
+          <t>7А
+каб. НВП (№28)</t>
         </is>
       </c>
       <c r="AB17" s="22" t="inlineStr">
         <is>
+          <t>1Б
+нач. класс 1Б (№8)</t>
+        </is>
+      </c>
+      <c r="AC17" s="22" t="inlineStr">
+        <is>
+          <t>3А
+нач. класс 3А (№7)</t>
+        </is>
+      </c>
+      <c r="AD17" s="22" t="inlineStr">
+        <is>
           <t>8А
-каб. русского языка (№20)</t>
-        </is>
-      </c>
-      <c r="AC17" s="22" t="inlineStr">
-        <is>
-          <t>11Б
-каб. русского языка (№20)</t>
-        </is>
-      </c>
-      <c r="AD17" s="22" t="inlineStr">
-        <is>
-          <t>7А
-каб. русского языка (№20)</t>
-        </is>
-      </c>
-      <c r="AE17" s="23" t="n"/>
-      <c r="AF17" s="23" t="n"/>
+каб. английского языка (№27)</t>
+        </is>
+      </c>
+      <c r="AE17" s="22" t="n"/>
+      <c r="AF17" s="22" t="n"/>
       <c r="AG17" s="22" t="n"/>
       <c r="AH17" s="22" t="inlineStr">
         <is>
-          <t>8А
-каб. русского языка (№20)</t>
+          <t>8Ә
+каб. английского языка (№27)</t>
         </is>
       </c>
       <c r="AI17" s="22" t="inlineStr">
         <is>
-          <t>9Б
-каб. русского языка (№20)</t>
-        </is>
-      </c>
-      <c r="AJ17" s="22" t="inlineStr">
-        <is>
-          <t>8Б
-каб. русского языка (№20)</t>
-        </is>
-      </c>
-      <c r="AK17" s="22" t="inlineStr">
-        <is>
-          <t>10А
-каб. русского языка (№20)</t>
-        </is>
-      </c>
-      <c r="AL17" s="23" t="n"/>
-      <c r="AM17" s="23" t="n"/>
+          <t>7А
+каб. английского языка (№27)</t>
+        </is>
+      </c>
+      <c r="AJ17" s="23" t="inlineStr">
+        <is>
+          <t>окно</t>
+        </is>
+      </c>
+      <c r="AK17" s="23" t="inlineStr">
+        <is>
+          <t>окно</t>
+        </is>
+      </c>
+      <c r="AL17" s="23" t="inlineStr">
+        <is>
+          <t>окно</t>
+        </is>
+      </c>
+      <c r="AM17" s="22" t="inlineStr">
+        <is>
+          <t>3А
+нач. класс 3А (№7)</t>
+        </is>
+      </c>
       <c r="AN17" s="22" t="n"/>
       <c r="AO17" s="22" t="n"/>
       <c r="AP17" s="21" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="AQ17" s="21" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="21" t="inlineStr">
         <is>
-          <t>Досаева М.Х.</t>
+          <t>Дмитриев Е.В.</t>
         </is>
       </c>
       <c r="B18" s="22" t="inlineStr">
         <is>
-          <t>5А
-каб. истории (№14)</t>
-        </is>
-      </c>
-      <c r="C18" s="24" t="inlineStr">
-        <is>
-          <t>окно</t>
+          <t>9Б
+каб. русского языка (№20)</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>11Б
+каб. русского языка (№20)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
         <is>
-          <t>6А
-каб. истории (№14)</t>
+          <t>8А
+каб. русского языка (№20)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
         <is>
-          <t>11А
-каб. истории (№14)</t>
+          <t>8Б
+каб. русского языка (№20)</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
         <is>
+          <t>10А
+каб. русского языка (№20)</t>
+        </is>
+      </c>
+      <c r="G18" s="24" t="n"/>
+      <c r="H18" s="24" t="n"/>
+      <c r="I18" s="22" t="n"/>
+      <c r="J18" s="22" t="n"/>
+      <c r="K18" s="22" t="n"/>
+      <c r="L18" s="22" t="inlineStr">
+        <is>
+          <t>7А
+каб. русского языка (№20)</t>
+        </is>
+      </c>
+      <c r="M18" s="22" t="inlineStr">
+        <is>
           <t>9Б
-каб. истории (№14)</t>
-        </is>
-      </c>
-      <c r="G18" s="22" t="inlineStr">
+каб. русского языка (№20)</t>
+        </is>
+      </c>
+      <c r="N18" s="22" t="inlineStr">
         <is>
           <t>8Б
-каб. истории (№14)</t>
-        </is>
-      </c>
-      <c r="H18" s="22" t="n"/>
-      <c r="I18" s="22" t="n"/>
-      <c r="J18" s="22" t="inlineStr">
-        <is>
-          <t>5А
-каб. истории (№14)</t>
-        </is>
-      </c>
-      <c r="K18" s="22" t="inlineStr">
-        <is>
-          <t>11А
-каб. истории (№14)</t>
-        </is>
-      </c>
-      <c r="L18" s="24" t="inlineStr">
-        <is>
-          <t>окно</t>
-        </is>
-      </c>
-      <c r="M18" s="22" t="inlineStr">
-        <is>
-          <t>7А
-каб. истории (№14)</t>
-        </is>
-      </c>
-      <c r="N18" s="22" t="inlineStr">
-        <is>
-          <t>6А
-каб. истории (№14)</t>
-        </is>
-      </c>
-      <c r="O18" s="22" t="inlineStr">
-        <is>
-          <t>11Б
-каб. истории (№14)</t>
-        </is>
-      </c>
+каб. русского языка (№20)</t>
+        </is>
+      </c>
+      <c r="O18" s="24" t="n"/>
       <c r="P18" s="22" t="inlineStr">
         <is>
-          <t>9Б
-каб. истории (№14)</t>
+          <t>8А
+каб. русского языка (№20)</t>
         </is>
       </c>
       <c r="Q18" s="22" t="n"/>
       <c r="R18" s="22" t="inlineStr">
         <is>
+          <t>8А
+каб. русского языка (№20)</t>
+        </is>
+      </c>
+      <c r="S18" s="22" t="inlineStr">
+        <is>
+          <t>7А
+каб. русского языка (№20)</t>
+        </is>
+      </c>
+      <c r="T18" s="22" t="inlineStr">
+        <is>
           <t>9Б
-каб. истории (№14)</t>
-        </is>
-      </c>
-      <c r="S18" s="22" t="inlineStr">
-        <is>
-          <t>6А
-каб. истории (№14)</t>
-        </is>
-      </c>
-      <c r="T18" s="22" t="inlineStr">
-        <is>
-          <t>8Ә
-каб. истории (№14)</t>
+каб. русского языка (№20)</t>
         </is>
       </c>
       <c r="U18" s="22" t="inlineStr">
         <is>
+          <t>11Б
+каб. русского языка (№20)</t>
+        </is>
+      </c>
+      <c r="V18" s="22" t="inlineStr">
+        <is>
+          <t>10А
+каб. русского языка (№20)</t>
+        </is>
+      </c>
+      <c r="W18" s="22" t="inlineStr">
+        <is>
           <t>8Б
-каб. истории (№14)</t>
-        </is>
-      </c>
-      <c r="V18" s="24" t="inlineStr">
-        <is>
-          <t>окно</t>
-        </is>
-      </c>
-      <c r="W18" s="22" t="inlineStr">
-        <is>
-          <t>11Б
-каб. истории (№14)</t>
+каб. русского языка (№20)</t>
         </is>
       </c>
       <c r="X18" s="22" t="n"/>
       <c r="Y18" s="22" t="n"/>
       <c r="Z18" s="22" t="inlineStr">
         <is>
+          <t>8Б
+каб. русского языка (№20)</t>
+        </is>
+      </c>
+      <c r="AA18" s="22" t="inlineStr">
+        <is>
+          <t>9Б
+каб. русского языка (№20)</t>
+        </is>
+      </c>
+      <c r="AB18" s="22" t="inlineStr">
+        <is>
+          <t>8А
+каб. русского языка (№20)</t>
+        </is>
+      </c>
+      <c r="AC18" s="22" t="inlineStr">
+        <is>
+          <t>11Б
+каб. русского языка (№20)</t>
+        </is>
+      </c>
+      <c r="AD18" s="22" t="inlineStr">
+        <is>
           <t>7А
-каб. истории (№14)</t>
-        </is>
-      </c>
-      <c r="AA18" s="22" t="inlineStr">
-        <is>
-          <t>11А
-каб. истории (№14)</t>
-        </is>
-      </c>
-      <c r="AB18" s="22" t="inlineStr">
-        <is>
-          <t>5А
-каб. истории (№14)</t>
-        </is>
-      </c>
-      <c r="AC18" s="24" t="inlineStr">
-        <is>
-          <t>окно</t>
-        </is>
-      </c>
-      <c r="AD18" s="24" t="inlineStr">
-        <is>
-          <t>окно</t>
-        </is>
-      </c>
-      <c r="AE18" s="22" t="inlineStr">
-        <is>
-          <t>8Ә
-каб. истории (№14)</t>
-        </is>
-      </c>
-      <c r="AF18" s="22" t="n"/>
+каб. русского языка (№20)</t>
+        </is>
+      </c>
+      <c r="AE18" s="24" t="n"/>
+      <c r="AF18" s="24" t="n"/>
       <c r="AG18" s="22" t="n"/>
       <c r="AH18" s="22" t="inlineStr">
         <is>
-          <t>11А
-каб. истории (№14)</t>
-        </is>
-      </c>
-      <c r="AI18" s="24" t="inlineStr">
-        <is>
-          <t>окно</t>
-        </is>
-      </c>
-      <c r="AJ18" s="24" t="inlineStr">
-        <is>
-          <t>окно</t>
+          <t>8А
+каб. русского языка (№20)</t>
+        </is>
+      </c>
+      <c r="AI18" s="22" t="inlineStr">
+        <is>
+          <t>9Б
+каб. русского языка (№20)</t>
+        </is>
+      </c>
+      <c r="AJ18" s="22" t="inlineStr">
+        <is>
+          <t>8Б
+каб. русского языка (№20)</t>
         </is>
       </c>
       <c r="AK18" s="22" t="inlineStr">
         <is>
-          <t>8Ә
-каб. истории (№14)</t>
-        </is>
-      </c>
-      <c r="AL18" s="22" t="inlineStr">
-        <is>
-          <t>11Б
-каб. истории (№14)</t>
-        </is>
-      </c>
-      <c r="AM18" s="22" t="inlineStr">
-        <is>
-          <t>9Б
-каб. истории (№14)</t>
-        </is>
-      </c>
+          <t>10А
+каб. русского языка (№20)</t>
+        </is>
+      </c>
+      <c r="AL18" s="24" t="n"/>
+      <c r="AM18" s="24" t="n"/>
       <c r="AN18" s="22" t="n"/>
       <c r="AO18" s="22" t="n"/>
       <c r="AP18" s="21" t="n">
         <v>24</v>
       </c>
       <c r="AQ18" s="21" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="21" t="inlineStr">
         <is>
-          <t>Дюсембаева А.К.</t>
+          <t>Досаева М.Х.</t>
         </is>
       </c>
       <c r="B19" s="22" t="inlineStr">
         <is>
-          <t>8А
-каб. английского языка (№27)</t>
-        </is>
-      </c>
-      <c r="C19" s="22" t="inlineStr">
-        <is>
-          <t>1Б
-нач. класс 1Б (№8)</t>
+          <t>5А
+каб. истории (№14)</t>
+        </is>
+      </c>
+      <c r="C19" s="23" t="inlineStr">
+        <is>
+          <t>окно</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
         <is>
-          <t>3А
-нач. класс 3А (№7)</t>
-        </is>
-      </c>
-      <c r="E19" s="24" t="inlineStr">
-        <is>
-          <t>окно</t>
-        </is>
-      </c>
-      <c r="F19" s="24" t="inlineStr">
-        <is>
-          <t>окно</t>
+          <t>6А
+каб. истории (№14)</t>
+        </is>
+      </c>
+      <c r="E19" s="22" t="inlineStr">
+        <is>
+          <t>11А
+каб. истории (№14)</t>
+        </is>
+      </c>
+      <c r="F19" s="22" t="inlineStr">
+        <is>
+          <t>9Б
+каб. истории (№14)</t>
         </is>
       </c>
       <c r="G19" s="22" t="inlineStr">
         <is>
-          <t>8Ә
-каб. НВП (№28)</t>
+          <t>8Б
+каб. истории (№14)</t>
         </is>
       </c>
       <c r="H19" s="22" t="n"/>
       <c r="I19" s="22" t="n"/>
-      <c r="J19" s="22" t="n"/>
+      <c r="J19" s="22" t="inlineStr">
+        <is>
+          <t>5А
+каб. истории (№14)</t>
+        </is>
+      </c>
       <c r="K19" s="22" t="inlineStr">
         <is>
+          <t>11А
+каб. истории (№14)</t>
+        </is>
+      </c>
+      <c r="L19" s="23" t="inlineStr">
+        <is>
+          <t>окно</t>
+        </is>
+      </c>
+      <c r="M19" s="22" t="inlineStr">
+        <is>
           <t>7А
-каб. физики (№16)</t>
-        </is>
-      </c>
-      <c r="L19" s="22" t="inlineStr">
+каб. истории (№14)</t>
+        </is>
+      </c>
+      <c r="N19" s="22" t="inlineStr">
+        <is>
+          <t>6А
+каб. истории (№14)</t>
+        </is>
+      </c>
+      <c r="O19" s="22" t="inlineStr">
+        <is>
+          <t>11Б
+каб. истории (№14)</t>
+        </is>
+      </c>
+      <c r="P19" s="22" t="inlineStr">
+        <is>
+          <t>9Б
+каб. истории (№14)</t>
+        </is>
+      </c>
+      <c r="Q19" s="22" t="n"/>
+      <c r="R19" s="22" t="inlineStr">
+        <is>
+          <t>9Б
+каб. истории (№14)</t>
+        </is>
+      </c>
+      <c r="S19" s="22" t="inlineStr">
+        <is>
+          <t>6А
+каб. истории (№14)</t>
+        </is>
+      </c>
+      <c r="T19" s="22" t="inlineStr">
         <is>
           <t>8Ә
-каб. физики (№16)</t>
-        </is>
-      </c>
-      <c r="M19" s="22" t="inlineStr">
-        <is>
-          <t>8А
-каб. физики (№16)</t>
-        </is>
-      </c>
-      <c r="N19" s="22" t="n"/>
-      <c r="O19" s="22" t="n"/>
-      <c r="P19" s="22" t="n"/>
-      <c r="Q19" s="22" t="n"/>
-      <c r="R19" s="22" t="n"/>
-      <c r="S19" s="22" t="n"/>
-      <c r="T19" s="22" t="inlineStr">
-        <is>
-          <t>8А
-каб. английского языка (№27)</t>
-        </is>
-      </c>
-      <c r="U19" s="24" t="inlineStr">
+каб. истории (№14)</t>
+        </is>
+      </c>
+      <c r="U19" s="22" t="inlineStr">
+        <is>
+          <t>8Б
+каб. истории (№14)</t>
+        </is>
+      </c>
+      <c r="V19" s="23" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
       </c>
-      <c r="V19" s="22" t="inlineStr">
-        <is>
-          <t>7А
-каб. английского языка (№27)</t>
-        </is>
-      </c>
       <c r="W19" s="22" t="inlineStr">
         <is>
-          <t>8Ә
-каб. английского языка (№27)</t>
+          <t>11Б
+каб. истории (№14)</t>
         </is>
       </c>
       <c r="X19" s="22" t="n"/>
       <c r="Y19" s="22" t="n"/>
       <c r="Z19" s="22" t="inlineStr">
         <is>
+          <t>7А
+каб. истории (№14)</t>
+        </is>
+      </c>
+      <c r="AA19" s="22" t="inlineStr">
+        <is>
+          <t>11А
+каб. истории (№14)</t>
+        </is>
+      </c>
+      <c r="AB19" s="22" t="inlineStr">
+        <is>
+          <t>5А
+каб. истории (№14)</t>
+        </is>
+      </c>
+      <c r="AC19" s="23" t="inlineStr">
+        <is>
+          <t>окно</t>
+        </is>
+      </c>
+      <c r="AD19" s="22" t="inlineStr">
+        <is>
           <t>8Ә
-каб. НВП (№28)</t>
-        </is>
-      </c>
-      <c r="AA19" s="22" t="inlineStr">
-        <is>
-          <t>7А
-каб. НВП (№28)</t>
-        </is>
-      </c>
-      <c r="AB19" s="22" t="inlineStr">
-        <is>
-          <t>1Б
-нач. класс 1Б (№8)</t>
-        </is>
-      </c>
-      <c r="AC19" s="22" t="inlineStr">
-        <is>
-          <t>3А
-нач. класс 3А (№7)</t>
-        </is>
-      </c>
-      <c r="AD19" s="22" t="inlineStr">
-        <is>
-          <t>8А
-каб. английского языка (№27)</t>
+каб. истории (№14)</t>
         </is>
       </c>
       <c r="AE19" s="22" t="n"/>
@@ -9706,41 +9705,42 @@
       <c r="AG19" s="22" t="n"/>
       <c r="AH19" s="22" t="inlineStr">
         <is>
+          <t>11А
+каб. истории (№14)</t>
+        </is>
+      </c>
+      <c r="AI19" s="23" t="inlineStr">
+        <is>
+          <t>окно</t>
+        </is>
+      </c>
+      <c r="AJ19" s="23" t="inlineStr">
+        <is>
+          <t>окно</t>
+        </is>
+      </c>
+      <c r="AK19" s="22" t="inlineStr">
+        <is>
           <t>8Ә
-каб. английского языка (№27)</t>
-        </is>
-      </c>
-      <c r="AI19" s="22" t="inlineStr">
-        <is>
-          <t>7А
-каб. английского языка (№27)</t>
-        </is>
-      </c>
-      <c r="AJ19" s="24" t="inlineStr">
-        <is>
-          <t>окно</t>
-        </is>
-      </c>
-      <c r="AK19" s="24" t="inlineStr">
-        <is>
-          <t>окно</t>
-        </is>
-      </c>
-      <c r="AL19" s="24" t="inlineStr">
-        <is>
-          <t>окно</t>
+каб. истории (№14)</t>
+        </is>
+      </c>
+      <c r="AL19" s="22" t="inlineStr">
+        <is>
+          <t>11Б
+каб. истории (№14)</t>
         </is>
       </c>
       <c r="AM19" s="22" t="inlineStr">
         <is>
-          <t>3А
-нач. класс 3А (№7)</t>
+          <t>9Б
+каб. истории (№14)</t>
         </is>
       </c>
       <c r="AN19" s="22" t="n"/>
       <c r="AO19" s="22" t="n"/>
       <c r="AP19" s="21" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="AQ19" s="21" t="n">
         <v>6</v>
@@ -9752,28 +9752,28 @@
           <t>Жантимиров А.К.</t>
         </is>
       </c>
-      <c r="B20" s="23" t="n"/>
-      <c r="C20" s="23" t="n"/>
-      <c r="D20" s="23" t="n"/>
-      <c r="E20" s="23" t="n"/>
-      <c r="F20" s="23" t="n"/>
-      <c r="G20" s="23" t="n"/>
-      <c r="H20" s="23" t="n"/>
-      <c r="I20" s="23" t="n"/>
-      <c r="J20" s="23" t="n"/>
-      <c r="K20" s="23" t="n"/>
-      <c r="L20" s="23" t="n"/>
-      <c r="M20" s="23" t="n"/>
-      <c r="N20" s="23" t="n"/>
-      <c r="O20" s="23" t="n"/>
-      <c r="P20" s="23" t="n"/>
-      <c r="Q20" s="23" t="n"/>
+      <c r="B20" s="24" t="n"/>
+      <c r="C20" s="24" t="n"/>
+      <c r="D20" s="24" t="n"/>
+      <c r="E20" s="24" t="n"/>
+      <c r="F20" s="24" t="n"/>
+      <c r="G20" s="24" t="n"/>
+      <c r="H20" s="24" t="n"/>
+      <c r="I20" s="24" t="n"/>
+      <c r="J20" s="24" t="n"/>
+      <c r="K20" s="24" t="n"/>
+      <c r="L20" s="24" t="n"/>
+      <c r="M20" s="24" t="n"/>
+      <c r="N20" s="24" t="n"/>
+      <c r="O20" s="24" t="n"/>
+      <c r="P20" s="24" t="n"/>
+      <c r="Q20" s="24" t="n"/>
       <c r="R20" s="22" t="n"/>
       <c r="S20" s="22" t="n"/>
       <c r="T20" s="22" t="n"/>
       <c r="U20" s="22" t="inlineStr">
         <is>
-          <t>7А/Мальчики
+          <t>1А
 каб. технологии (мальчики) (№39)</t>
         </is>
       </c>
@@ -9798,12 +9798,12 @@
 каб. технологии (мальчики) (№39)</t>
         </is>
       </c>
-      <c r="AB20" s="24" t="inlineStr">
+      <c r="AB20" s="23" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
       </c>
-      <c r="AC20" s="24" t="inlineStr">
+      <c r="AC20" s="23" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -9814,7 +9814,7 @@
 каб. технологии (мальчики) (№39)</t>
         </is>
       </c>
-      <c r="AE20" s="24" t="inlineStr">
+      <c r="AE20" s="23" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -9826,7 +9826,12 @@
         </is>
       </c>
       <c r="AG20" s="22" t="n"/>
-      <c r="AH20" s="22" t="n"/>
+      <c r="AH20" s="22" t="inlineStr">
+        <is>
+          <t>7А/Мальчики
+каб. технологии (мальчики) (№39)</t>
+        </is>
+      </c>
       <c r="AI20" s="22" t="inlineStr">
         <is>
           <t>6Б/Мальчики
@@ -9839,7 +9844,7 @@
 каб. технологии (мальчики) (№39)</t>
         </is>
       </c>
-      <c r="AK20" s="24" t="inlineStr">
+      <c r="AK20" s="23" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -9864,7 +9869,7 @@
       </c>
       <c r="AO20" s="22" t="n"/>
       <c r="AP20" s="21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ20" s="21" t="n">
         <v>4</v>
@@ -9876,21 +9881,21 @@
           <t>Жантимиров Э.А.</t>
         </is>
       </c>
-      <c r="B21" s="23" t="n"/>
-      <c r="C21" s="23" t="n"/>
-      <c r="D21" s="23" t="n"/>
-      <c r="E21" s="23" t="n"/>
-      <c r="F21" s="23" t="n"/>
-      <c r="G21" s="23" t="n"/>
-      <c r="H21" s="23" t="n"/>
-      <c r="I21" s="23" t="n"/>
+      <c r="B21" s="24" t="n"/>
+      <c r="C21" s="24" t="n"/>
+      <c r="D21" s="24" t="n"/>
+      <c r="E21" s="24" t="n"/>
+      <c r="F21" s="24" t="n"/>
+      <c r="G21" s="24" t="n"/>
+      <c r="H21" s="24" t="n"/>
+      <c r="I21" s="24" t="n"/>
       <c r="J21" s="22" t="inlineStr">
         <is>
           <t>2А
 каб. информатики (№26)</t>
         </is>
       </c>
-      <c r="K21" s="24" t="inlineStr">
+      <c r="K21" s="23" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -9901,7 +9906,7 @@
 каб. информатики (№26)</t>
         </is>
       </c>
-      <c r="M21" s="24" t="inlineStr">
+      <c r="M21" s="23" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -9912,7 +9917,7 @@
 каб. информатики (№26)</t>
         </is>
       </c>
-      <c r="O21" s="24" t="inlineStr">
+      <c r="O21" s="23" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -9924,22 +9929,22 @@
         </is>
       </c>
       <c r="Q21" s="22" t="n"/>
-      <c r="R21" s="23" t="n"/>
-      <c r="S21" s="23" t="n"/>
-      <c r="T21" s="23" t="n"/>
-      <c r="U21" s="23" t="n"/>
-      <c r="V21" s="23" t="n"/>
-      <c r="W21" s="23" t="n"/>
-      <c r="X21" s="23" t="n"/>
-      <c r="Y21" s="23" t="n"/>
-      <c r="Z21" s="23" t="n"/>
-      <c r="AA21" s="23" t="n"/>
-      <c r="AB21" s="23" t="n"/>
-      <c r="AC21" s="23" t="n"/>
-      <c r="AD21" s="23" t="n"/>
-      <c r="AE21" s="23" t="n"/>
-      <c r="AF21" s="23" t="n"/>
-      <c r="AG21" s="23" t="n"/>
+      <c r="R21" s="24" t="n"/>
+      <c r="S21" s="24" t="n"/>
+      <c r="T21" s="24" t="n"/>
+      <c r="U21" s="24" t="n"/>
+      <c r="V21" s="24" t="n"/>
+      <c r="W21" s="24" t="n"/>
+      <c r="X21" s="24" t="n"/>
+      <c r="Y21" s="24" t="n"/>
+      <c r="Z21" s="24" t="n"/>
+      <c r="AA21" s="24" t="n"/>
+      <c r="AB21" s="24" t="n"/>
+      <c r="AC21" s="24" t="n"/>
+      <c r="AD21" s="24" t="n"/>
+      <c r="AE21" s="24" t="n"/>
+      <c r="AF21" s="24" t="n"/>
+      <c r="AG21" s="24" t="n"/>
       <c r="AH21" s="22" t="n"/>
       <c r="AI21" s="22" t="inlineStr">
         <is>
@@ -9947,7 +9952,7 @@
 каб. информатики (№26)</t>
         </is>
       </c>
-      <c r="AJ21" s="24" t="inlineStr">
+      <c r="AJ21" s="23" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -9958,12 +9963,12 @@
 каб. информатики (№26)</t>
         </is>
       </c>
-      <c r="AL21" s="24" t="inlineStr">
+      <c r="AL21" s="23" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
       </c>
-      <c r="AM21" s="24" t="inlineStr">
+      <c r="AM21" s="23" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -10070,7 +10075,7 @@
       <c r="U22" s="22" t="inlineStr">
         <is>
           <t>2А
-каб. технологии (девочки) (№29)</t>
+нач. класс 2А/4А (№42)</t>
         </is>
       </c>
       <c r="V22" s="22" t="inlineStr">
@@ -10157,67 +10162,79 @@
         </is>
       </c>
       <c r="B23" s="22" t="n"/>
-      <c r="C23" s="23" t="n"/>
+      <c r="C23" s="24" t="n"/>
       <c r="D23" s="22" t="n"/>
       <c r="E23" s="22" t="n"/>
       <c r="F23" s="22" t="n"/>
       <c r="G23" s="22" t="n"/>
       <c r="H23" s="22" t="n"/>
       <c r="I23" s="22" t="n"/>
-      <c r="J23" s="23" t="n"/>
+      <c r="J23" s="24" t="n"/>
       <c r="K23" s="22" t="n"/>
-      <c r="L23" s="23" t="n"/>
+      <c r="L23" s="24" t="n"/>
       <c r="M23" s="22" t="n"/>
       <c r="N23" s="22" t="n"/>
       <c r="O23" s="22" t="n"/>
       <c r="P23" s="22" t="n"/>
       <c r="Q23" s="22" t="n"/>
-      <c r="R23" s="23" t="n"/>
+      <c r="R23" s="24" t="n"/>
       <c r="S23" s="22" t="inlineStr">
         <is>
           <t>2Б
 каб. технологии (девочки) (№29)</t>
         </is>
       </c>
-      <c r="T23" s="23" t="n"/>
-      <c r="U23" s="22" t="inlineStr">
+      <c r="T23" s="23" t="inlineStr">
+        <is>
+          <t>окно</t>
+        </is>
+      </c>
+      <c r="U23" s="23" t="inlineStr">
+        <is>
+          <t>окно</t>
+        </is>
+      </c>
+      <c r="V23" s="23" t="inlineStr">
+        <is>
+          <t>окно</t>
+        </is>
+      </c>
+      <c r="W23" s="22" t="inlineStr">
+        <is>
+          <t>6Б/Девочки
+каб. технологии (девочки) (№29)</t>
+        </is>
+      </c>
+      <c r="X23" s="22" t="n"/>
+      <c r="Y23" s="22" t="n"/>
+      <c r="Z23" s="24" t="n"/>
+      <c r="AA23" s="22" t="n"/>
+      <c r="AB23" s="24" t="n"/>
+      <c r="AC23" s="24" t="n"/>
+      <c r="AD23" s="22" t="inlineStr">
+        <is>
+          <t>5Б/Девочки
+каб. технологии (девочки) (№29)</t>
+        </is>
+      </c>
+      <c r="AE23" s="23" t="inlineStr">
+        <is>
+          <t>окно</t>
+        </is>
+      </c>
+      <c r="AF23" s="22" t="inlineStr">
+        <is>
+          <t>8А/Девочки
+каб. технологии (девочки) (№29)</t>
+        </is>
+      </c>
+      <c r="AG23" s="22" t="n"/>
+      <c r="AH23" s="22" t="inlineStr">
         <is>
           <t>7А/Девочки
 каб. технологии (девочки) (№29)</t>
         </is>
       </c>
-      <c r="V23" s="23" t="n"/>
-      <c r="W23" s="22" t="inlineStr">
-        <is>
-          <t>6Б/Девочки
-каб. технологии (девочки) (№29)</t>
-        </is>
-      </c>
-      <c r="X23" s="22" t="n"/>
-      <c r="Y23" s="22" t="n"/>
-      <c r="Z23" s="23" t="n"/>
-      <c r="AA23" s="22" t="n"/>
-      <c r="AB23" s="22" t="n"/>
-      <c r="AC23" s="22" t="n"/>
-      <c r="AD23" s="22" t="inlineStr">
-        <is>
-          <t>5Б/Девочки
-каб. технологии (девочки) (№29)</t>
-        </is>
-      </c>
-      <c r="AE23" s="24" t="inlineStr">
-        <is>
-          <t>окно</t>
-        </is>
-      </c>
-      <c r="AF23" s="22" t="inlineStr">
-        <is>
-          <t>8А/Девочки
-каб. технологии (девочки) (№29)</t>
-        </is>
-      </c>
-      <c r="AG23" s="22" t="n"/>
-      <c r="AH23" s="22" t="n"/>
       <c r="AI23" s="22" t="inlineStr">
         <is>
           <t>6Б/Девочки,6В
@@ -10230,7 +10247,7 @@
 каб. технологии (девочки) (№29)</t>
         </is>
       </c>
-      <c r="AK23" s="24" t="inlineStr">
+      <c r="AK23" s="23" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -10258,7 +10275,7 @@
         <v>10</v>
       </c>
       <c r="AQ23" s="21" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1">
@@ -10279,36 +10296,36 @@
 каб. робототехники (№15)</t>
         </is>
       </c>
-      <c r="D24" s="23" t="n"/>
-      <c r="E24" s="23" t="n"/>
-      <c r="F24" s="23" t="n"/>
-      <c r="G24" s="23" t="n"/>
-      <c r="H24" s="23" t="n"/>
-      <c r="I24" s="23" t="n"/>
-      <c r="J24" s="23" t="n"/>
-      <c r="K24" s="23" t="n"/>
-      <c r="L24" s="23" t="n"/>
-      <c r="M24" s="23" t="n"/>
-      <c r="N24" s="23" t="n"/>
-      <c r="O24" s="23" t="n"/>
-      <c r="P24" s="23" t="n"/>
-      <c r="Q24" s="23" t="n"/>
-      <c r="R24" s="23" t="n"/>
-      <c r="S24" s="23" t="n"/>
-      <c r="T24" s="23" t="n"/>
-      <c r="U24" s="23" t="n"/>
-      <c r="V24" s="23" t="n"/>
-      <c r="W24" s="23" t="n"/>
-      <c r="X24" s="23" t="n"/>
-      <c r="Y24" s="23" t="n"/>
-      <c r="Z24" s="23" t="n"/>
-      <c r="AA24" s="23" t="n"/>
-      <c r="AB24" s="23" t="n"/>
-      <c r="AC24" s="23" t="n"/>
-      <c r="AD24" s="23" t="n"/>
-      <c r="AE24" s="23" t="n"/>
-      <c r="AF24" s="23" t="n"/>
-      <c r="AG24" s="23" t="n"/>
+      <c r="D24" s="24" t="n"/>
+      <c r="E24" s="24" t="n"/>
+      <c r="F24" s="24" t="n"/>
+      <c r="G24" s="24" t="n"/>
+      <c r="H24" s="24" t="n"/>
+      <c r="I24" s="24" t="n"/>
+      <c r="J24" s="24" t="n"/>
+      <c r="K24" s="24" t="n"/>
+      <c r="L24" s="24" t="n"/>
+      <c r="M24" s="24" t="n"/>
+      <c r="N24" s="24" t="n"/>
+      <c r="O24" s="24" t="n"/>
+      <c r="P24" s="24" t="n"/>
+      <c r="Q24" s="24" t="n"/>
+      <c r="R24" s="24" t="n"/>
+      <c r="S24" s="24" t="n"/>
+      <c r="T24" s="24" t="n"/>
+      <c r="U24" s="24" t="n"/>
+      <c r="V24" s="24" t="n"/>
+      <c r="W24" s="24" t="n"/>
+      <c r="X24" s="24" t="n"/>
+      <c r="Y24" s="24" t="n"/>
+      <c r="Z24" s="24" t="n"/>
+      <c r="AA24" s="24" t="n"/>
+      <c r="AB24" s="24" t="n"/>
+      <c r="AC24" s="24" t="n"/>
+      <c r="AD24" s="24" t="n"/>
+      <c r="AE24" s="24" t="n"/>
+      <c r="AF24" s="24" t="n"/>
+      <c r="AG24" s="24" t="n"/>
       <c r="AH24" s="22" t="inlineStr">
         <is>
           <t>6Б,6В
@@ -10321,12 +10338,12 @@
 каб. робототехники (№15)</t>
         </is>
       </c>
-      <c r="AJ24" s="23" t="n"/>
-      <c r="AK24" s="23" t="n"/>
-      <c r="AL24" s="23" t="n"/>
-      <c r="AM24" s="23" t="n"/>
-      <c r="AN24" s="23" t="n"/>
-      <c r="AO24" s="23" t="n"/>
+      <c r="AJ24" s="24" t="n"/>
+      <c r="AK24" s="24" t="n"/>
+      <c r="AL24" s="24" t="n"/>
+      <c r="AM24" s="24" t="n"/>
+      <c r="AN24" s="24" t="n"/>
+      <c r="AO24" s="24" t="n"/>
       <c r="AP24" s="21" t="n">
         <v>4</v>
       </c>
@@ -10358,7 +10375,7 @@
 каб. мультимедийный (№18)</t>
         </is>
       </c>
-      <c r="E25" s="24" t="inlineStr">
+      <c r="E25" s="23" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -10455,7 +10472,7 @@
 каб. мультимедийный (№18)</t>
         </is>
       </c>
-      <c r="AB25" s="24" t="inlineStr">
+      <c r="AB25" s="23" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -10539,7 +10556,7 @@
 малый зал</t>
         </is>
       </c>
-      <c r="E26" s="24" t="inlineStr">
+      <c r="E26" s="23" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -10604,7 +10621,7 @@
 малый зал</t>
         </is>
       </c>
-      <c r="AJ26" s="24" t="inlineStr">
+      <c r="AJ26" s="23" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -10694,7 +10711,7 @@
 нач. класс 2Б (№6)</t>
         </is>
       </c>
-      <c r="S27" s="23" t="n"/>
+      <c r="S27" s="24" t="n"/>
       <c r="T27" s="22" t="inlineStr">
         <is>
           <t>2Б
@@ -10811,12 +10828,12 @@
 каб. биологии (№19)</t>
         </is>
       </c>
-      <c r="M28" s="24" t="inlineStr">
+      <c r="M28" s="23" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
       </c>
-      <c r="N28" s="24" t="inlineStr">
+      <c r="N28" s="23" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -10846,14 +10863,14 @@
 каб. химии (№17)</t>
         </is>
       </c>
-      <c r="T28" s="23" t="n"/>
+      <c r="T28" s="24" t="n"/>
       <c r="U28" s="22" t="inlineStr">
         <is>
           <t>10А
 каб. биологии (№19)</t>
         </is>
       </c>
-      <c r="V28" s="24" t="inlineStr">
+      <c r="V28" s="23" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -10884,12 +10901,12 @@
 каб. биологии (№19)</t>
         </is>
       </c>
-      <c r="AC28" s="24" t="inlineStr">
+      <c r="AC28" s="23" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
       </c>
-      <c r="AD28" s="24" t="inlineStr">
+      <c r="AD28" s="23" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -10914,7 +10931,7 @@
 каб. биологии (№19)</t>
         </is>
       </c>
-      <c r="AJ28" s="24" t="inlineStr">
+      <c r="AJ28" s="23" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -10962,9 +10979,9 @@
       <c r="D29" s="22" t="n"/>
       <c r="E29" s="22" t="n"/>
       <c r="F29" s="22" t="n"/>
-      <c r="G29" s="23" t="n"/>
-      <c r="H29" s="23" t="n"/>
-      <c r="I29" s="23" t="n"/>
+      <c r="G29" s="24" t="n"/>
+      <c r="H29" s="24" t="n"/>
+      <c r="I29" s="24" t="n"/>
       <c r="J29" s="22" t="n"/>
       <c r="K29" s="22" t="inlineStr">
         <is>
@@ -10972,12 +10989,12 @@
 спортзал (№01)</t>
         </is>
       </c>
-      <c r="L29" s="24" t="inlineStr">
+      <c r="L29" s="23" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
       </c>
-      <c r="M29" s="24" t="inlineStr">
+      <c r="M29" s="23" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -10988,9 +11005,9 @@
 малый зал</t>
         </is>
       </c>
-      <c r="O29" s="23" t="n"/>
-      <c r="P29" s="23" t="n"/>
-      <c r="Q29" s="23" t="n"/>
+      <c r="O29" s="24" t="n"/>
+      <c r="P29" s="24" t="n"/>
+      <c r="Q29" s="24" t="n"/>
       <c r="R29" s="22" t="n"/>
       <c r="S29" s="22" t="n"/>
       <c r="T29" s="22" t="n"/>
@@ -11001,9 +11018,9 @@
 малый зал</t>
         </is>
       </c>
-      <c r="W29" s="23" t="n"/>
-      <c r="X29" s="23" t="n"/>
-      <c r="Y29" s="23" t="n"/>
+      <c r="W29" s="24" t="n"/>
+      <c r="X29" s="24" t="n"/>
+      <c r="Y29" s="24" t="n"/>
       <c r="Z29" s="22" t="n"/>
       <c r="AA29" s="22" t="inlineStr">
         <is>
@@ -11011,7 +11028,7 @@
 спортзал (№01)</t>
         </is>
       </c>
-      <c r="AB29" s="24" t="inlineStr">
+      <c r="AB29" s="23" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -11028,9 +11045,9 @@
 малый зал</t>
         </is>
       </c>
-      <c r="AE29" s="23" t="n"/>
-      <c r="AF29" s="23" t="n"/>
-      <c r="AG29" s="23" t="n"/>
+      <c r="AE29" s="24" t="n"/>
+      <c r="AF29" s="24" t="n"/>
+      <c r="AG29" s="24" t="n"/>
       <c r="AH29" s="22" t="inlineStr">
         <is>
           <t>10А
@@ -11041,9 +11058,9 @@
       <c r="AJ29" s="22" t="n"/>
       <c r="AK29" s="22" t="n"/>
       <c r="AL29" s="22" t="n"/>
-      <c r="AM29" s="23" t="n"/>
-      <c r="AN29" s="23" t="n"/>
-      <c r="AO29" s="23" t="n"/>
+      <c r="AM29" s="24" t="n"/>
+      <c r="AN29" s="24" t="n"/>
+      <c r="AO29" s="24" t="n"/>
       <c r="AP29" s="21" t="n">
         <v>9</v>
       </c>
@@ -11067,17 +11084,17 @@
         </is>
       </c>
       <c r="F30" s="22" t="n"/>
-      <c r="G30" s="23" t="n"/>
-      <c r="H30" s="23" t="n"/>
-      <c r="I30" s="23" t="n"/>
+      <c r="G30" s="24" t="n"/>
+      <c r="H30" s="24" t="n"/>
+      <c r="I30" s="24" t="n"/>
       <c r="J30" s="22" t="n"/>
       <c r="K30" s="22" t="n"/>
-      <c r="L30" s="23" t="n"/>
+      <c r="L30" s="24" t="n"/>
       <c r="M30" s="22" t="n"/>
       <c r="N30" s="22" t="n"/>
-      <c r="O30" s="23" t="n"/>
-      <c r="P30" s="23" t="n"/>
-      <c r="Q30" s="23" t="n"/>
+      <c r="O30" s="24" t="n"/>
+      <c r="P30" s="24" t="n"/>
+      <c r="Q30" s="24" t="n"/>
       <c r="R30" s="22" t="n"/>
       <c r="S30" s="22" t="n"/>
       <c r="T30" s="22" t="n"/>
@@ -11088,25 +11105,25 @@
 каб. истории (№14)</t>
         </is>
       </c>
-      <c r="W30" s="23" t="n"/>
-      <c r="X30" s="23" t="n"/>
-      <c r="Y30" s="23" t="n"/>
+      <c r="W30" s="24" t="n"/>
+      <c r="X30" s="24" t="n"/>
+      <c r="Y30" s="24" t="n"/>
       <c r="Z30" s="22" t="n"/>
       <c r="AA30" s="22" t="n"/>
-      <c r="AB30" s="23" t="n"/>
+      <c r="AB30" s="24" t="n"/>
       <c r="AC30" s="22" t="n"/>
       <c r="AD30" s="22" t="inlineStr">
         <is>
           <t>6Б
-каб. истории (№14)</t>
-        </is>
-      </c>
-      <c r="AE30" s="23" t="n"/>
-      <c r="AF30" s="23" t="n"/>
-      <c r="AG30" s="23" t="n"/>
+каб. робототехники (№15)</t>
+        </is>
+      </c>
+      <c r="AE30" s="24" t="n"/>
+      <c r="AF30" s="24" t="n"/>
+      <c r="AG30" s="24" t="n"/>
       <c r="AH30" s="22" t="n"/>
       <c r="AI30" s="22" t="n"/>
-      <c r="AJ30" s="23" t="n"/>
+      <c r="AJ30" s="24" t="n"/>
       <c r="AK30" s="22" t="inlineStr">
         <is>
           <t>7А
@@ -11119,9 +11136,9 @@
 каб. математики (№25)</t>
         </is>
       </c>
-      <c r="AM30" s="23" t="n"/>
-      <c r="AN30" s="23" t="n"/>
-      <c r="AO30" s="23" t="n"/>
+      <c r="AM30" s="24" t="n"/>
+      <c r="AN30" s="24" t="n"/>
+      <c r="AO30" s="24" t="n"/>
       <c r="AP30" s="21" t="n">
         <v>5</v>
       </c>
@@ -11144,7 +11161,7 @@
 спортзал (№01)</t>
         </is>
       </c>
-      <c r="F31" s="24" t="inlineStr">
+      <c r="F31" s="23" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -11171,7 +11188,7 @@
 спортзал (№01)</t>
         </is>
       </c>
-      <c r="N31" s="24" t="inlineStr">
+      <c r="N31" s="23" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -11195,19 +11212,20 @@
 спортзал (№01)</t>
         </is>
       </c>
-      <c r="S31" s="24" t="inlineStr">
+      <c r="S31" s="23" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
       </c>
-      <c r="T31" s="24" t="inlineStr">
+      <c r="T31" s="23" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
       </c>
-      <c r="U31" s="24" t="inlineStr">
-        <is>
-          <t>окно</t>
+      <c r="U31" s="22" t="inlineStr">
+        <is>
+          <t>7А
+спортзал (№01)</t>
         </is>
       </c>
       <c r="V31" s="22" t="inlineStr">
@@ -11216,10 +11234,9 @@
 спортзал (№01)</t>
         </is>
       </c>
-      <c r="W31" s="22" t="inlineStr">
-        <is>
-          <t>7А
-спортзал (№01)</t>
+      <c r="W31" s="23" t="inlineStr">
+        <is>
+          <t>окно</t>
         </is>
       </c>
       <c r="X31" s="22" t="inlineStr">
@@ -11235,22 +11252,22 @@
 спортзал (№01)</t>
         </is>
       </c>
-      <c r="AA31" s="24" t="inlineStr">
+      <c r="AA31" s="23" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
       </c>
-      <c r="AB31" s="24" t="inlineStr">
+      <c r="AB31" s="23" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
       </c>
-      <c r="AC31" s="24" t="inlineStr">
+      <c r="AC31" s="23" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
       </c>
-      <c r="AD31" s="24" t="inlineStr">
+      <c r="AD31" s="23" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -11277,7 +11294,7 @@
 спортзал (№01)</t>
         </is>
       </c>
-      <c r="AL31" s="24" t="inlineStr">
+      <c r="AL31" s="23" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -11315,14 +11332,14 @@
 каб. математики (№25)</t>
         </is>
       </c>
-      <c r="D32" s="23" t="n"/>
+      <c r="D32" s="24" t="n"/>
       <c r="E32" s="22" t="n"/>
       <c r="F32" s="22" t="n"/>
       <c r="G32" s="22" t="n"/>
       <c r="H32" s="22" t="n"/>
       <c r="I32" s="22" t="n"/>
       <c r="J32" s="22" t="n"/>
-      <c r="K32" s="23" t="n"/>
+      <c r="K32" s="24" t="n"/>
       <c r="L32" s="22" t="inlineStr">
         <is>
           <t>6Б,6В
@@ -11433,7 +11450,7 @@
 нач. класс 4Б (№9)</t>
         </is>
       </c>
-      <c r="D33" s="24" t="inlineStr">
+      <c r="D33" s="23" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -11466,7 +11483,7 @@
 нач. класс 4Б (№9)</t>
         </is>
       </c>
-      <c r="M33" s="24" t="inlineStr">
+      <c r="M33" s="23" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -11492,12 +11509,12 @@
 нач. класс 4Б (№9)</t>
         </is>
       </c>
-      <c r="T33" s="24" t="inlineStr">
+      <c r="T33" s="23" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
       </c>
-      <c r="U33" s="24" t="inlineStr">
+      <c r="U33" s="23" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -11529,7 +11546,7 @@
 нач. класс 4Б (№9)</t>
         </is>
       </c>
-      <c r="AC33" s="24" t="inlineStr">
+      <c r="AC33" s="23" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -11629,22 +11646,18 @@
 каб. физики (№16)</t>
         </is>
       </c>
-      <c r="V34" s="24" t="inlineStr">
+      <c r="V34" s="23" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
       </c>
-      <c r="W34" s="24" t="inlineStr">
-        <is>
-          <t>окно</t>
-        </is>
-      </c>
-      <c r="X34" s="22" t="inlineStr">
+      <c r="W34" s="22" t="inlineStr">
         <is>
           <t>7А
 каб. физики (№16)</t>
         </is>
       </c>
+      <c r="X34" s="22" t="n"/>
       <c r="Y34" s="22" t="n"/>
       <c r="Z34" s="22" t="n"/>
       <c r="AA34" s="22" t="n"/>
@@ -11659,43 +11672,39 @@
       <c r="AE34" s="22" t="n"/>
       <c r="AF34" s="22" t="n"/>
       <c r="AG34" s="22" t="n"/>
-      <c r="AH34" s="22" t="inlineStr">
+      <c r="AH34" s="22" t="n"/>
+      <c r="AI34" s="22" t="n"/>
+      <c r="AJ34" s="22" t="inlineStr">
+        <is>
+          <t>9Б
+каб. физики (№16)</t>
+        </is>
+      </c>
+      <c r="AK34" s="22" t="inlineStr">
+        <is>
+          <t>11Б
+каб. физики (№16)</t>
+        </is>
+      </c>
+      <c r="AL34" s="22" t="inlineStr">
+        <is>
+          <t>10А
+каб. физики (№16)</t>
+        </is>
+      </c>
+      <c r="AM34" s="22" t="inlineStr">
         <is>
           <t>7А
 каб. физики (№16)</t>
         </is>
       </c>
-      <c r="AI34" s="24" t="inlineStr">
-        <is>
-          <t>окно</t>
-        </is>
-      </c>
-      <c r="AJ34" s="22" t="inlineStr">
-        <is>
-          <t>9Б
-каб. физики (№16)</t>
-        </is>
-      </c>
-      <c r="AK34" s="22" t="inlineStr">
-        <is>
-          <t>11Б
-каб. физики (№16)</t>
-        </is>
-      </c>
-      <c r="AL34" s="22" t="inlineStr">
-        <is>
-          <t>10А
-каб. физики (№16)</t>
-        </is>
-      </c>
-      <c r="AM34" s="22" t="n"/>
       <c r="AN34" s="22" t="n"/>
       <c r="AO34" s="22" t="n"/>
       <c r="AP34" s="21" t="n">
         <v>13</v>
       </c>
       <c r="AQ34" s="21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35" ht="30" customHeight="1">
@@ -11704,25 +11713,25 @@
           <t>Сапаргалиева Г.С.</t>
         </is>
       </c>
-      <c r="B35" s="23" t="n"/>
-      <c r="C35" s="23" t="n"/>
-      <c r="D35" s="23" t="n"/>
-      <c r="E35" s="23" t="n"/>
-      <c r="F35" s="23" t="n"/>
-      <c r="G35" s="23" t="n"/>
-      <c r="H35" s="23" t="n"/>
-      <c r="I35" s="23" t="n"/>
-      <c r="J35" s="23" t="n"/>
-      <c r="K35" s="23" t="n"/>
-      <c r="L35" s="23" t="n"/>
-      <c r="M35" s="23" t="n"/>
-      <c r="N35" s="23" t="n"/>
-      <c r="O35" s="23" t="n"/>
-      <c r="P35" s="23" t="n"/>
-      <c r="Q35" s="23" t="n"/>
-      <c r="R35" s="23" t="n"/>
-      <c r="S35" s="23" t="n"/>
-      <c r="T35" s="23" t="n"/>
+      <c r="B35" s="24" t="n"/>
+      <c r="C35" s="24" t="n"/>
+      <c r="D35" s="24" t="n"/>
+      <c r="E35" s="24" t="n"/>
+      <c r="F35" s="24" t="n"/>
+      <c r="G35" s="24" t="n"/>
+      <c r="H35" s="24" t="n"/>
+      <c r="I35" s="24" t="n"/>
+      <c r="J35" s="24" t="n"/>
+      <c r="K35" s="24" t="n"/>
+      <c r="L35" s="24" t="n"/>
+      <c r="M35" s="24" t="n"/>
+      <c r="N35" s="24" t="n"/>
+      <c r="O35" s="24" t="n"/>
+      <c r="P35" s="24" t="n"/>
+      <c r="Q35" s="24" t="n"/>
+      <c r="R35" s="24" t="n"/>
+      <c r="S35" s="24" t="n"/>
+      <c r="T35" s="24" t="n"/>
       <c r="U35" s="22" t="inlineStr">
         <is>
           <t>5А
@@ -11748,9 +11757,9 @@
         </is>
       </c>
       <c r="Y35" s="22" t="n"/>
-      <c r="Z35" s="23" t="n"/>
-      <c r="AA35" s="23" t="n"/>
-      <c r="AB35" s="23" t="n"/>
+      <c r="Z35" s="24" t="n"/>
+      <c r="AA35" s="24" t="n"/>
+      <c r="AB35" s="24" t="n"/>
       <c r="AC35" s="22" t="inlineStr">
         <is>
           <t>6А
@@ -11776,14 +11785,14 @@
         </is>
       </c>
       <c r="AG35" s="22" t="n"/>
-      <c r="AH35" s="23" t="n"/>
-      <c r="AI35" s="23" t="n"/>
-      <c r="AJ35" s="23" t="n"/>
-      <c r="AK35" s="23" t="n"/>
-      <c r="AL35" s="23" t="n"/>
-      <c r="AM35" s="23" t="n"/>
-      <c r="AN35" s="23" t="n"/>
-      <c r="AO35" s="23" t="n"/>
+      <c r="AH35" s="24" t="n"/>
+      <c r="AI35" s="24" t="n"/>
+      <c r="AJ35" s="24" t="n"/>
+      <c r="AK35" s="24" t="n"/>
+      <c r="AL35" s="24" t="n"/>
+      <c r="AM35" s="24" t="n"/>
+      <c r="AN35" s="24" t="n"/>
+      <c r="AO35" s="24" t="n"/>
       <c r="AP35" s="21" t="n">
         <v>8</v>
       </c>
@@ -11797,26 +11806,26 @@
           <t>Сидоров В.Б.</t>
         </is>
       </c>
-      <c r="B36" s="23" t="n"/>
-      <c r="C36" s="23" t="n"/>
-      <c r="D36" s="23" t="n"/>
-      <c r="E36" s="23" t="n"/>
-      <c r="F36" s="23" t="n"/>
-      <c r="G36" s="23" t="n"/>
-      <c r="H36" s="23" t="n"/>
-      <c r="I36" s="23" t="n"/>
+      <c r="B36" s="24" t="n"/>
+      <c r="C36" s="24" t="n"/>
+      <c r="D36" s="24" t="n"/>
+      <c r="E36" s="24" t="n"/>
+      <c r="F36" s="24" t="n"/>
+      <c r="G36" s="24" t="n"/>
+      <c r="H36" s="24" t="n"/>
+      <c r="I36" s="24" t="n"/>
       <c r="J36" s="22" t="inlineStr">
         <is>
           <t>7А
 каб. НВП (№28)</t>
         </is>
       </c>
-      <c r="K36" s="24" t="inlineStr">
+      <c r="K36" s="23" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
       </c>
-      <c r="L36" s="24" t="inlineStr">
+      <c r="L36" s="23" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -11846,14 +11855,14 @@
         </is>
       </c>
       <c r="Q36" s="22" t="n"/>
-      <c r="R36" s="23" t="n"/>
-      <c r="S36" s="23" t="n"/>
-      <c r="T36" s="23" t="n"/>
-      <c r="U36" s="23" t="n"/>
-      <c r="V36" s="23" t="n"/>
-      <c r="W36" s="23" t="n"/>
-      <c r="X36" s="23" t="n"/>
-      <c r="Y36" s="23" t="n"/>
+      <c r="R36" s="24" t="n"/>
+      <c r="S36" s="24" t="n"/>
+      <c r="T36" s="24" t="n"/>
+      <c r="U36" s="24" t="n"/>
+      <c r="V36" s="24" t="n"/>
+      <c r="W36" s="24" t="n"/>
+      <c r="X36" s="24" t="n"/>
+      <c r="Y36" s="24" t="n"/>
       <c r="Z36" s="22" t="n"/>
       <c r="AA36" s="22" t="n"/>
       <c r="AB36" s="22" t="inlineStr">
@@ -11887,14 +11896,14 @@
         </is>
       </c>
       <c r="AG36" s="22" t="n"/>
-      <c r="AH36" s="23" t="n"/>
-      <c r="AI36" s="23" t="n"/>
-      <c r="AJ36" s="23" t="n"/>
-      <c r="AK36" s="23" t="n"/>
-      <c r="AL36" s="23" t="n"/>
-      <c r="AM36" s="23" t="n"/>
-      <c r="AN36" s="23" t="n"/>
-      <c r="AO36" s="23" t="n"/>
+      <c r="AH36" s="24" t="n"/>
+      <c r="AI36" s="24" t="n"/>
+      <c r="AJ36" s="24" t="n"/>
+      <c r="AK36" s="24" t="n"/>
+      <c r="AL36" s="24" t="n"/>
+      <c r="AM36" s="24" t="n"/>
+      <c r="AN36" s="24" t="n"/>
+      <c r="AO36" s="24" t="n"/>
       <c r="AP36" s="21" t="n">
         <v>10</v>
       </c>
@@ -11923,7 +11932,7 @@
       <c r="D37" s="22" t="inlineStr">
         <is>
           <t>6Б,6В
-каб. технологии (мальчики) (№39)</t>
+каб. математики (№25)</t>
         </is>
       </c>
       <c r="E37" s="22" t="inlineStr">
@@ -11963,7 +11972,7 @@
       <c r="N37" s="22" t="inlineStr">
         <is>
           <t>6Б,6В
-каб. технологии (мальчики) (№39)</t>
+каб. английского языка (№27)</t>
         </is>
       </c>
       <c r="O37" s="22" t="n"/>
@@ -11984,7 +11993,7 @@
       <c r="T37" s="22" t="inlineStr">
         <is>
           <t>6Б,6В
-каб. технологии (мальчики) (№39)</t>
+каб. биологии (№19)</t>
         </is>
       </c>
       <c r="U37" s="22" t="inlineStr">
@@ -12018,7 +12027,7 @@
       <c r="AC37" s="22" t="inlineStr">
         <is>
           <t>6Б,6В
-каб. технологии (мальчики) (№39)</t>
+каб. истории (№14)</t>
         </is>
       </c>
       <c r="AD37" s="22" t="inlineStr">
@@ -12042,7 +12051,7 @@
 нач. класс 3А (№7)</t>
         </is>
       </c>
-      <c r="AJ37" s="24" t="inlineStr">
+      <c r="AJ37" s="23" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -12050,7 +12059,7 @@
       <c r="AK37" s="22" t="inlineStr">
         <is>
           <t>6Б,6В
-каб. технологии (мальчики) (№39)</t>
+каб. английского языка (№27)</t>
         </is>
       </c>
       <c r="AL37" s="22" t="n"/>
@@ -12124,12 +12133,12 @@
 спортзал (№01)</t>
         </is>
       </c>
-      <c r="U38" s="24" t="inlineStr">
+      <c r="U38" s="23" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
       </c>
-      <c r="V38" s="24" t="inlineStr">
+      <c r="V38" s="23" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -12168,7 +12177,7 @@
 спортзал (№01)</t>
         </is>
       </c>
-      <c r="AK38" s="24" t="inlineStr">
+      <c r="AK38" s="23" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -12606,7 +12615,7 @@
       <c r="G4" s="22" t="inlineStr">
         <is>
           <t>8Ә
-Дюсембаева</t>
+Власова</t>
         </is>
       </c>
       <c r="J4" s="22" t="inlineStr">
@@ -12672,13 +12681,13 @@
       <c r="Z4" s="22" t="inlineStr">
         <is>
           <t>8Ә
-Дюсембаева</t>
+Власова</t>
         </is>
       </c>
       <c r="AA4" s="22" t="inlineStr">
         <is>
           <t>7А
-Дюсембаева</t>
+Власова</t>
         </is>
       </c>
       <c r="AB4" s="22" t="inlineStr">
@@ -12757,7 +12766,7 @@
       <c r="B5" s="22" t="inlineStr">
         <is>
           <t>8А
-Дюсембаева</t>
+Власова</t>
         </is>
       </c>
       <c r="C5" s="22" t="inlineStr">
@@ -12814,6 +12823,12 @@
 Акауова</t>
         </is>
       </c>
+      <c r="N5" s="22" t="inlineStr">
+        <is>
+          <t>6Б,6В
+Темерканова</t>
+        </is>
+      </c>
       <c r="R5" s="22" t="inlineStr">
         <is>
           <t>4А
@@ -12829,7 +12844,7 @@
       <c r="T5" s="22" t="inlineStr">
         <is>
           <t>8А
-Дюсембаева</t>
+Власова</t>
         </is>
       </c>
       <c r="U5" s="22" t="inlineStr">
@@ -12841,13 +12856,13 @@
       <c r="V5" s="22" t="inlineStr">
         <is>
           <t>7А
-Дюсембаева</t>
+Власова</t>
         </is>
       </c>
       <c r="W5" s="22" t="inlineStr">
         <is>
           <t>8Ә
-Дюсембаева</t>
+Власова</t>
         </is>
       </c>
       <c r="X5" s="22" t="inlineStr">
@@ -12877,7 +12892,7 @@
       <c r="AD5" s="22" t="inlineStr">
         <is>
           <t>8А
-Дюсембаева</t>
+Власова</t>
         </is>
       </c>
       <c r="AE5" s="22" t="inlineStr">
@@ -12895,13 +12910,13 @@
       <c r="AH5" s="22" t="inlineStr">
         <is>
           <t>8Ә
-Дюсембаева</t>
+Власова</t>
         </is>
       </c>
       <c r="AI5" s="22" t="inlineStr">
         <is>
           <t>7А
-Дюсембаева</t>
+Власова</t>
         </is>
       </c>
       <c r="AJ5" s="22" t="inlineStr">
@@ -12910,6 +12925,12 @@
 Акауова</t>
         </is>
       </c>
+      <c r="AK5" s="22" t="inlineStr">
+        <is>
+          <t>6Б,6В
+Темерканова</t>
+        </is>
+      </c>
       <c r="AM5" s="22" t="inlineStr">
         <is>
           <t>6Б
@@ -12989,6 +13010,12 @@
 Бабич</t>
         </is>
       </c>
+      <c r="T6" s="22" t="inlineStr">
+        <is>
+          <t>6Б,6В
+Темерканова</t>
+        </is>
+      </c>
       <c r="U6" s="22" t="inlineStr">
         <is>
           <t>10А
@@ -13363,2470 +13390,2470 @@
 Досаева</t>
         </is>
       </c>
+      <c r="AC8" s="22" t="inlineStr">
+        <is>
+          <t>6Б,6В
+Темерканова</t>
+        </is>
+      </c>
       <c r="AD8" s="22" t="inlineStr">
+        <is>
+          <t>8Ә
+Досаева</t>
+        </is>
+      </c>
+      <c r="AE8" s="22" t="inlineStr">
+        <is>
+          <t>8Ә
+Ізбасты</t>
+        </is>
+      </c>
+      <c r="AH8" s="22" t="inlineStr">
+        <is>
+          <t>11А
+Досаева</t>
+        </is>
+      </c>
+      <c r="AK8" s="22" t="inlineStr">
+        <is>
+          <t>8Ә
+Досаева</t>
+        </is>
+      </c>
+      <c r="AL8" s="22" t="inlineStr">
+        <is>
+          <t>11Б
+Досаева</t>
+        </is>
+      </c>
+      <c r="AM8" s="22" t="inlineStr">
+        <is>
+          <t>9Б
+Досаева</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="26" t="inlineStr">
+        <is>
+          <t>Кабинет казахского языка (№24)</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>6А
+Асаева</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>8Б
+Асаева</t>
+        </is>
+      </c>
+      <c r="D9" s="22" t="inlineStr">
+        <is>
+          <t>8Ә
+Балташева</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t>8Ә
+Балташева</t>
+        </is>
+      </c>
+      <c r="G9" s="22" t="inlineStr">
+        <is>
+          <t>11А
+Балташева</t>
+        </is>
+      </c>
+      <c r="J9" s="22" t="inlineStr">
+        <is>
+          <t>11Б
+Асаева</t>
+        </is>
+      </c>
+      <c r="K9" s="22" t="inlineStr">
+        <is>
+          <t>6А
+Асаева</t>
+        </is>
+      </c>
+      <c r="L9" s="22" t="inlineStr">
+        <is>
+          <t>8Б
+Асаева</t>
+        </is>
+      </c>
+      <c r="N9" s="22" t="inlineStr">
+        <is>
+          <t>9Б
+Асаева</t>
+        </is>
+      </c>
+      <c r="R9" s="22" t="inlineStr">
+        <is>
+          <t>6А
+Асаева</t>
+        </is>
+      </c>
+      <c r="S9" s="22" t="inlineStr">
+        <is>
+          <t>11Б
+Асаева</t>
+        </is>
+      </c>
+      <c r="T9" s="22" t="inlineStr">
+        <is>
+          <t>8Б
+Асаева</t>
+        </is>
+      </c>
+      <c r="U9" s="22" t="inlineStr">
+        <is>
+          <t>5Б
+Алекпарова</t>
+        </is>
+      </c>
+      <c r="V9" s="22" t="inlineStr">
+        <is>
+          <t>9Б
+Асаева</t>
+        </is>
+      </c>
+      <c r="W9" s="22" t="inlineStr">
+        <is>
+          <t>9Б
+Алекпарова</t>
+        </is>
+      </c>
+      <c r="Z9" s="22" t="inlineStr">
+        <is>
+          <t>6А
+Асаева</t>
+        </is>
+      </c>
+      <c r="AB9" s="22" t="inlineStr">
+        <is>
+          <t>8Б
+Асаева</t>
+        </is>
+      </c>
+      <c r="AC9" s="22" t="inlineStr">
+        <is>
+          <t>7А
+Алекпарова</t>
+        </is>
+      </c>
+      <c r="AD9" s="22" t="inlineStr">
+        <is>
+          <t>9Б
+Асаева</t>
+        </is>
+      </c>
+      <c r="AE9" s="22" t="inlineStr">
+        <is>
+          <t>11Б
+Асаева</t>
+        </is>
+      </c>
+      <c r="AH9" s="22" t="inlineStr">
+        <is>
+          <t>8Б
+Алекпарова</t>
+        </is>
+      </c>
+      <c r="AI9" s="22" t="inlineStr">
+        <is>
+          <t>6А
+Асаева</t>
+        </is>
+      </c>
+      <c r="AJ9" s="22" t="inlineStr">
+        <is>
+          <t>8А
+Алекпарова</t>
+        </is>
+      </c>
+      <c r="AK9" s="22" t="inlineStr">
+        <is>
+          <t>9Б
+Асаева</t>
+        </is>
+      </c>
+      <c r="AL9" s="22" t="inlineStr">
+        <is>
+          <t>6Б
+Алекпарова</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="26" t="inlineStr">
+        <is>
+          <t>Кабинет казахского языка и литературы (№23)</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>2А
+Балгабаева</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>8Ә
+Балгабаева</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="inlineStr">
+        <is>
+          <t>7А
+Балгабаева</t>
+        </is>
+      </c>
+      <c r="E10" s="22" t="inlineStr">
+        <is>
+          <t>6А
+Балгабаева</t>
+        </is>
+      </c>
+      <c r="F10" s="22" t="inlineStr">
+        <is>
+          <t>6Б
+Балгабаева</t>
+        </is>
+      </c>
+      <c r="J10" s="22" t="inlineStr">
+        <is>
+          <t>8Ә
+Балгабаева</t>
+        </is>
+      </c>
+      <c r="K10" s="22" t="inlineStr">
+        <is>
+          <t>6Б,6В
+Балгабаева</t>
+        </is>
+      </c>
+      <c r="L10" s="22" t="inlineStr">
+        <is>
+          <t>6А
+Балгабаева</t>
+        </is>
+      </c>
+      <c r="M10" s="22" t="inlineStr">
+        <is>
+          <t>4А
+Балгабаева</t>
+        </is>
+      </c>
+      <c r="N10" s="22" t="inlineStr">
+        <is>
+          <t>5А
+Балгабаева</t>
+        </is>
+      </c>
+      <c r="O10" s="22" t="inlineStr">
+        <is>
+          <t>5Б
+Балгабаева</t>
+        </is>
+      </c>
+      <c r="R10" s="22" t="inlineStr">
+        <is>
+          <t>8Б
+Алекпарова</t>
+        </is>
+      </c>
+      <c r="S10" s="22" t="inlineStr">
+        <is>
+          <t>5Б
+Балгабаева</t>
+        </is>
+      </c>
+      <c r="T10" s="22" t="inlineStr">
+        <is>
+          <t>5А
+Балгабаева</t>
+        </is>
+      </c>
+      <c r="U10" s="22" t="inlineStr">
+        <is>
+          <t>6Б
+Балгабаева</t>
+        </is>
+      </c>
+      <c r="W10" s="22" t="inlineStr">
+        <is>
+          <t>11А
+Балгабаева</t>
+        </is>
+      </c>
+      <c r="Z10" s="22" t="inlineStr">
+        <is>
+          <t>2А
+Балгабаева</t>
+        </is>
+      </c>
+      <c r="AA10" s="22" t="inlineStr">
+        <is>
+          <t>6Б,6В
+Балгабаева</t>
+        </is>
+      </c>
+      <c r="AB10" s="22" t="inlineStr">
+        <is>
+          <t>8Ә
+Балгабаева</t>
+        </is>
+      </c>
+      <c r="AC10" s="22" t="inlineStr">
+        <is>
+          <t>5А
+Балгабаева</t>
+        </is>
+      </c>
+      <c r="AD10" s="22" t="inlineStr">
+        <is>
+          <t>6А
+Балгабаева</t>
+        </is>
+      </c>
+      <c r="AE10" s="22" t="inlineStr">
+        <is>
+          <t>6Б
+Алекпарова</t>
+        </is>
+      </c>
+      <c r="AF10" s="22" t="inlineStr">
+        <is>
+          <t>9Б
+Алекпарова</t>
+        </is>
+      </c>
+      <c r="AH10" s="22" t="inlineStr">
+        <is>
+          <t>4А
+Балгабаева</t>
+        </is>
+      </c>
+      <c r="AI10" s="22" t="inlineStr">
+        <is>
+          <t>8Ә
+Алекпарова</t>
+        </is>
+      </c>
+      <c r="AK10" s="22" t="inlineStr">
+        <is>
+          <t>11А
+Балгабаева</t>
+        </is>
+      </c>
+      <c r="AL10" s="22" t="inlineStr">
+        <is>
+          <t>7А
+Балгабаева</t>
+        </is>
+      </c>
+      <c r="AM10" s="22" t="inlineStr">
+        <is>
+          <t>5Б
+Балгабаева</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="26" t="inlineStr">
+        <is>
+          <t>Кабинет математики (№25)</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>11Б
+Пащенко</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>6Б,6В
+Пащенко</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="inlineStr">
+        <is>
+          <t>6Б,6В
+Темерканова</t>
+        </is>
+      </c>
+      <c r="E11" s="22" t="inlineStr">
         <is>
           <t>6Б
 Мельникова</t>
         </is>
       </c>
-      <c r="AE8" s="22" t="inlineStr">
+      <c r="F11" s="22" t="inlineStr">
+        <is>
+          <t>2А
+Жекеева</t>
+        </is>
+      </c>
+      <c r="K11" s="22" t="inlineStr">
+        <is>
+          <t>2А
+Жекеева</t>
+        </is>
+      </c>
+      <c r="L11" s="22" t="inlineStr">
+        <is>
+          <t>6Б,6В
+Пащенко</t>
+        </is>
+      </c>
+      <c r="M11" s="22" t="inlineStr">
+        <is>
+          <t>11Б
+Пащенко</t>
+        </is>
+      </c>
+      <c r="N11" s="22" t="inlineStr">
+        <is>
+          <t>7А
+Пащенко</t>
+        </is>
+      </c>
+      <c r="R11" s="22" t="inlineStr">
+        <is>
+          <t>11Б
+Пащенко</t>
+        </is>
+      </c>
+      <c r="S11" s="22" t="inlineStr">
+        <is>
+          <t>6Б,6В
+Пащенко</t>
+        </is>
+      </c>
+      <c r="T11" s="22" t="inlineStr">
+        <is>
+          <t>7А
+Пащенко</t>
+        </is>
+      </c>
+      <c r="U11" s="22" t="inlineStr">
+        <is>
+          <t>5А
+Сапаргалиева</t>
+        </is>
+      </c>
+      <c r="V11" s="22" t="inlineStr">
+        <is>
+          <t>11А
+Сапаргалиева</t>
+        </is>
+      </c>
+      <c r="W11" s="22" t="inlineStr">
+        <is>
+          <t>6А
+Сапаргалиева</t>
+        </is>
+      </c>
+      <c r="X11" s="22" t="inlineStr">
         <is>
           <t>8Ә
-Досаева</t>
-        </is>
-      </c>
-      <c r="AH8" s="22" t="inlineStr">
+Сапаргалиева</t>
+        </is>
+      </c>
+      <c r="AA11" s="22" t="inlineStr">
+        <is>
+          <t>11Б
+Пащенко</t>
+        </is>
+      </c>
+      <c r="AB11" s="22" t="inlineStr">
+        <is>
+          <t>6Б,6В
+Пащенко</t>
+        </is>
+      </c>
+      <c r="AC11" s="22" t="inlineStr">
+        <is>
+          <t>6А
+Сапаргалиева</t>
+        </is>
+      </c>
+      <c r="AD11" s="22" t="inlineStr">
+        <is>
+          <t>5А
+Сапаргалиева</t>
+        </is>
+      </c>
+      <c r="AE11" s="22" t="inlineStr">
         <is>
           <t>11А
-Досаева</t>
-        </is>
-      </c>
-      <c r="AK8" s="22" t="inlineStr">
+Сапаргалиева</t>
+        </is>
+      </c>
+      <c r="AF11" s="22" t="inlineStr">
         <is>
           <t>8Ә
-Досаева</t>
-        </is>
-      </c>
-      <c r="AL8" s="22" t="inlineStr">
+Сапаргалиева</t>
+        </is>
+      </c>
+      <c r="AH11" s="22" t="inlineStr">
         <is>
           <t>11Б
-Досаева</t>
-        </is>
-      </c>
-      <c r="AM8" s="22" t="inlineStr">
+Пащенко</t>
+        </is>
+      </c>
+      <c r="AI11" s="22" t="inlineStr">
+        <is>
+          <t>11Б
+Пащенко</t>
+        </is>
+      </c>
+      <c r="AJ11" s="22" t="inlineStr">
+        <is>
+          <t>6Б,6В
+Пащенко</t>
+        </is>
+      </c>
+      <c r="AK11" s="22" t="inlineStr">
+        <is>
+          <t>7А
+Мельникова</t>
+        </is>
+      </c>
+      <c r="AL11" s="22" t="inlineStr">
+        <is>
+          <t>8Б
+Мельникова</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="26" t="inlineStr">
+        <is>
+          <t>Кабинет мультимедийный (№18)</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>5Б
+Ильясова</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>11А
+Ильясова</t>
+        </is>
+      </c>
+      <c r="D12" s="22" t="inlineStr">
+        <is>
+          <t>5А
+Ильясова</t>
+        </is>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
+        <is>
+          <t>5Б
+Ажикенова</t>
+        </is>
+      </c>
+      <c r="F12" s="22" t="inlineStr">
+        <is>
+          <t>6Б
+Ильясова</t>
+        </is>
+      </c>
+      <c r="J12" s="22" t="inlineStr">
+        <is>
+          <t>5Б
+Ильясова</t>
+        </is>
+      </c>
+      <c r="K12" s="22" t="inlineStr">
+        <is>
+          <t>6Б
+Ильясова</t>
+        </is>
+      </c>
+      <c r="L12" s="22" t="inlineStr">
+        <is>
+          <t>10А
+Ильясова</t>
+        </is>
+      </c>
+      <c r="M12" s="22" t="inlineStr">
+        <is>
+          <t>5А
+Ильясова</t>
+        </is>
+      </c>
+      <c r="N12" s="22" t="inlineStr">
         <is>
           <t>9Б
-Досаева</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="26" t="inlineStr">
-        <is>
-          <t>Кабинет казахского языка (№24)</t>
-        </is>
-      </c>
-      <c r="B9" s="22" t="inlineStr">
+Ильясова</t>
+        </is>
+      </c>
+      <c r="O12" s="22" t="inlineStr">
+        <is>
+          <t>11А
+Ильясова</t>
+        </is>
+      </c>
+      <c r="R12" s="22" t="inlineStr">
+        <is>
+          <t>5А
+Ильясова</t>
+        </is>
+      </c>
+      <c r="S12" s="22" t="inlineStr">
+        <is>
+          <t>10А
+Ильясова</t>
+        </is>
+      </c>
+      <c r="T12" s="22" t="inlineStr">
+        <is>
+          <t>5Б
+Ильясова</t>
+        </is>
+      </c>
+      <c r="U12" s="22" t="inlineStr">
+        <is>
+          <t>6Б
+Ильясова</t>
+        </is>
+      </c>
+      <c r="V12" s="22" t="inlineStr">
+        <is>
+          <t>9Б
+Ильясова</t>
+        </is>
+      </c>
+      <c r="Z12" s="22" t="inlineStr">
+        <is>
+          <t>10А
+Ильясова</t>
+        </is>
+      </c>
+      <c r="AA12" s="22" t="inlineStr">
+        <is>
+          <t>6Б
+Ильясова</t>
+        </is>
+      </c>
+      <c r="AC12" s="22" t="inlineStr">
+        <is>
+          <t>5Б
+Ильясова</t>
+        </is>
+      </c>
+      <c r="AD12" s="22" t="inlineStr">
+        <is>
+          <t>9Б
+Ильясова</t>
+        </is>
+      </c>
+      <c r="AE12" s="22" t="inlineStr">
+        <is>
+          <t>5А
+Ильясова</t>
+        </is>
+      </c>
+      <c r="AH12" s="22" t="inlineStr">
+        <is>
+          <t>5А
+Ильясова</t>
+        </is>
+      </c>
+      <c r="AI12" s="22" t="inlineStr">
+        <is>
+          <t>10А
+Ильясова</t>
+        </is>
+      </c>
+      <c r="AJ12" s="22" t="inlineStr">
+        <is>
+          <t>11А
+Ильясова</t>
+        </is>
+      </c>
+      <c r="AK12" s="22" t="inlineStr">
+        <is>
+          <t>9Б
+Ильясова</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="26" t="inlineStr">
+        <is>
+          <t>Кабинет робототехники (№15)</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>6Б,6В
+Иващенко</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>5Б
+Иващенко</t>
+        </is>
+      </c>
+      <c r="E13" s="22" t="inlineStr">
+        <is>
+          <t>10А
+Бучкова</t>
+        </is>
+      </c>
+      <c r="G13" s="22" t="inlineStr">
+        <is>
+          <t>8А
+Бучкова</t>
+        </is>
+      </c>
+      <c r="J13" s="22" t="inlineStr">
+        <is>
+          <t>11А
+Ізбасты</t>
+        </is>
+      </c>
+      <c r="K13" s="22" t="inlineStr">
+        <is>
+          <t>8Ә
+Ізбасты</t>
+        </is>
+      </c>
+      <c r="L13" s="22" t="inlineStr">
+        <is>
+          <t>5А
+Ізбасты</t>
+        </is>
+      </c>
+      <c r="M13" s="22" t="inlineStr">
         <is>
           <t>6А
-Асаева</t>
-        </is>
-      </c>
-      <c r="C9" s="22" t="inlineStr">
+Ізбасты</t>
+        </is>
+      </c>
+      <c r="N13" s="22" t="inlineStr">
+        <is>
+          <t>5Б
+Бучкова</t>
+        </is>
+      </c>
+      <c r="O13" s="22" t="inlineStr">
+        <is>
+          <t>10А
+Бучкова</t>
+        </is>
+      </c>
+      <c r="R13" s="22" t="inlineStr">
+        <is>
+          <t>11А
+Ізбасты</t>
+        </is>
+      </c>
+      <c r="S13" s="22" t="inlineStr">
+        <is>
+          <t>5А
+Ізбасты</t>
+        </is>
+      </c>
+      <c r="T13" s="22" t="inlineStr">
+        <is>
+          <t>6А
+Ізбасты</t>
+        </is>
+      </c>
+      <c r="U13" s="22" t="inlineStr">
+        <is>
+          <t>8Ә
+Ізбасты</t>
+        </is>
+      </c>
+      <c r="V13" s="22" t="inlineStr">
+        <is>
+          <t>5Б
+Бучкова</t>
+        </is>
+      </c>
+      <c r="W13" s="22" t="inlineStr">
+        <is>
+          <t>8А
+Бучкова</t>
+        </is>
+      </c>
+      <c r="Z13" s="22" t="inlineStr">
+        <is>
+          <t>5Б
+Алекпарова</t>
+        </is>
+      </c>
+      <c r="AA13" s="22" t="inlineStr">
+        <is>
+          <t>8Ә
+Алекпарова</t>
+        </is>
+      </c>
+      <c r="AB13" s="22" t="inlineStr">
+        <is>
+          <t>5Б
+Ажикенова</t>
+        </is>
+      </c>
+      <c r="AC13" s="22" t="inlineStr">
+        <is>
+          <t>11А
+Ізбасты</t>
+        </is>
+      </c>
+      <c r="AD13" s="22" t="inlineStr">
+        <is>
+          <t>6Б
+Мельникова</t>
+        </is>
+      </c>
+      <c r="AE13" s="22" t="inlineStr">
+        <is>
+          <t>10А
+Бучкова</t>
+        </is>
+      </c>
+      <c r="AH13" s="22" t="inlineStr">
+        <is>
+          <t>6Б,6В
+Иващенко</t>
+        </is>
+      </c>
+      <c r="AI13" s="22" t="inlineStr">
+        <is>
+          <t>5Б
+Иващенко</t>
+        </is>
+      </c>
+      <c r="AK13" s="22" t="inlineStr">
+        <is>
+          <t>5Б
+Бучкова</t>
+        </is>
+      </c>
+      <c r="AL13" s="22" t="inlineStr">
+        <is>
+          <t>8А
+Бучкова</t>
+        </is>
+      </c>
+      <c r="AM13" s="22" t="inlineStr">
+        <is>
+          <t>10А
+Бучкова</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="26" t="inlineStr">
+        <is>
+          <t>Кабинет русского языка (№20)</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>9Б
+Дмитриев</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>11Б
+Дмитриев</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>8А
+Дмитриев</t>
+        </is>
+      </c>
+      <c r="E14" s="22" t="inlineStr">
         <is>
           <t>8Б
-Асаева</t>
-        </is>
-      </c>
-      <c r="D9" s="22" t="inlineStr">
+Дмитриев</t>
+        </is>
+      </c>
+      <c r="F14" s="22" t="inlineStr">
+        <is>
+          <t>10А
+Дмитриев</t>
+        </is>
+      </c>
+      <c r="L14" s="22" t="inlineStr">
+        <is>
+          <t>7А
+Дмитриев</t>
+        </is>
+      </c>
+      <c r="M14" s="22" t="inlineStr">
+        <is>
+          <t>9Б
+Дмитриев</t>
+        </is>
+      </c>
+      <c r="N14" s="22" t="inlineStr">
+        <is>
+          <t>8Б
+Дмитриев</t>
+        </is>
+      </c>
+      <c r="P14" s="22" t="inlineStr">
+        <is>
+          <t>8А
+Дмитриев</t>
+        </is>
+      </c>
+      <c r="R14" s="22" t="inlineStr">
+        <is>
+          <t>8А
+Дмитриев</t>
+        </is>
+      </c>
+      <c r="S14" s="22" t="inlineStr">
+        <is>
+          <t>7А
+Дмитриев</t>
+        </is>
+      </c>
+      <c r="T14" s="22" t="inlineStr">
+        <is>
+          <t>9Б
+Дмитриев</t>
+        </is>
+      </c>
+      <c r="U14" s="22" t="inlineStr">
+        <is>
+          <t>11Б
+Дмитриев</t>
+        </is>
+      </c>
+      <c r="V14" s="22" t="inlineStr">
+        <is>
+          <t>10А
+Дмитриев</t>
+        </is>
+      </c>
+      <c r="W14" s="22" t="inlineStr">
+        <is>
+          <t>8Б
+Дмитриев</t>
+        </is>
+      </c>
+      <c r="Z14" s="22" t="inlineStr">
+        <is>
+          <t>8Б
+Дмитриев</t>
+        </is>
+      </c>
+      <c r="AA14" s="22" t="inlineStr">
+        <is>
+          <t>9Б
+Дмитриев</t>
+        </is>
+      </c>
+      <c r="AB14" s="22" t="inlineStr">
+        <is>
+          <t>8А
+Дмитриев</t>
+        </is>
+      </c>
+      <c r="AC14" s="22" t="inlineStr">
+        <is>
+          <t>11Б
+Дмитриев</t>
+        </is>
+      </c>
+      <c r="AD14" s="22" t="inlineStr">
+        <is>
+          <t>7А
+Дмитриев</t>
+        </is>
+      </c>
+      <c r="AH14" s="22" t="inlineStr">
+        <is>
+          <t>8А
+Дмитриев</t>
+        </is>
+      </c>
+      <c r="AI14" s="22" t="inlineStr">
+        <is>
+          <t>9Б
+Дмитриев</t>
+        </is>
+      </c>
+      <c r="AJ14" s="22" t="inlineStr">
+        <is>
+          <t>8Б
+Дмитриев</t>
+        </is>
+      </c>
+      <c r="AK14" s="22" t="inlineStr">
+        <is>
+          <t>10А
+Дмитриев</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="26" t="inlineStr">
+        <is>
+          <t>Кабинет технологии (девочки) (№29)</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>2А
+Жекеева</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="inlineStr">
+        <is>
+          <t>9Б
+Алекпарова</t>
+        </is>
+      </c>
+      <c r="E15" s="22" t="inlineStr">
+        <is>
+          <t>8А
+Алекпарова</t>
+        </is>
+      </c>
+      <c r="F15" s="22" t="inlineStr">
+        <is>
+          <t>7А
+Алекпарова</t>
+        </is>
+      </c>
+      <c r="G15" s="22" t="inlineStr">
+        <is>
+          <t>6Б
+Алекпарова</t>
+        </is>
+      </c>
+      <c r="J15" s="22" t="inlineStr">
+        <is>
+          <t>8Б
+Алекпарова</t>
+        </is>
+      </c>
+      <c r="K15" s="22" t="inlineStr">
+        <is>
+          <t>8А
+Алекпарова</t>
+        </is>
+      </c>
+      <c r="L15" s="22" t="inlineStr">
+        <is>
+          <t>5Б
+Алекпарова</t>
+        </is>
+      </c>
+      <c r="N15" s="22" t="inlineStr">
         <is>
           <t>8Ә
-Балташева</t>
-        </is>
-      </c>
-      <c r="E9" s="22" t="inlineStr">
+Алекпарова</t>
+        </is>
+      </c>
+      <c r="O15" s="22" t="inlineStr">
+        <is>
+          <t>7А
+Алекпарова</t>
+        </is>
+      </c>
+      <c r="S15" s="22" t="inlineStr">
+        <is>
+          <t>2Б
+Жукова</t>
+        </is>
+      </c>
+      <c r="T15" s="22" t="inlineStr">
+        <is>
+          <t>2А
+Жекеева</t>
+        </is>
+      </c>
+      <c r="V15" s="22" t="inlineStr">
+        <is>
+          <t>4Б
+Радионова</t>
+        </is>
+      </c>
+      <c r="W15" s="22" t="inlineStr">
+        <is>
+          <t>6Б
+Жукова</t>
+        </is>
+      </c>
+      <c r="AA15" s="22" t="inlineStr">
+        <is>
+          <t>2А
+Жекеева</t>
+        </is>
+      </c>
+      <c r="AB15" s="22" t="inlineStr">
+        <is>
+          <t>2А,4А
+Актаева</t>
+        </is>
+      </c>
+      <c r="AC15" s="22" t="inlineStr">
+        <is>
+          <t>2А
+Жекеева</t>
+        </is>
+      </c>
+      <c r="AD15" s="22" t="inlineStr">
+        <is>
+          <t>5Б
+Жукова</t>
+        </is>
+      </c>
+      <c r="AF15" s="22" t="inlineStr">
+        <is>
+          <t>8А
+Жукова</t>
+        </is>
+      </c>
+      <c r="AH15" s="22" t="inlineStr">
+        <is>
+          <t>7А
+Жукова</t>
+        </is>
+      </c>
+      <c r="AI15" s="22" t="inlineStr">
+        <is>
+          <t>6Б,6В
+Жукова</t>
+        </is>
+      </c>
+      <c r="AJ15" s="22" t="inlineStr">
+        <is>
+          <t>2Б
+Жукова</t>
+        </is>
+      </c>
+      <c r="AK15" s="22" t="inlineStr">
+        <is>
+          <t>1Б
+Ажикенова</t>
+        </is>
+      </c>
+      <c r="AL15" s="22" t="inlineStr">
+        <is>
+          <t>5Б
+Жукова</t>
+        </is>
+      </c>
+      <c r="AM15" s="22" t="inlineStr">
+        <is>
+          <t>8Б
+Жукова</t>
+        </is>
+      </c>
+      <c r="AN15" s="22" t="inlineStr">
+        <is>
+          <t>9Б
+Жукова</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="26" t="inlineStr">
+        <is>
+          <t>Кабинет технологии (мальчики) (№39)</t>
+        </is>
+      </c>
+      <c r="M16" s="22" t="inlineStr">
+        <is>
+          <t>3А
+Темерканова</t>
+        </is>
+      </c>
+      <c r="U16" s="22" t="inlineStr">
+        <is>
+          <t>1А
+Жантимиров</t>
+        </is>
+      </c>
+      <c r="V16" s="22" t="inlineStr">
+        <is>
+          <t>5А,6А,8Ә
+Жантимиров</t>
+        </is>
+      </c>
+      <c r="W16" s="22" t="inlineStr">
+        <is>
+          <t>6Б
+Жантимиров</t>
+        </is>
+      </c>
+      <c r="AA16" s="22" t="inlineStr">
+        <is>
+          <t>1А
+Жантимиров</t>
+        </is>
+      </c>
+      <c r="AD16" s="22" t="inlineStr">
+        <is>
+          <t>5Б
+Жантимиров</t>
+        </is>
+      </c>
+      <c r="AF16" s="22" t="inlineStr">
+        <is>
+          <t>8А
+Жантимиров</t>
+        </is>
+      </c>
+      <c r="AH16" s="22" t="inlineStr">
+        <is>
+          <t>7А
+Жантимиров</t>
+        </is>
+      </c>
+      <c r="AI16" s="22" t="inlineStr">
+        <is>
+          <t>6Б
+Жантимиров</t>
+        </is>
+      </c>
+      <c r="AJ16" s="22" t="inlineStr">
+        <is>
+          <t>5А,6А
+Жантимиров</t>
+        </is>
+      </c>
+      <c r="AL16" s="22" t="inlineStr">
+        <is>
+          <t>5Б
+Жантимиров</t>
+        </is>
+      </c>
+      <c r="AM16" s="22" t="inlineStr">
+        <is>
+          <t>8Б
+Жантимиров</t>
+        </is>
+      </c>
+      <c r="AN16" s="22" t="inlineStr">
+        <is>
+          <t>9Б
+Жантимиров</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="26" t="inlineStr">
+        <is>
+          <t>Кабинет физики (№16)</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="inlineStr">
+        <is>
+          <t>8Б
+Русина</t>
+        </is>
+      </c>
+      <c r="E17" s="22" t="inlineStr">
+        <is>
+          <t>11Б
+Русина</t>
+        </is>
+      </c>
+      <c r="F17" s="22" t="inlineStr">
+        <is>
+          <t>8А
+Русина</t>
+        </is>
+      </c>
+      <c r="G17" s="22" t="inlineStr">
+        <is>
+          <t>9Б
+Русина</t>
+        </is>
+      </c>
+      <c r="J17" s="22" t="inlineStr">
+        <is>
+          <t>10А
+Русина</t>
+        </is>
+      </c>
+      <c r="K17" s="22" t="inlineStr">
+        <is>
+          <t>7А
+Власова</t>
+        </is>
+      </c>
+      <c r="L17" s="22" t="inlineStr">
         <is>
           <t>8Ә
-Балташева</t>
-        </is>
-      </c>
-      <c r="G9" s="22" t="inlineStr">
+Власова</t>
+        </is>
+      </c>
+      <c r="M17" s="22" t="inlineStr">
+        <is>
+          <t>8А
+Власова</t>
+        </is>
+      </c>
+      <c r="T17" s="22" t="inlineStr">
+        <is>
+          <t>11Б
+Русина</t>
+        </is>
+      </c>
+      <c r="U17" s="22" t="inlineStr">
+        <is>
+          <t>8А
+Русина</t>
+        </is>
+      </c>
+      <c r="W17" s="22" t="inlineStr">
+        <is>
+          <t>7А
+Русина</t>
+        </is>
+      </c>
+      <c r="Z17" s="22" t="inlineStr">
+        <is>
+          <t>5А
+Ізбасты</t>
+        </is>
+      </c>
+      <c r="AA17" s="22" t="inlineStr">
+        <is>
+          <t>6А
+Ізбасты</t>
+        </is>
+      </c>
+      <c r="AB17" s="22" t="inlineStr">
+        <is>
+          <t>11А
+Ізбасты</t>
+        </is>
+      </c>
+      <c r="AC17" s="22" t="inlineStr">
+        <is>
+          <t>8Б
+Русина</t>
+        </is>
+      </c>
+      <c r="AI17" s="22" t="inlineStr">
+        <is>
+          <t>2А
+Жекеева</t>
+        </is>
+      </c>
+      <c r="AJ17" s="22" t="inlineStr">
+        <is>
+          <t>9Б
+Русина</t>
+        </is>
+      </c>
+      <c r="AK17" s="22" t="inlineStr">
+        <is>
+          <t>11Б
+Русина</t>
+        </is>
+      </c>
+      <c r="AL17" s="22" t="inlineStr">
+        <is>
+          <t>10А
+Русина</t>
+        </is>
+      </c>
+      <c r="AM17" s="22" t="inlineStr">
+        <is>
+          <t>7А
+Русина</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="26" t="inlineStr">
+        <is>
+          <t>Кабинет химии (№17)</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>8Б
+Бабич</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>8А
+Бабич</t>
+        </is>
+      </c>
+      <c r="D18" s="22" t="inlineStr">
+        <is>
+          <t>10А
+Бабич</t>
+        </is>
+      </c>
+      <c r="E18" s="22" t="inlineStr">
+        <is>
+          <t>9Б
+Бабич</t>
+        </is>
+      </c>
+      <c r="F18" s="22" t="inlineStr">
         <is>
           <t>11А
 Балташева</t>
         </is>
       </c>
-      <c r="J9" s="22" t="inlineStr">
+      <c r="G18" s="22" t="inlineStr">
+        <is>
+          <t>10А
+Красноперова</t>
+        </is>
+      </c>
+      <c r="J18" s="22" t="inlineStr">
+        <is>
+          <t>8А
+Красноперова</t>
+        </is>
+      </c>
+      <c r="K18" s="22" t="inlineStr">
+        <is>
+          <t>8Б
+Бабич</t>
+        </is>
+      </c>
+      <c r="L18" s="22" t="inlineStr">
+        <is>
+          <t>8А
+Бабич</t>
+        </is>
+      </c>
+      <c r="M18" s="22" t="inlineStr">
+        <is>
+          <t>10А
+Алекпарова</t>
+        </is>
+      </c>
+      <c r="N18" s="22" t="inlineStr">
+        <is>
+          <t>10А
+Бабич</t>
+        </is>
+      </c>
+      <c r="O18" s="22" t="inlineStr">
+        <is>
+          <t>8Б
+Красноперова</t>
+        </is>
+      </c>
+      <c r="P18" s="22" t="inlineStr">
+        <is>
+          <t>7А
+Красноперова</t>
+        </is>
+      </c>
+      <c r="R18" s="22" t="inlineStr">
+        <is>
+          <t>10А
+Бабич</t>
+        </is>
+      </c>
+      <c r="S18" s="22" t="inlineStr">
+        <is>
+          <t>9Б
+Красноперова</t>
+        </is>
+      </c>
+      <c r="T18" s="22" t="inlineStr">
+        <is>
+          <t>10А
+Алекпарова</t>
+        </is>
+      </c>
+      <c r="U18" s="22" t="inlineStr">
+        <is>
+          <t>9Б
+Бабич</t>
+        </is>
+      </c>
+      <c r="V18" s="22" t="inlineStr">
+        <is>
+          <t>8Б
+Бабич</t>
+        </is>
+      </c>
+      <c r="W18" s="22" t="inlineStr">
+        <is>
+          <t>10А
+Красноперова</t>
+        </is>
+      </c>
+      <c r="Z18" s="22" t="inlineStr">
+        <is>
+          <t>8А
+Бабич</t>
+        </is>
+      </c>
+      <c r="AA18" s="22" t="inlineStr">
+        <is>
+          <t>8Б
+Бабич</t>
+        </is>
+      </c>
+      <c r="AB18" s="22" t="inlineStr">
+        <is>
+          <t>10А
+Алекпарова</t>
+        </is>
+      </c>
+      <c r="AC18" s="22" t="inlineStr">
+        <is>
+          <t>10А
+Бабич</t>
+        </is>
+      </c>
+      <c r="AD18" s="22" t="inlineStr">
+        <is>
+          <t>10А
+Бабич</t>
+        </is>
+      </c>
+      <c r="AE18" s="22" t="inlineStr">
+        <is>
+          <t>8А
+Красноперова</t>
+        </is>
+      </c>
+      <c r="AF18" s="22" t="inlineStr">
+        <is>
+          <t>8Б
+Красноперова</t>
+        </is>
+      </c>
+      <c r="AH18" s="22" t="inlineStr">
+        <is>
+          <t>9Б
+Бабич</t>
+        </is>
+      </c>
+      <c r="AI18" s="22" t="inlineStr">
+        <is>
+          <t>8А
+Бабич</t>
+        </is>
+      </c>
+      <c r="AJ18" s="22" t="inlineStr">
+        <is>
+          <t>10А
+Бабич</t>
+        </is>
+      </c>
+      <c r="AK18" s="22" t="inlineStr">
+        <is>
+          <t>8Б
+Бабич</t>
+        </is>
+      </c>
+      <c r="AL18" s="22" t="inlineStr">
+        <is>
+          <t>9Б
+Красноперова</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="26" t="inlineStr">
+        <is>
+          <t>Малый зал</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>11А
+Кашиков</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>1А
+Кашиков</t>
+        </is>
+      </c>
+      <c r="D19" s="22" t="inlineStr">
+        <is>
+          <t>2А,4А
+Кашиков</t>
+        </is>
+      </c>
+      <c r="E19" s="22" t="inlineStr">
+        <is>
+          <t>1Б
+Чифин</t>
+        </is>
+      </c>
+      <c r="F19" s="22" t="inlineStr">
+        <is>
+          <t>5А,6А,8Ә
+Кашиков</t>
+        </is>
+      </c>
+      <c r="G19" s="22" t="inlineStr">
+        <is>
+          <t>5Б
+Чифин</t>
+        </is>
+      </c>
+      <c r="K19" s="22" t="inlineStr">
+        <is>
+          <t>5Б
+Чифин</t>
+        </is>
+      </c>
+      <c r="N19" s="22" t="inlineStr">
         <is>
           <t>11Б
-Асаева</t>
-        </is>
-      </c>
-      <c r="K9" s="22" t="inlineStr">
-        <is>
-          <t>6А
-Асаева</t>
-        </is>
-      </c>
-      <c r="L9" s="22" t="inlineStr">
-        <is>
-          <t>8Б
-Асаева</t>
-        </is>
-      </c>
-      <c r="N9" s="22" t="inlineStr">
-        <is>
-          <t>9Б
-Асаева</t>
-        </is>
-      </c>
-      <c r="R9" s="22" t="inlineStr">
-        <is>
-          <t>6А
-Асаева</t>
-        </is>
-      </c>
-      <c r="S9" s="22" t="inlineStr">
+Мельников</t>
+        </is>
+      </c>
+      <c r="O19" s="22" t="inlineStr">
+        <is>
+          <t>5А,6А,8Ә
+Кашиков</t>
+        </is>
+      </c>
+      <c r="S19" s="22" t="inlineStr">
+        <is>
+          <t>2А,4А
+Кашиков</t>
+        </is>
+      </c>
+      <c r="T19" s="22" t="inlineStr">
+        <is>
+          <t>1А
+Кашиков</t>
+        </is>
+      </c>
+      <c r="V19" s="22" t="inlineStr">
         <is>
           <t>11Б
-Асаева</t>
-        </is>
-      </c>
-      <c r="T9" s="22" t="inlineStr">
-        <is>
-          <t>8Б
-Асаева</t>
-        </is>
-      </c>
-      <c r="U9" s="22" t="inlineStr">
+Мельников</t>
+        </is>
+      </c>
+      <c r="AD19" s="22" t="inlineStr">
+        <is>
+          <t>11Б
+Мельников</t>
+        </is>
+      </c>
+      <c r="AE19" s="22" t="inlineStr">
         <is>
           <t>5Б
-Алекпарова</t>
-        </is>
-      </c>
-      <c r="V9" s="22" t="inlineStr">
-        <is>
-          <t>9Б
-Асаева</t>
-        </is>
-      </c>
-      <c r="W9" s="22" t="inlineStr">
-        <is>
-          <t>9Б
-Алекпарова</t>
-        </is>
-      </c>
-      <c r="Z9" s="22" t="inlineStr">
-        <is>
-          <t>6А
-Асаева</t>
-        </is>
-      </c>
-      <c r="AB9" s="22" t="inlineStr">
-        <is>
-          <t>8Б
-Асаева</t>
-        </is>
-      </c>
-      <c r="AC9" s="22" t="inlineStr">
-        <is>
-          <t>7А
-Алекпарова</t>
-        </is>
-      </c>
-      <c r="AD9" s="22" t="inlineStr">
-        <is>
-          <t>9Б
-Асаева</t>
-        </is>
-      </c>
-      <c r="AE9" s="22" t="inlineStr">
-        <is>
-          <t>11Б
-Асаева</t>
-        </is>
-      </c>
-      <c r="AH9" s="22" t="inlineStr">
-        <is>
-          <t>8Б
-Алекпарова</t>
-        </is>
-      </c>
-      <c r="AI9" s="22" t="inlineStr">
-        <is>
-          <t>6А
-Асаева</t>
-        </is>
-      </c>
-      <c r="AJ9" s="22" t="inlineStr">
-        <is>
-          <t>8А
-Алекпарова</t>
-        </is>
-      </c>
-      <c r="AK9" s="22" t="inlineStr">
-        <is>
-          <t>9Б
-Асаева</t>
-        </is>
-      </c>
-      <c r="AL9" s="22" t="inlineStr">
-        <is>
-          <t>6Б
-Алекпарова</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="26" t="inlineStr">
-        <is>
-          <t>Кабинет казахского языка и литературы (№23)</t>
-        </is>
-      </c>
-      <c r="B10" s="22" t="inlineStr">
+Чифин</t>
+        </is>
+      </c>
+      <c r="AF19" s="22" t="inlineStr">
+        <is>
+          <t>11А
+Кашиков</t>
+        </is>
+      </c>
+      <c r="AI19" s="22" t="inlineStr">
+        <is>
+          <t>1А
+Кашиков</t>
+        </is>
+      </c>
+      <c r="AK19" s="22" t="inlineStr">
+        <is>
+          <t>2А,4А
+Кашиков</t>
+        </is>
+      </c>
+      <c r="AL19" s="22" t="inlineStr">
+        <is>
+          <t>5А,6А,8Ә
+Кашиков</t>
+        </is>
+      </c>
+      <c r="AM19" s="22" t="inlineStr">
+        <is>
+          <t>11А
+Кашиков</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="26" t="inlineStr">
+        <is>
+          <t>Начальный класс 1А (№22)</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>1А
+Жекеева</t>
+        </is>
+      </c>
+      <c r="D20" s="22" t="inlineStr">
+        <is>
+          <t>1А
+Жекеева</t>
+        </is>
+      </c>
+      <c r="E20" s="22" t="inlineStr">
+        <is>
+          <t>1А
+Жекеева</t>
+        </is>
+      </c>
+      <c r="J20" s="22" t="inlineStr">
+        <is>
+          <t>1А
+Жекеева</t>
+        </is>
+      </c>
+      <c r="L20" s="22" t="inlineStr">
+        <is>
+          <t>1А
+Жекеева</t>
+        </is>
+      </c>
+      <c r="R20" s="22" t="inlineStr">
+        <is>
+          <t>1А
+Жекеева</t>
+        </is>
+      </c>
+      <c r="S20" s="22" t="inlineStr">
+        <is>
+          <t>1А
+Жекеева</t>
+        </is>
+      </c>
+      <c r="Z20" s="22" t="inlineStr">
+        <is>
+          <t>1А
+Жекеева</t>
+        </is>
+      </c>
+      <c r="AB20" s="22" t="inlineStr">
+        <is>
+          <t>1А
+Жекеева</t>
+        </is>
+      </c>
+      <c r="AH20" s="22" t="inlineStr">
+        <is>
+          <t>1А
+Жекеева</t>
+        </is>
+      </c>
+      <c r="AJ20" s="22" t="inlineStr">
+        <is>
+          <t>1А
+Жекеева</t>
+        </is>
+      </c>
+      <c r="AK20" s="22" t="inlineStr">
+        <is>
+          <t>1А
+Жекеева</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="26" t="inlineStr">
+        <is>
+          <t>Начальный класс 1Б (№8)</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>1Б
+Ажикенова</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>1Б
+Власова</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="inlineStr">
+        <is>
+          <t>1Б
+Ажикенова</t>
+        </is>
+      </c>
+      <c r="J21" s="22" t="inlineStr">
+        <is>
+          <t>1Б
+Ажикенова</t>
+        </is>
+      </c>
+      <c r="K21" s="22" t="inlineStr">
+        <is>
+          <t>1Б
+Ажикенова</t>
+        </is>
+      </c>
+      <c r="L21" s="22" t="inlineStr">
+        <is>
+          <t>1Б
+Ажикенова</t>
+        </is>
+      </c>
+      <c r="R21" s="22" t="inlineStr">
+        <is>
+          <t>1Б
+Ажикенова</t>
+        </is>
+      </c>
+      <c r="T21" s="22" t="inlineStr">
+        <is>
+          <t>1Б
+Ажикенова</t>
+        </is>
+      </c>
+      <c r="U21" s="22" t="inlineStr">
+        <is>
+          <t>1Б
+Ажикенова</t>
+        </is>
+      </c>
+      <c r="Z21" s="22" t="inlineStr">
+        <is>
+          <t>1Б
+Ажикенова</t>
+        </is>
+      </c>
+      <c r="AA21" s="22" t="inlineStr">
+        <is>
+          <t>1Б
+Ажикенова</t>
+        </is>
+      </c>
+      <c r="AB21" s="22" t="inlineStr">
+        <is>
+          <t>1Б
+Власова</t>
+        </is>
+      </c>
+      <c r="AC21" s="22" t="inlineStr">
+        <is>
+          <t>1Б
+Ажикенова</t>
+        </is>
+      </c>
+      <c r="AH21" s="22" t="inlineStr">
+        <is>
+          <t>1Б
+Ажикенова</t>
+        </is>
+      </c>
+      <c r="AJ21" s="22" t="inlineStr">
+        <is>
+          <t>1Б
+Ажикенова</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="26" t="inlineStr">
+        <is>
+          <t>Начальный класс 2А/4А (№42)</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>4А
+Актаева</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>4А
+Актаева</t>
+        </is>
+      </c>
+      <c r="E22" s="22" t="inlineStr">
         <is>
           <t>2А
-Балгабаева</t>
-        </is>
-      </c>
-      <c r="C10" s="22" t="inlineStr">
-        <is>
-          <t>8Ә
-Балгабаева</t>
-        </is>
-      </c>
-      <c r="D10" s="22" t="inlineStr">
-        <is>
-          <t>7А
-Балгабаева</t>
-        </is>
-      </c>
-      <c r="E10" s="22" t="inlineStr">
-        <is>
-          <t>6А
-Балгабаева</t>
-        </is>
-      </c>
-      <c r="F10" s="22" t="inlineStr">
-        <is>
-          <t>6Б
-Балгабаева</t>
-        </is>
-      </c>
-      <c r="J10" s="22" t="inlineStr">
-        <is>
-          <t>8Ә
-Балгабаева</t>
-        </is>
-      </c>
-      <c r="K10" s="22" t="inlineStr">
-        <is>
-          <t>6Б,6В
-Балгабаева</t>
-        </is>
-      </c>
-      <c r="L10" s="22" t="inlineStr">
-        <is>
-          <t>6А
-Балгабаева</t>
-        </is>
-      </c>
-      <c r="M10" s="22" t="inlineStr">
+Актаева</t>
+        </is>
+      </c>
+      <c r="F22" s="22" t="inlineStr">
         <is>
           <t>4А
-Балгабаева</t>
-        </is>
-      </c>
-      <c r="N10" s="22" t="inlineStr">
-        <is>
-          <t>5А
-Балгабаева</t>
-        </is>
-      </c>
-      <c r="O10" s="22" t="inlineStr">
-        <is>
-          <t>5Б
-Балгабаева</t>
-        </is>
-      </c>
-      <c r="R10" s="22" t="inlineStr">
-        <is>
-          <t>8Б
-Алекпарова</t>
-        </is>
-      </c>
-      <c r="S10" s="22" t="inlineStr">
-        <is>
-          <t>5Б
-Балгабаева</t>
-        </is>
-      </c>
-      <c r="T10" s="22" t="inlineStr">
-        <is>
-          <t>5А
-Балгабаева</t>
-        </is>
-      </c>
-      <c r="U10" s="22" t="inlineStr">
-        <is>
-          <t>6Б
-Балгабаева</t>
-        </is>
-      </c>
-      <c r="W10" s="22" t="inlineStr">
-        <is>
-          <t>11А
-Балгабаева</t>
-        </is>
-      </c>
-      <c r="Z10" s="22" t="inlineStr">
-        <is>
-          <t>2А
-Балгабаева</t>
-        </is>
-      </c>
-      <c r="AA10" s="22" t="inlineStr">
-        <is>
-          <t>6Б,6В
-Балгабаева</t>
-        </is>
-      </c>
-      <c r="AB10" s="22" t="inlineStr">
-        <is>
-          <t>8Ә
-Балгабаева</t>
-        </is>
-      </c>
-      <c r="AC10" s="22" t="inlineStr">
-        <is>
-          <t>5А
-Балгабаева</t>
-        </is>
-      </c>
-      <c r="AD10" s="22" t="inlineStr">
-        <is>
-          <t>6А
-Балгабаева</t>
-        </is>
-      </c>
-      <c r="AE10" s="22" t="inlineStr">
-        <is>
-          <t>6Б
-Алекпарова</t>
-        </is>
-      </c>
-      <c r="AF10" s="22" t="inlineStr">
-        <is>
-          <t>9Б
-Алекпарова</t>
-        </is>
-      </c>
-      <c r="AH10" s="22" t="inlineStr">
+Актаева</t>
+        </is>
+      </c>
+      <c r="J22" s="22" t="inlineStr">
         <is>
           <t>4А
-Балгабаева</t>
-        </is>
-      </c>
-      <c r="AI10" s="22" t="inlineStr">
-        <is>
-          <t>8Ә
-Алекпарова</t>
-        </is>
-      </c>
-      <c r="AK10" s="22" t="inlineStr">
-        <is>
-          <t>11А
-Балгабаева</t>
-        </is>
-      </c>
-      <c r="AL10" s="22" t="inlineStr">
-        <is>
-          <t>7А
-Балгабаева</t>
-        </is>
-      </c>
-      <c r="AM10" s="22" t="inlineStr">
-        <is>
-          <t>5Б
-Балгабаева</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="26" t="inlineStr">
-        <is>
-          <t>Кабинет математики (№25)</t>
-        </is>
-      </c>
-      <c r="B11" s="22" t="inlineStr">
-        <is>
-          <t>11Б
-Пащенко</t>
-        </is>
-      </c>
-      <c r="C11" s="22" t="inlineStr">
-        <is>
-          <t>6Б,6В
-Пащенко</t>
-        </is>
-      </c>
-      <c r="E11" s="22" t="inlineStr">
-        <is>
-          <t>6Б
-Мельникова</t>
-        </is>
-      </c>
-      <c r="F11" s="22" t="inlineStr">
+Актаева</t>
+        </is>
+      </c>
+      <c r="K22" s="22" t="inlineStr">
+        <is>
+          <t>4А
+Актаева</t>
+        </is>
+      </c>
+      <c r="M22" s="22" t="inlineStr">
         <is>
           <t>2А
 Жекеева</t>
         </is>
       </c>
-      <c r="K11" s="22" t="inlineStr">
+      <c r="R22" s="22" t="inlineStr">
         <is>
           <t>2А
+Актаева</t>
+        </is>
+      </c>
+      <c r="T22" s="22" t="inlineStr">
+        <is>
+          <t>4А
+Актаева</t>
+        </is>
+      </c>
+      <c r="U22" s="22" t="inlineStr">
+        <is>
+          <t>4А
+Актаева</t>
+        </is>
+      </c>
+      <c r="V22" s="22" t="inlineStr">
+        <is>
+          <t>4А
 Жекеева</t>
         </is>
       </c>
-      <c r="L11" s="22" t="inlineStr">
-        <is>
-          <t>6Б,6В
-Пащенко</t>
-        </is>
-      </c>
-      <c r="M11" s="22" t="inlineStr">
-        <is>
-          <t>11Б
-Пащенко</t>
-        </is>
-      </c>
-      <c r="N11" s="22" t="inlineStr">
-        <is>
-          <t>7А
-Пащенко</t>
-        </is>
-      </c>
-      <c r="R11" s="22" t="inlineStr">
-        <is>
-          <t>11Б
-Пащенко</t>
-        </is>
-      </c>
-      <c r="S11" s="22" t="inlineStr">
-        <is>
-          <t>6Б,6В
-Пащенко</t>
-        </is>
-      </c>
-      <c r="T11" s="22" t="inlineStr">
-        <is>
-          <t>7А
-Пащенко</t>
-        </is>
-      </c>
-      <c r="U11" s="22" t="inlineStr">
-        <is>
-          <t>5А
-Сапаргалиева</t>
-        </is>
-      </c>
-      <c r="V11" s="22" t="inlineStr">
-        <is>
-          <t>11А
-Сапаргалиева</t>
-        </is>
-      </c>
-      <c r="W11" s="22" t="inlineStr">
-        <is>
-          <t>6А
-Сапаргалиева</t>
-        </is>
-      </c>
-      <c r="X11" s="22" t="inlineStr">
-        <is>
-          <t>8Ә
-Сапаргалиева</t>
-        </is>
-      </c>
-      <c r="AA11" s="22" t="inlineStr">
-        <is>
-          <t>11Б
-Пащенко</t>
-        </is>
-      </c>
-      <c r="AB11" s="22" t="inlineStr">
-        <is>
-          <t>6Б,6В
-Пащенко</t>
-        </is>
-      </c>
-      <c r="AC11" s="22" t="inlineStr">
-        <is>
-          <t>6А
-Сапаргалиева</t>
-        </is>
-      </c>
-      <c r="AD11" s="22" t="inlineStr">
-        <is>
-          <t>5А
-Сапаргалиева</t>
-        </is>
-      </c>
-      <c r="AE11" s="22" t="inlineStr">
-        <is>
-          <t>11А
-Сапаргалиева</t>
-        </is>
-      </c>
-      <c r="AF11" s="22" t="inlineStr">
-        <is>
-          <t>8Ә
-Сапаргалиева</t>
-        </is>
-      </c>
-      <c r="AH11" s="22" t="inlineStr">
-        <is>
-          <t>11Б
-Пащенко</t>
-        </is>
-      </c>
-      <c r="AI11" s="22" t="inlineStr">
-        <is>
-          <t>11Б
-Пащенко</t>
-        </is>
-      </c>
-      <c r="AJ11" s="22" t="inlineStr">
-        <is>
-          <t>6Б,6В
-Пащенко</t>
-        </is>
-      </c>
-      <c r="AK11" s="22" t="inlineStr">
-        <is>
-          <t>7А
-Мельникова</t>
-        </is>
-      </c>
-      <c r="AL11" s="22" t="inlineStr">
-        <is>
-          <t>8Б
-Мельникова</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="26" t="inlineStr">
-        <is>
-          <t>Кабинет мультимедийный (№18)</t>
-        </is>
-      </c>
-      <c r="B12" s="22" t="inlineStr">
-        <is>
-          <t>5Б
-Ильясова</t>
-        </is>
-      </c>
-      <c r="C12" s="22" t="inlineStr">
-        <is>
-          <t>11А
-Ильясова</t>
-        </is>
-      </c>
-      <c r="D12" s="22" t="inlineStr">
-        <is>
-          <t>5А
-Ильясова</t>
-        </is>
-      </c>
-      <c r="F12" s="22" t="inlineStr">
-        <is>
-          <t>6Б
-Ильясова</t>
-        </is>
-      </c>
-      <c r="J12" s="22" t="inlineStr">
-        <is>
-          <t>5Б
-Ильясова</t>
-        </is>
-      </c>
-      <c r="K12" s="22" t="inlineStr">
-        <is>
-          <t>6Б
-Ильясова</t>
-        </is>
-      </c>
-      <c r="L12" s="22" t="inlineStr">
-        <is>
-          <t>10А
-Ильясова</t>
-        </is>
-      </c>
-      <c r="M12" s="22" t="inlineStr">
-        <is>
-          <t>5А
-Ильясова</t>
-        </is>
-      </c>
-      <c r="N12" s="22" t="inlineStr">
-        <is>
-          <t>9Б
-Ильясова</t>
-        </is>
-      </c>
-      <c r="O12" s="22" t="inlineStr">
-        <is>
-          <t>11А
-Ильясова</t>
-        </is>
-      </c>
-      <c r="R12" s="22" t="inlineStr">
-        <is>
-          <t>5А
-Ильясова</t>
-        </is>
-      </c>
-      <c r="S12" s="22" t="inlineStr">
-        <is>
-          <t>10А
-Ильясова</t>
-        </is>
-      </c>
-      <c r="T12" s="22" t="inlineStr">
-        <is>
-          <t>5Б
-Ильясова</t>
-        </is>
-      </c>
-      <c r="U12" s="22" t="inlineStr">
-        <is>
-          <t>6Б
-Ильясова</t>
-        </is>
-      </c>
-      <c r="V12" s="22" t="inlineStr">
-        <is>
-          <t>9Б
-Ильясова</t>
-        </is>
-      </c>
-      <c r="Z12" s="22" t="inlineStr">
-        <is>
-          <t>10А
-Ильясова</t>
-        </is>
-      </c>
-      <c r="AA12" s="22" t="inlineStr">
-        <is>
-          <t>6Б
-Ильясова</t>
-        </is>
-      </c>
-      <c r="AC12" s="22" t="inlineStr">
-        <is>
-          <t>5Б
-Ильясова</t>
-        </is>
-      </c>
-      <c r="AD12" s="22" t="inlineStr">
-        <is>
-          <t>9Б
-Ильясова</t>
-        </is>
-      </c>
-      <c r="AE12" s="22" t="inlineStr">
-        <is>
-          <t>5А
-Ильясова</t>
-        </is>
-      </c>
-      <c r="AH12" s="22" t="inlineStr">
-        <is>
-          <t>5А
-Ильясова</t>
-        </is>
-      </c>
-      <c r="AI12" s="22" t="inlineStr">
-        <is>
-          <t>10А
-Ильясова</t>
-        </is>
-      </c>
-      <c r="AJ12" s="22" t="inlineStr">
-        <is>
-          <t>11А
-Ильясова</t>
-        </is>
-      </c>
-      <c r="AK12" s="22" t="inlineStr">
-        <is>
-          <t>9Б
-Ильясова</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="26" t="inlineStr">
-        <is>
-          <t>Кабинет робототехники (№15)</t>
-        </is>
-      </c>
-      <c r="B13" s="22" t="inlineStr">
-        <is>
-          <t>6Б,6В
-Иващенко</t>
-        </is>
-      </c>
-      <c r="C13" s="22" t="inlineStr">
-        <is>
-          <t>5Б
-Иващенко</t>
-        </is>
-      </c>
-      <c r="E13" s="22" t="inlineStr">
-        <is>
-          <t>10А
-Бучкова</t>
-        </is>
-      </c>
-      <c r="G13" s="22" t="inlineStr">
-        <is>
-          <t>8А
-Бучкова</t>
-        </is>
-      </c>
-      <c r="J13" s="22" t="inlineStr">
-        <is>
-          <t>11А
-Ізбасты</t>
-        </is>
-      </c>
-      <c r="K13" s="22" t="inlineStr">
-        <is>
-          <t>8Ә
-Ізбасты</t>
-        </is>
-      </c>
-      <c r="L13" s="22" t="inlineStr">
-        <is>
-          <t>5А
-Ізбасты</t>
-        </is>
-      </c>
-      <c r="M13" s="22" t="inlineStr">
-        <is>
-          <t>6А
-Ізбасты</t>
-        </is>
-      </c>
-      <c r="N13" s="22" t="inlineStr">
-        <is>
-          <t>5Б
-Бучкова</t>
-        </is>
-      </c>
-      <c r="O13" s="22" t="inlineStr">
-        <is>
-          <t>10А
-Бучкова</t>
-        </is>
-      </c>
-      <c r="R13" s="22" t="inlineStr">
-        <is>
-          <t>11А
-Ізбасты</t>
-        </is>
-      </c>
-      <c r="S13" s="22" t="inlineStr">
-        <is>
-          <t>5А
-Ізбасты</t>
-        </is>
-      </c>
-      <c r="T13" s="22" t="inlineStr">
-        <is>
-          <t>6А
-Ізбасты</t>
-        </is>
-      </c>
-      <c r="U13" s="22" t="inlineStr">
-        <is>
-          <t>8Ә
-Ізбасты</t>
-        </is>
-      </c>
-      <c r="V13" s="22" t="inlineStr">
-        <is>
-          <t>5Б
-Бучкова</t>
-        </is>
-      </c>
-      <c r="W13" s="22" t="inlineStr">
-        <is>
-          <t>8А
-Бучкова</t>
-        </is>
-      </c>
-      <c r="Z13" s="22" t="inlineStr">
-        <is>
-          <t>5Б
-Алекпарова</t>
-        </is>
-      </c>
-      <c r="AA13" s="22" t="inlineStr">
-        <is>
-          <t>8Ә
-Алекпарова</t>
-        </is>
-      </c>
-      <c r="AB13" s="22" t="inlineStr">
-        <is>
-          <t>5Б
-Ажикенова</t>
-        </is>
-      </c>
-      <c r="AC13" s="22" t="inlineStr">
-        <is>
-          <t>11А
-Ізбасты</t>
-        </is>
-      </c>
-      <c r="AD13" s="22" t="inlineStr">
-        <is>
-          <t>8Ә
-Ізбасты</t>
-        </is>
-      </c>
-      <c r="AE13" s="22" t="inlineStr">
-        <is>
-          <t>10А
-Бучкова</t>
-        </is>
-      </c>
-      <c r="AH13" s="22" t="inlineStr">
-        <is>
-          <t>6Б,6В
-Иващенко</t>
-        </is>
-      </c>
-      <c r="AI13" s="22" t="inlineStr">
-        <is>
-          <t>5Б
-Иващенко</t>
-        </is>
-      </c>
-      <c r="AK13" s="22" t="inlineStr">
-        <is>
-          <t>5Б
-Бучкова</t>
-        </is>
-      </c>
-      <c r="AL13" s="22" t="inlineStr">
-        <is>
-          <t>8А
-Бучкова</t>
-        </is>
-      </c>
-      <c r="AM13" s="22" t="inlineStr">
-        <is>
-          <t>10А
-Бучкова</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="26" t="inlineStr">
-        <is>
-          <t>Кабинет русского языка (№20)</t>
-        </is>
-      </c>
-      <c r="B14" s="22" t="inlineStr">
-        <is>
-          <t>9Б
-Дмитриев</t>
-        </is>
-      </c>
-      <c r="C14" s="22" t="inlineStr">
-        <is>
-          <t>11Б
-Дмитриев</t>
-        </is>
-      </c>
-      <c r="D14" s="22" t="inlineStr">
-        <is>
-          <t>8А
-Дмитриев</t>
-        </is>
-      </c>
-      <c r="E14" s="22" t="inlineStr">
-        <is>
-          <t>8Б
-Дмитриев</t>
-        </is>
-      </c>
-      <c r="F14" s="22" t="inlineStr">
-        <is>
-          <t>10А
-Дмитриев</t>
-        </is>
-      </c>
-      <c r="L14" s="22" t="inlineStr">
-        <is>
-          <t>7А
-Дмитриев</t>
-        </is>
-      </c>
-      <c r="M14" s="22" t="inlineStr">
-        <is>
-          <t>9Б
-Дмитриев</t>
-        </is>
-      </c>
-      <c r="N14" s="22" t="inlineStr">
-        <is>
-          <t>8Б
-Дмитриев</t>
-        </is>
-      </c>
-      <c r="P14" s="22" t="inlineStr">
-        <is>
-          <t>8А
-Дмитриев</t>
-        </is>
-      </c>
-      <c r="R14" s="22" t="inlineStr">
-        <is>
-          <t>8А
-Дмитриев</t>
-        </is>
-      </c>
-      <c r="S14" s="22" t="inlineStr">
-        <is>
-          <t>7А
-Дмитриев</t>
-        </is>
-      </c>
-      <c r="T14" s="22" t="inlineStr">
-        <is>
-          <t>9Б
-Дмитриев</t>
-        </is>
-      </c>
-      <c r="U14" s="22" t="inlineStr">
-        <is>
-          <t>11Б
-Дмитриев</t>
-        </is>
-      </c>
-      <c r="V14" s="22" t="inlineStr">
-        <is>
-          <t>10А
-Дмитриев</t>
-        </is>
-      </c>
-      <c r="W14" s="22" t="inlineStr">
-        <is>
-          <t>8Б
-Дмитриев</t>
-        </is>
-      </c>
-      <c r="Z14" s="22" t="inlineStr">
-        <is>
-          <t>8Б
-Дмитриев</t>
-        </is>
-      </c>
-      <c r="AA14" s="22" t="inlineStr">
-        <is>
-          <t>9Б
-Дмитриев</t>
-        </is>
-      </c>
-      <c r="AB14" s="22" t="inlineStr">
-        <is>
-          <t>8А
-Дмитриев</t>
-        </is>
-      </c>
-      <c r="AC14" s="22" t="inlineStr">
-        <is>
-          <t>11Б
-Дмитриев</t>
-        </is>
-      </c>
-      <c r="AD14" s="22" t="inlineStr">
-        <is>
-          <t>7А
-Дмитриев</t>
-        </is>
-      </c>
-      <c r="AH14" s="22" t="inlineStr">
-        <is>
-          <t>8А
-Дмитриев</t>
-        </is>
-      </c>
-      <c r="AI14" s="22" t="inlineStr">
-        <is>
-          <t>9Б
-Дмитриев</t>
-        </is>
-      </c>
-      <c r="AJ14" s="22" t="inlineStr">
-        <is>
-          <t>8Б
-Дмитриев</t>
-        </is>
-      </c>
-      <c r="AK14" s="22" t="inlineStr">
-        <is>
-          <t>10А
-Дмитриев</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="26" t="inlineStr">
-        <is>
-          <t>Кабинет технологии (девочки) (№29)</t>
-        </is>
-      </c>
-      <c r="C15" s="22" t="inlineStr">
+      <c r="Z22" s="22" t="inlineStr">
+        <is>
+          <t>4А
+Актаева</t>
+        </is>
+      </c>
+      <c r="AA22" s="22" t="inlineStr">
+        <is>
+          <t>4А
+Актаева</t>
+        </is>
+      </c>
+      <c r="AC22" s="22" t="inlineStr">
+        <is>
+          <t>4А
+Актаева</t>
+        </is>
+      </c>
+      <c r="AD22" s="22" t="inlineStr">
+        <is>
+          <t>4А
+Актаева</t>
+        </is>
+      </c>
+      <c r="AH22" s="22" t="inlineStr">
         <is>
           <t>2А
-Жекеева</t>
-        </is>
-      </c>
-      <c r="D15" s="22" t="inlineStr">
-        <is>
-          <t>9Б
-Алекпарова</t>
-        </is>
-      </c>
-      <c r="E15" s="22" t="inlineStr">
-        <is>
-          <t>8А
-Алекпарова</t>
-        </is>
-      </c>
-      <c r="F15" s="22" t="inlineStr">
-        <is>
-          <t>7А
-Алекпарова</t>
-        </is>
-      </c>
-      <c r="G15" s="22" t="inlineStr">
-        <is>
-          <t>6Б
-Алекпарова</t>
-        </is>
-      </c>
-      <c r="J15" s="22" t="inlineStr">
-        <is>
-          <t>8Б
-Алекпарова</t>
-        </is>
-      </c>
-      <c r="K15" s="22" t="inlineStr">
-        <is>
-          <t>8А
-Алекпарова</t>
-        </is>
-      </c>
-      <c r="L15" s="22" t="inlineStr">
-        <is>
-          <t>5Б
-Алекпарова</t>
-        </is>
-      </c>
-      <c r="N15" s="22" t="inlineStr">
-        <is>
-          <t>8Ә
-Алекпарова</t>
-        </is>
-      </c>
-      <c r="O15" s="22" t="inlineStr">
-        <is>
-          <t>7А
-Алекпарова</t>
-        </is>
-      </c>
-      <c r="S15" s="22" t="inlineStr">
+Актаева</t>
+        </is>
+      </c>
+      <c r="AI22" s="22" t="inlineStr">
+        <is>
+          <t>4А
+Актаева</t>
+        </is>
+      </c>
+      <c r="AJ22" s="22" t="inlineStr">
+        <is>
+          <t>2А,4А
+Актаева</t>
+        </is>
+      </c>
+      <c r="AL22" s="22" t="inlineStr">
+        <is>
+          <t>4А
+Актаева</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="26" t="inlineStr">
+        <is>
+          <t>Начальный класс 2Б (№6)</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
         <is>
           <t>2Б
-Жукова</t>
-        </is>
-      </c>
-      <c r="T15" s="22" t="inlineStr">
-        <is>
-          <t>2А
-Жекеева</t>
-        </is>
-      </c>
-      <c r="U15" s="22" t="inlineStr">
-        <is>
-          <t>7А
-Жукова</t>
-        </is>
-      </c>
-      <c r="V15" s="22" t="inlineStr">
+Квашнина</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="inlineStr">
+        <is>
+          <t>2Б
+Квашнина</t>
+        </is>
+      </c>
+      <c r="D23" s="22" t="inlineStr">
+        <is>
+          <t>2Б
+Асаева</t>
+        </is>
+      </c>
+      <c r="J23" s="22" t="inlineStr">
+        <is>
+          <t>2Б
+Квашнина</t>
+        </is>
+      </c>
+      <c r="K23" s="22" t="inlineStr">
+        <is>
+          <t>2Б
+Квашнина</t>
+        </is>
+      </c>
+      <c r="L23" s="22" t="inlineStr">
+        <is>
+          <t>2Б
+Квашнина</t>
+        </is>
+      </c>
+      <c r="M23" s="22" t="inlineStr">
+        <is>
+          <t>2Б
+Квашнина</t>
+        </is>
+      </c>
+      <c r="R23" s="22" t="inlineStr">
+        <is>
+          <t>2Б
+Квашнина</t>
+        </is>
+      </c>
+      <c r="T23" s="22" t="inlineStr">
+        <is>
+          <t>2Б
+Квашнина</t>
+        </is>
+      </c>
+      <c r="Z23" s="22" t="inlineStr">
+        <is>
+          <t>2Б
+Квашнина</t>
+        </is>
+      </c>
+      <c r="AA23" s="22" t="inlineStr">
+        <is>
+          <t>2Б
+Квашнина</t>
+        </is>
+      </c>
+      <c r="AB23" s="22" t="inlineStr">
+        <is>
+          <t>2Б
+Квашнина</t>
+        </is>
+      </c>
+      <c r="AC23" s="22" t="inlineStr">
+        <is>
+          <t>2Б
+Асаева</t>
+        </is>
+      </c>
+      <c r="AH23" s="22" t="inlineStr">
+        <is>
+          <t>2Б
+Квашнина</t>
+        </is>
+      </c>
+      <c r="AI23" s="22" t="inlineStr">
+        <is>
+          <t>2Б
+Квашнина</t>
+        </is>
+      </c>
+      <c r="AL23" s="22" t="inlineStr">
+        <is>
+          <t>2Б
+Асаева</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="26" t="inlineStr">
+        <is>
+          <t>Начальный класс 3А (№7)</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>3А
+Темерканова</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="inlineStr">
+        <is>
+          <t>3А
+Темерканова</t>
+        </is>
+      </c>
+      <c r="D24" s="22" t="inlineStr">
+        <is>
+          <t>3А
+Власова</t>
+        </is>
+      </c>
+      <c r="E24" s="22" t="inlineStr">
+        <is>
+          <t>3А
+Темерканова</t>
+        </is>
+      </c>
+      <c r="J24" s="22" t="inlineStr">
+        <is>
+          <t>3А
+Темерканова</t>
+        </is>
+      </c>
+      <c r="K24" s="22" t="inlineStr">
+        <is>
+          <t>3А
+Темерканова</t>
+        </is>
+      </c>
+      <c r="L24" s="22" t="inlineStr">
+        <is>
+          <t>3А
+Темерканова</t>
+        </is>
+      </c>
+      <c r="R24" s="22" t="inlineStr">
+        <is>
+          <t>3А
+Темерканова</t>
+        </is>
+      </c>
+      <c r="S24" s="22" t="inlineStr">
+        <is>
+          <t>3А
+Темерканова</t>
+        </is>
+      </c>
+      <c r="U24" s="22" t="inlineStr">
+        <is>
+          <t>3А
+Темерканова</t>
+        </is>
+      </c>
+      <c r="V24" s="22" t="inlineStr">
+        <is>
+          <t>3А
+Акауова</t>
+        </is>
+      </c>
+      <c r="Z24" s="22" t="inlineStr">
+        <is>
+          <t>3А
+Темерканова</t>
+        </is>
+      </c>
+      <c r="AA24" s="22" t="inlineStr">
+        <is>
+          <t>3А
+Темерканова</t>
+        </is>
+      </c>
+      <c r="AB24" s="22" t="inlineStr">
+        <is>
+          <t>3А
+Темерканова</t>
+        </is>
+      </c>
+      <c r="AC24" s="22" t="inlineStr">
+        <is>
+          <t>3А
+Власова</t>
+        </is>
+      </c>
+      <c r="AD24" s="22" t="inlineStr">
+        <is>
+          <t>3А
+Темерканова</t>
+        </is>
+      </c>
+      <c r="AH24" s="22" t="inlineStr">
+        <is>
+          <t>3А
+Темерканова</t>
+        </is>
+      </c>
+      <c r="AI24" s="22" t="inlineStr">
+        <is>
+          <t>3А
+Темерканова</t>
+        </is>
+      </c>
+      <c r="AK24" s="22" t="inlineStr">
+        <is>
+          <t>3А
+Акауова</t>
+        </is>
+      </c>
+      <c r="AM24" s="22" t="inlineStr">
+        <is>
+          <t>3А
+Власова</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="26" t="inlineStr">
+        <is>
+          <t>Начальный класс 4Б (№9)</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="inlineStr">
         <is>
           <t>4Б
 Радионова</t>
         </is>
       </c>
-      <c r="W15" s="22" t="inlineStr">
-        <is>
-          <t>6Б
-Жукова</t>
-        </is>
-      </c>
-      <c r="AA15" s="22" t="inlineStr">
-        <is>
-          <t>2А
-Жекеева</t>
-        </is>
-      </c>
-      <c r="AB15" s="22" t="inlineStr">
-        <is>
-          <t>2А,4А
-Актаева</t>
-        </is>
-      </c>
-      <c r="AC15" s="22" t="inlineStr">
-        <is>
-          <t>2А
-Жекеева</t>
-        </is>
-      </c>
-      <c r="AD15" s="22" t="inlineStr">
-        <is>
-          <t>5Б
-Жукова</t>
-        </is>
-      </c>
-      <c r="AF15" s="22" t="inlineStr">
+      <c r="C25" s="22" t="inlineStr">
+        <is>
+          <t>4Б
+Радионова</t>
+        </is>
+      </c>
+      <c r="E25" s="22" t="inlineStr">
+        <is>
+          <t>4Б
+Радионова</t>
+        </is>
+      </c>
+      <c r="F25" s="22" t="inlineStr">
+        <is>
+          <t>4Б
+Асаева</t>
+        </is>
+      </c>
+      <c r="J25" s="22" t="inlineStr">
+        <is>
+          <t>4Б
+Радионова</t>
+        </is>
+      </c>
+      <c r="K25" s="22" t="inlineStr">
+        <is>
+          <t>4Б
+Радионова</t>
+        </is>
+      </c>
+      <c r="L25" s="22" t="inlineStr">
+        <is>
+          <t>4Б
+Радионова</t>
+        </is>
+      </c>
+      <c r="M25" s="22" t="inlineStr">
+        <is>
+          <t>4Б
+Асаева</t>
+        </is>
+      </c>
+      <c r="N25" s="22" t="inlineStr">
+        <is>
+          <t>4Б
+Радионова</t>
+        </is>
+      </c>
+      <c r="R25" s="22" t="inlineStr">
+        <is>
+          <t>4Б
+Радионова</t>
+        </is>
+      </c>
+      <c r="S25" s="22" t="inlineStr">
+        <is>
+          <t>4Б
+Радионова</t>
+        </is>
+      </c>
+      <c r="U25" s="22" t="inlineStr">
+        <is>
+          <t>4Б
+Асаева</t>
+        </is>
+      </c>
+      <c r="W25" s="22" t="inlineStr">
+        <is>
+          <t>4Б
+Акауова</t>
+        </is>
+      </c>
+      <c r="Z25" s="22" t="inlineStr">
+        <is>
+          <t>4Б
+Радионова</t>
+        </is>
+      </c>
+      <c r="AA25" s="22" t="inlineStr">
+        <is>
+          <t>4Б
+Радионова</t>
+        </is>
+      </c>
+      <c r="AB25" s="22" t="inlineStr">
+        <is>
+          <t>4Б
+Радионова</t>
+        </is>
+      </c>
+      <c r="AC25" s="22" t="inlineStr">
+        <is>
+          <t>4Б
+Акауова</t>
+        </is>
+      </c>
+      <c r="AD25" s="22" t="inlineStr">
+        <is>
+          <t>4Б
+Радионова</t>
+        </is>
+      </c>
+      <c r="AH25" s="22" t="inlineStr">
+        <is>
+          <t>4Б
+Радионова</t>
+        </is>
+      </c>
+      <c r="AI25" s="22" t="inlineStr">
+        <is>
+          <t>4Б
+Радионова</t>
+        </is>
+      </c>
+      <c r="AJ25" s="22" t="inlineStr">
+        <is>
+          <t>4Б
+Асаева</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="26" t="inlineStr">
+        <is>
+          <t>Спортивный зал (№01)</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="inlineStr">
+        <is>
+          <t>10А
+Мельников</t>
+        </is>
+      </c>
+      <c r="C26" s="22" t="inlineStr">
+        <is>
+          <t>9Б
+Мельников</t>
+        </is>
+      </c>
+      <c r="D26" s="22" t="inlineStr">
+        <is>
+          <t>4Б
+Чифин</t>
+        </is>
+      </c>
+      <c r="E26" s="22" t="inlineStr">
+        <is>
+          <t>2Б
+Ольков</t>
+        </is>
+      </c>
+      <c r="F26" s="22" t="inlineStr">
+        <is>
+          <t>3А
+Чифин</t>
+        </is>
+      </c>
+      <c r="G26" s="22" t="inlineStr">
+        <is>
+          <t>7А
+Ольков</t>
+        </is>
+      </c>
+      <c r="H26" s="22" t="inlineStr">
         <is>
           <t>8А
-Жукова</t>
-        </is>
-      </c>
-      <c r="AI15" s="22" t="inlineStr">
+Ольков</t>
+        </is>
+      </c>
+      <c r="K26" s="22" t="inlineStr">
+        <is>
+          <t>9Б
+Мельников</t>
+        </is>
+      </c>
+      <c r="M26" s="22" t="inlineStr">
         <is>
           <t>6Б,6В
-Жукова</t>
-        </is>
-      </c>
-      <c r="AJ15" s="22" t="inlineStr">
-        <is>
-          <t>2Б
-Жукова</t>
-        </is>
-      </c>
-      <c r="AK15" s="22" t="inlineStr">
-        <is>
-          <t>1Б
-Ажикенова</t>
-        </is>
-      </c>
-      <c r="AL15" s="22" t="inlineStr">
-        <is>
-          <t>5Б
-Жукова</t>
-        </is>
-      </c>
-      <c r="AM15" s="22" t="inlineStr">
+Ольков</t>
+        </is>
+      </c>
+      <c r="O26" s="22" t="inlineStr">
+        <is>
+          <t>8А
+Ольков</t>
+        </is>
+      </c>
+      <c r="P26" s="22" t="inlineStr">
         <is>
           <t>8Б
-Жукова</t>
-        </is>
-      </c>
-      <c r="AN15" s="22" t="inlineStr">
-        <is>
-          <t>9Б
-Жукова</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="26" t="inlineStr">
-        <is>
-          <t>Кабинет технологии (мальчики) (№39)</t>
-        </is>
-      </c>
-      <c r="D16" s="22" t="inlineStr">
+Ольков</t>
+        </is>
+      </c>
+      <c r="R26" s="22" t="inlineStr">
         <is>
           <t>6Б,6В
-Темерканова</t>
-        </is>
-      </c>
-      <c r="M16" s="22" t="inlineStr">
-        <is>
-          <t>3А
-Темерканова</t>
-        </is>
-      </c>
-      <c r="N16" s="22" t="inlineStr">
-        <is>
-          <t>6Б,6В
-Темерканова</t>
-        </is>
-      </c>
-      <c r="T16" s="22" t="inlineStr">
-        <is>
-          <t>6Б,6В
-Темерканова</t>
-        </is>
-      </c>
-      <c r="U16" s="22" t="inlineStr">
-        <is>
-          <t>7А
-Жантимиров</t>
-        </is>
-      </c>
-      <c r="V16" s="22" t="inlineStr">
-        <is>
-          <t>5А,6А,8Ә
-Жантимиров</t>
-        </is>
-      </c>
-      <c r="W16" s="22" t="inlineStr">
-        <is>
-          <t>6Б
-Жантимиров</t>
-        </is>
-      </c>
-      <c r="AA16" s="22" t="inlineStr">
-        <is>
-          <t>1А
-Жантимиров</t>
-        </is>
-      </c>
-      <c r="AC16" s="22" t="inlineStr">
-        <is>
-          <t>6Б,6В
-Темерканова</t>
-        </is>
-      </c>
-      <c r="AD16" s="22" t="inlineStr">
-        <is>
-          <t>5Б
-Жантимиров</t>
-        </is>
-      </c>
-      <c r="AF16" s="22" t="inlineStr">
-        <is>
-          <t>8А
-Жантимиров</t>
-        </is>
-      </c>
-      <c r="AI16" s="22" t="inlineStr">
-        <is>
-          <t>6Б
-Жантимиров</t>
-        </is>
-      </c>
-      <c r="AJ16" s="22" t="inlineStr">
-        <is>
-          <t>5А,6А
-Жантимиров</t>
-        </is>
-      </c>
-      <c r="AK16" s="22" t="inlineStr">
-        <is>
-          <t>6Б,6В
-Темерканова</t>
-        </is>
-      </c>
-      <c r="AL16" s="22" t="inlineStr">
-        <is>
-          <t>5Б
-Жантимиров</t>
-        </is>
-      </c>
-      <c r="AM16" s="22" t="inlineStr">
-        <is>
-          <t>8Б
-Жантимиров</t>
-        </is>
-      </c>
-      <c r="AN16" s="22" t="inlineStr">
-        <is>
-          <t>9Б
-Жантимиров</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="26" t="inlineStr">
-        <is>
-          <t>Кабинет физики (№16)</t>
-        </is>
-      </c>
-      <c r="D17" s="22" t="inlineStr">
-        <is>
-          <t>8Б
-Русина</t>
-        </is>
-      </c>
-      <c r="E17" s="22" t="inlineStr">
-        <is>
-          <t>11Б
-Русина</t>
-        </is>
-      </c>
-      <c r="F17" s="22" t="inlineStr">
-        <is>
-          <t>8А
-Русина</t>
-        </is>
-      </c>
-      <c r="G17" s="22" t="inlineStr">
-        <is>
-          <t>9Б
-Русина</t>
-        </is>
-      </c>
-      <c r="J17" s="22" t="inlineStr">
-        <is>
-          <t>10А
-Русина</t>
-        </is>
-      </c>
-      <c r="K17" s="22" t="inlineStr">
-        <is>
-          <t>7А
-Дюсембаева</t>
-        </is>
-      </c>
-      <c r="L17" s="22" t="inlineStr">
-        <is>
-          <t>8Ә
-Дюсембаева</t>
-        </is>
-      </c>
-      <c r="M17" s="22" t="inlineStr">
-        <is>
-          <t>8А
-Дюсембаева</t>
-        </is>
-      </c>
-      <c r="T17" s="22" t="inlineStr">
-        <is>
-          <t>11Б
-Русина</t>
-        </is>
-      </c>
-      <c r="U17" s="22" t="inlineStr">
-        <is>
-          <t>8А
-Русина</t>
-        </is>
-      </c>
-      <c r="X17" s="22" t="inlineStr">
-        <is>
-          <t>7А
-Русина</t>
-        </is>
-      </c>
-      <c r="Z17" s="22" t="inlineStr">
-        <is>
-          <t>5А
-Ізбасты</t>
-        </is>
-      </c>
-      <c r="AA17" s="22" t="inlineStr">
-        <is>
-          <t>6А
-Ізбасты</t>
-        </is>
-      </c>
-      <c r="AB17" s="22" t="inlineStr">
-        <is>
-          <t>11А
-Ізбасты</t>
-        </is>
-      </c>
-      <c r="AC17" s="22" t="inlineStr">
-        <is>
-          <t>8Б
-Русина</t>
-        </is>
-      </c>
-      <c r="AH17" s="22" t="inlineStr">
-        <is>
-          <t>7А
-Русина</t>
-        </is>
-      </c>
-      <c r="AI17" s="22" t="inlineStr">
-        <is>
-          <t>2А
-Жекеева</t>
-        </is>
-      </c>
-      <c r="AJ17" s="22" t="inlineStr">
-        <is>
-          <t>9Б
-Русина</t>
-        </is>
-      </c>
-      <c r="AK17" s="22" t="inlineStr">
-        <is>
-          <t>11Б
-Русина</t>
-        </is>
-      </c>
-      <c r="AL17" s="22" t="inlineStr">
-        <is>
-          <t>10А
-Русина</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="26" t="inlineStr">
-        <is>
-          <t>Кабинет химии (№17)</t>
-        </is>
-      </c>
-      <c r="B18" s="22" t="inlineStr">
-        <is>
-          <t>8Б
-Бабич</t>
-        </is>
-      </c>
-      <c r="C18" s="22" t="inlineStr">
-        <is>
-          <t>8А
-Бабич</t>
-        </is>
-      </c>
-      <c r="D18" s="22" t="inlineStr">
-        <is>
-          <t>10А
-Бабич</t>
-        </is>
-      </c>
-      <c r="E18" s="22" t="inlineStr">
-        <is>
-          <t>9Б
-Бабич</t>
-        </is>
-      </c>
-      <c r="F18" s="22" t="inlineStr">
-        <is>
-          <t>11А
-Балташева</t>
-        </is>
-      </c>
-      <c r="G18" s="22" t="inlineStr">
-        <is>
-          <t>10А
-Красноперова</t>
-        </is>
-      </c>
-      <c r="J18" s="22" t="inlineStr">
-        <is>
-          <t>8А
-Красноперова</t>
-        </is>
-      </c>
-      <c r="K18" s="22" t="inlineStr">
-        <is>
-          <t>8Б
-Бабич</t>
-        </is>
-      </c>
-      <c r="L18" s="22" t="inlineStr">
-        <is>
-          <t>8А
-Бабич</t>
-        </is>
-      </c>
-      <c r="M18" s="22" t="inlineStr">
-        <is>
-          <t>10А
-Алекпарова</t>
-        </is>
-      </c>
-      <c r="N18" s="22" t="inlineStr">
-        <is>
-          <t>10А
-Бабич</t>
-        </is>
-      </c>
-      <c r="O18" s="22" t="inlineStr">
-        <is>
-          <t>8Б
-Красноперова</t>
-        </is>
-      </c>
-      <c r="P18" s="22" t="inlineStr">
-        <is>
-          <t>7А
-Красноперова</t>
-        </is>
-      </c>
-      <c r="R18" s="22" t="inlineStr">
-        <is>
-          <t>10А
-Бабич</t>
-        </is>
-      </c>
-      <c r="S18" s="22" t="inlineStr">
-        <is>
-          <t>9Б
-Красноперова</t>
-        </is>
-      </c>
-      <c r="T18" s="22" t="inlineStr">
-        <is>
-          <t>10А
-Алекпарова</t>
-        </is>
-      </c>
-      <c r="U18" s="22" t="inlineStr">
-        <is>
-          <t>9Б
-Бабич</t>
-        </is>
-      </c>
-      <c r="V18" s="22" t="inlineStr">
-        <is>
-          <t>8Б
-Бабич</t>
-        </is>
-      </c>
-      <c r="W18" s="22" t="inlineStr">
-        <is>
-          <t>10А
-Красноперова</t>
-        </is>
-      </c>
-      <c r="Z18" s="22" t="inlineStr">
-        <is>
-          <t>8А
-Бабич</t>
-        </is>
-      </c>
-      <c r="AA18" s="22" t="inlineStr">
-        <is>
-          <t>8Б
-Бабич</t>
-        </is>
-      </c>
-      <c r="AB18" s="22" t="inlineStr">
-        <is>
-          <t>10А
-Алекпарова</t>
-        </is>
-      </c>
-      <c r="AC18" s="22" t="inlineStr">
-        <is>
-          <t>10А
-Бабич</t>
-        </is>
-      </c>
-      <c r="AD18" s="22" t="inlineStr">
-        <is>
-          <t>10А
-Бабич</t>
-        </is>
-      </c>
-      <c r="AE18" s="22" t="inlineStr">
-        <is>
-          <t>8А
-Красноперова</t>
-        </is>
-      </c>
-      <c r="AF18" s="22" t="inlineStr">
-        <is>
-          <t>8Б
-Красноперова</t>
-        </is>
-      </c>
-      <c r="AH18" s="22" t="inlineStr">
-        <is>
-          <t>9Б
-Бабич</t>
-        </is>
-      </c>
-      <c r="AI18" s="22" t="inlineStr">
-        <is>
-          <t>8А
-Бабич</t>
-        </is>
-      </c>
-      <c r="AJ18" s="22" t="inlineStr">
-        <is>
-          <t>10А
-Бабич</t>
-        </is>
-      </c>
-      <c r="AK18" s="22" t="inlineStr">
-        <is>
-          <t>8Б
-Бабич</t>
-        </is>
-      </c>
-      <c r="AL18" s="22" t="inlineStr">
-        <is>
-          <t>9Б
-Красноперова</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="26" t="inlineStr">
-        <is>
-          <t>Малый зал</t>
-        </is>
-      </c>
-      <c r="B19" s="22" t="inlineStr">
-        <is>
-          <t>11А
-Кашиков</t>
-        </is>
-      </c>
-      <c r="C19" s="22" t="inlineStr">
-        <is>
-          <t>1А
-Кашиков</t>
-        </is>
-      </c>
-      <c r="D19" s="22" t="inlineStr">
-        <is>
-          <t>2А,4А
-Кашиков</t>
-        </is>
-      </c>
-      <c r="E19" s="22" t="inlineStr">
+Ольков</t>
+        </is>
+      </c>
+      <c r="S26" s="22" t="inlineStr">
         <is>
           <t>1Б
 Чифин</t>
         </is>
       </c>
-      <c r="F19" s="22" t="inlineStr">
-        <is>
-          <t>5А,6А,8Ә
-Кашиков</t>
-        </is>
-      </c>
-      <c r="G19" s="22" t="inlineStr">
-        <is>
-          <t>5Б
-Чифин</t>
-        </is>
-      </c>
-      <c r="K19" s="22" t="inlineStr">
-        <is>
-          <t>5Б
-Чифин</t>
-        </is>
-      </c>
-      <c r="N19" s="22" t="inlineStr">
-        <is>
-          <t>11Б
-Мельников</t>
-        </is>
-      </c>
-      <c r="O19" s="22" t="inlineStr">
-        <is>
-          <t>5А,6А,8Ә
-Кашиков</t>
-        </is>
-      </c>
-      <c r="S19" s="22" t="inlineStr">
-        <is>
-          <t>2А,4А
-Кашиков</t>
-        </is>
-      </c>
-      <c r="T19" s="22" t="inlineStr">
-        <is>
-          <t>1А
-Кашиков</t>
-        </is>
-      </c>
-      <c r="V19" s="22" t="inlineStr">
-        <is>
-          <t>11Б
-Мельников</t>
-        </is>
-      </c>
-      <c r="AD19" s="22" t="inlineStr">
-        <is>
-          <t>11Б
-Мельников</t>
-        </is>
-      </c>
-      <c r="AE19" s="22" t="inlineStr">
-        <is>
-          <t>5Б
-Чифин</t>
-        </is>
-      </c>
-      <c r="AF19" s="22" t="inlineStr">
-        <is>
-          <t>11А
-Кашиков</t>
-        </is>
-      </c>
-      <c r="AI19" s="22" t="inlineStr">
-        <is>
-          <t>1А
-Кашиков</t>
-        </is>
-      </c>
-      <c r="AK19" s="22" t="inlineStr">
-        <is>
-          <t>2А,4А
-Кашиков</t>
-        </is>
-      </c>
-      <c r="AL19" s="22" t="inlineStr">
-        <is>
-          <t>5А,6А,8Ә
-Кашиков</t>
-        </is>
-      </c>
-      <c r="AM19" s="22" t="inlineStr">
-        <is>
-          <t>11А
-Кашиков</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="26" t="inlineStr">
-        <is>
-          <t>Начальный класс 1А (№22)</t>
-        </is>
-      </c>
-      <c r="B20" s="22" t="inlineStr">
-        <is>
-          <t>1А
-Жекеева</t>
-        </is>
-      </c>
-      <c r="D20" s="22" t="inlineStr">
-        <is>
-          <t>1А
-Жекеева</t>
-        </is>
-      </c>
-      <c r="E20" s="22" t="inlineStr">
-        <is>
-          <t>1А
-Жекеева</t>
-        </is>
-      </c>
-      <c r="J20" s="22" t="inlineStr">
-        <is>
-          <t>1А
-Жекеева</t>
-        </is>
-      </c>
-      <c r="L20" s="22" t="inlineStr">
-        <is>
-          <t>1А
-Жекеева</t>
-        </is>
-      </c>
-      <c r="R20" s="22" t="inlineStr">
-        <is>
-          <t>1А
-Жекеева</t>
-        </is>
-      </c>
-      <c r="S20" s="22" t="inlineStr">
-        <is>
-          <t>1А
-Жекеева</t>
-        </is>
-      </c>
-      <c r="Z20" s="22" t="inlineStr">
-        <is>
-          <t>1А
-Жекеева</t>
-        </is>
-      </c>
-      <c r="AB20" s="22" t="inlineStr">
-        <is>
-          <t>1А
-Жекеева</t>
-        </is>
-      </c>
-      <c r="AH20" s="22" t="inlineStr">
-        <is>
-          <t>1А
-Жекеева</t>
-        </is>
-      </c>
-      <c r="AJ20" s="22" t="inlineStr">
-        <is>
-          <t>1А
-Жекеева</t>
-        </is>
-      </c>
-      <c r="AK20" s="22" t="inlineStr">
-        <is>
-          <t>1А
-Жекеева</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="26" t="inlineStr">
-        <is>
-          <t>Начальный класс 1Б (№8)</t>
-        </is>
-      </c>
-      <c r="B21" s="22" t="inlineStr">
-        <is>
-          <t>1Б
-Ажикенова</t>
-        </is>
-      </c>
-      <c r="C21" s="22" t="inlineStr">
-        <is>
-          <t>1Б
-Дюсембаева</t>
-        </is>
-      </c>
-      <c r="D21" s="22" t="inlineStr">
-        <is>
-          <t>1Б
-Ажикенова</t>
-        </is>
-      </c>
-      <c r="J21" s="22" t="inlineStr">
-        <is>
-          <t>1Б
-Ажикенова</t>
-        </is>
-      </c>
-      <c r="K21" s="22" t="inlineStr">
-        <is>
-          <t>1Б
-Ажикенова</t>
-        </is>
-      </c>
-      <c r="L21" s="22" t="inlineStr">
-        <is>
-          <t>1Б
-Ажикенова</t>
-        </is>
-      </c>
-      <c r="R21" s="22" t="inlineStr">
-        <is>
-          <t>1Б
-Ажикенова</t>
-        </is>
-      </c>
-      <c r="T21" s="22" t="inlineStr">
-        <is>
-          <t>1Б
-Ажикенова</t>
-        </is>
-      </c>
-      <c r="U21" s="22" t="inlineStr">
-        <is>
-          <t>1Б
-Ажикенова</t>
-        </is>
-      </c>
-      <c r="Z21" s="22" t="inlineStr">
-        <is>
-          <t>1Б
-Ажикенова</t>
-        </is>
-      </c>
-      <c r="AA21" s="22" t="inlineStr">
-        <is>
-          <t>1Б
-Ажикенова</t>
-        </is>
-      </c>
-      <c r="AB21" s="22" t="inlineStr">
-        <is>
-          <t>1Б
-Дюсембаева</t>
-        </is>
-      </c>
-      <c r="AC21" s="22" t="inlineStr">
-        <is>
-          <t>1Б
-Ажикенова</t>
-        </is>
-      </c>
-      <c r="AH21" s="22" t="inlineStr">
-        <is>
-          <t>1Б
-Ажикенова</t>
-        </is>
-      </c>
-      <c r="AJ21" s="22" t="inlineStr">
-        <is>
-          <t>1Б
-Ажикенова</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="26" t="inlineStr">
-        <is>
-          <t>Начальный класс 2А/4А (№42)</t>
-        </is>
-      </c>
-      <c r="B22" s="22" t="inlineStr">
-        <is>
-          <t>4А
-Актаева</t>
-        </is>
-      </c>
-      <c r="C22" s="22" t="inlineStr">
-        <is>
-          <t>4А
-Актаева</t>
-        </is>
-      </c>
-      <c r="E22" s="22" t="inlineStr">
-        <is>
-          <t>2А
-Актаева</t>
-        </is>
-      </c>
-      <c r="F22" s="22" t="inlineStr">
-        <is>
-          <t>4А
-Актаева</t>
-        </is>
-      </c>
-      <c r="J22" s="22" t="inlineStr">
-        <is>
-          <t>4А
-Актаева</t>
-        </is>
-      </c>
-      <c r="K22" s="22" t="inlineStr">
-        <is>
-          <t>4А
-Актаева</t>
-        </is>
-      </c>
-      <c r="M22" s="22" t="inlineStr">
-        <is>
-          <t>2А
-Жекеева</t>
-        </is>
-      </c>
-      <c r="R22" s="22" t="inlineStr">
-        <is>
-          <t>2А
-Актаева</t>
-        </is>
-      </c>
-      <c r="T22" s="22" t="inlineStr">
-        <is>
-          <t>4А
-Актаева</t>
-        </is>
-      </c>
-      <c r="U22" s="22" t="inlineStr">
-        <is>
-          <t>4А
-Актаева</t>
-        </is>
-      </c>
-      <c r="V22" s="22" t="inlineStr">
-        <is>
-          <t>4А
-Жекеева</t>
-        </is>
-      </c>
-      <c r="Z22" s="22" t="inlineStr">
-        <is>
-          <t>4А
-Актаева</t>
-        </is>
-      </c>
-      <c r="AA22" s="22" t="inlineStr">
-        <is>
-          <t>4А
-Актаева</t>
-        </is>
-      </c>
-      <c r="AC22" s="22" t="inlineStr">
-        <is>
-          <t>4А
-Актаева</t>
-        </is>
-      </c>
-      <c r="AD22" s="22" t="inlineStr">
-        <is>
-          <t>4А
-Актаева</t>
-        </is>
-      </c>
-      <c r="AH22" s="22" t="inlineStr">
-        <is>
-          <t>2А
-Актаева</t>
-        </is>
-      </c>
-      <c r="AI22" s="22" t="inlineStr">
-        <is>
-          <t>4А
-Актаева</t>
-        </is>
-      </c>
-      <c r="AJ22" s="22" t="inlineStr">
-        <is>
-          <t>2А,4А
-Актаева</t>
-        </is>
-      </c>
-      <c r="AL22" s="22" t="inlineStr">
-        <is>
-          <t>4А
-Актаева</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="26" t="inlineStr">
-        <is>
-          <t>Начальный класс 2Б (№6)</t>
-        </is>
-      </c>
-      <c r="B23" s="22" t="inlineStr">
-        <is>
-          <t>2Б
-Квашнина</t>
-        </is>
-      </c>
-      <c r="C23" s="22" t="inlineStr">
-        <is>
-          <t>2Б
-Квашнина</t>
-        </is>
-      </c>
-      <c r="D23" s="22" t="inlineStr">
-        <is>
-          <t>2Б
-Асаева</t>
-        </is>
-      </c>
-      <c r="J23" s="22" t="inlineStr">
-        <is>
-          <t>2Б
-Квашнина</t>
-        </is>
-      </c>
-      <c r="K23" s="22" t="inlineStr">
-        <is>
-          <t>2Б
-Квашнина</t>
-        </is>
-      </c>
-      <c r="L23" s="22" t="inlineStr">
-        <is>
-          <t>2Б
-Квашнина</t>
-        </is>
-      </c>
-      <c r="M23" s="22" t="inlineStr">
-        <is>
-          <t>2Б
-Квашнина</t>
-        </is>
-      </c>
-      <c r="R23" s="22" t="inlineStr">
-        <is>
-          <t>2Б
-Квашнина</t>
-        </is>
-      </c>
-      <c r="T23" s="22" t="inlineStr">
-        <is>
-          <t>2Б
-Квашнина</t>
-        </is>
-      </c>
-      <c r="Z23" s="22" t="inlineStr">
-        <is>
-          <t>2Б
-Квашнина</t>
-        </is>
-      </c>
-      <c r="AA23" s="22" t="inlineStr">
-        <is>
-          <t>2Б
-Квашнина</t>
-        </is>
-      </c>
-      <c r="AB23" s="22" t="inlineStr">
-        <is>
-          <t>2Б
-Квашнина</t>
-        </is>
-      </c>
-      <c r="AC23" s="22" t="inlineStr">
-        <is>
-          <t>2Б
-Асаева</t>
-        </is>
-      </c>
-      <c r="AH23" s="22" t="inlineStr">
-        <is>
-          <t>2Б
-Квашнина</t>
-        </is>
-      </c>
-      <c r="AI23" s="22" t="inlineStr">
-        <is>
-          <t>2Б
-Квашнина</t>
-        </is>
-      </c>
-      <c r="AL23" s="22" t="inlineStr">
-        <is>
-          <t>2Б
-Асаева</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="26" t="inlineStr">
-        <is>
-          <t>Начальный класс 3А (№7)</t>
-        </is>
-      </c>
-      <c r="B24" s="22" t="inlineStr">
-        <is>
-          <t>3А
-Темерканова</t>
-        </is>
-      </c>
-      <c r="C24" s="22" t="inlineStr">
-        <is>
-          <t>3А
-Темерканова</t>
-        </is>
-      </c>
-      <c r="D24" s="22" t="inlineStr">
-        <is>
-          <t>3А
-Дюсембаева</t>
-        </is>
-      </c>
-      <c r="E24" s="22" t="inlineStr">
-        <is>
-          <t>3А
-Темерканова</t>
-        </is>
-      </c>
-      <c r="J24" s="22" t="inlineStr">
-        <is>
-          <t>3А
-Темерканова</t>
-        </is>
-      </c>
-      <c r="K24" s="22" t="inlineStr">
-        <is>
-          <t>3А
-Темерканова</t>
-        </is>
-      </c>
-      <c r="L24" s="22" t="inlineStr">
-        <is>
-          <t>3А
-Темерканова</t>
-        </is>
-      </c>
-      <c r="R24" s="22" t="inlineStr">
-        <is>
-          <t>3А
-Темерканова</t>
-        </is>
-      </c>
-      <c r="S24" s="22" t="inlineStr">
-        <is>
-          <t>3А
-Темерканова</t>
-        </is>
-      </c>
-      <c r="U24" s="22" t="inlineStr">
-        <is>
-          <t>3А
-Темерканова</t>
-        </is>
-      </c>
-      <c r="V24" s="22" t="inlineStr">
-        <is>
-          <t>3А
-Акауова</t>
-        </is>
-      </c>
-      <c r="Z24" s="22" t="inlineStr">
-        <is>
-          <t>3А
-Темерканова</t>
-        </is>
-      </c>
-      <c r="AA24" s="22" t="inlineStr">
-        <is>
-          <t>3А
-Темерканова</t>
-        </is>
-      </c>
-      <c r="AB24" s="22" t="inlineStr">
-        <is>
-          <t>3А
-Темерканова</t>
-        </is>
-      </c>
-      <c r="AC24" s="22" t="inlineStr">
-        <is>
-          <t>3А
-Дюсембаева</t>
-        </is>
-      </c>
-      <c r="AD24" s="22" t="inlineStr">
-        <is>
-          <t>3А
-Темерканова</t>
-        </is>
-      </c>
-      <c r="AH24" s="22" t="inlineStr">
-        <is>
-          <t>3А
-Темерканова</t>
-        </is>
-      </c>
-      <c r="AI24" s="22" t="inlineStr">
-        <is>
-          <t>3А
-Темерканова</t>
-        </is>
-      </c>
-      <c r="AK24" s="22" t="inlineStr">
-        <is>
-          <t>3А
-Акауова</t>
-        </is>
-      </c>
-      <c r="AM24" s="22" t="inlineStr">
-        <is>
-          <t>3А
-Дюсембаева</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="26" t="inlineStr">
-        <is>
-          <t>Начальный класс 4Б (№9)</t>
-        </is>
-      </c>
-      <c r="B25" s="22" t="inlineStr">
-        <is>
-          <t>4Б
-Радионова</t>
-        </is>
-      </c>
-      <c r="C25" s="22" t="inlineStr">
-        <is>
-          <t>4Б
-Радионова</t>
-        </is>
-      </c>
-      <c r="E25" s="22" t="inlineStr">
-        <is>
-          <t>4Б
-Радионова</t>
-        </is>
-      </c>
-      <c r="F25" s="22" t="inlineStr">
-        <is>
-          <t>4Б
-Асаева</t>
-        </is>
-      </c>
-      <c r="J25" s="22" t="inlineStr">
-        <is>
-          <t>4Б
-Радионова</t>
-        </is>
-      </c>
-      <c r="K25" s="22" t="inlineStr">
-        <is>
-          <t>4Б
-Радионова</t>
-        </is>
-      </c>
-      <c r="L25" s="22" t="inlineStr">
-        <is>
-          <t>4Б
-Радионова</t>
-        </is>
-      </c>
-      <c r="M25" s="22" t="inlineStr">
-        <is>
-          <t>4Б
-Асаева</t>
-        </is>
-      </c>
-      <c r="N25" s="22" t="inlineStr">
-        <is>
-          <t>4Б
-Радионова</t>
-        </is>
-      </c>
-      <c r="R25" s="22" t="inlineStr">
-        <is>
-          <t>4Б
-Радионова</t>
-        </is>
-      </c>
-      <c r="S25" s="22" t="inlineStr">
-        <is>
-          <t>4Б
-Радионова</t>
-        </is>
-      </c>
-      <c r="U25" s="22" t="inlineStr">
-        <is>
-          <t>4Б
-Асаева</t>
-        </is>
-      </c>
-      <c r="W25" s="22" t="inlineStr">
-        <is>
-          <t>4Б
-Акауова</t>
-        </is>
-      </c>
-      <c r="Z25" s="22" t="inlineStr">
-        <is>
-          <t>4Б
-Радионова</t>
-        </is>
-      </c>
-      <c r="AA25" s="22" t="inlineStr">
-        <is>
-          <t>4Б
-Радионова</t>
-        </is>
-      </c>
-      <c r="AB25" s="22" t="inlineStr">
-        <is>
-          <t>4Б
-Радионова</t>
-        </is>
-      </c>
-      <c r="AC25" s="22" t="inlineStr">
-        <is>
-          <t>4Б
-Акауова</t>
-        </is>
-      </c>
-      <c r="AD25" s="22" t="inlineStr">
-        <is>
-          <t>4Б
-Радионова</t>
-        </is>
-      </c>
-      <c r="AH25" s="22" t="inlineStr">
-        <is>
-          <t>4Б
-Радионова</t>
-        </is>
-      </c>
-      <c r="AI25" s="22" t="inlineStr">
-        <is>
-          <t>4Б
-Радионова</t>
-        </is>
-      </c>
-      <c r="AJ25" s="22" t="inlineStr">
-        <is>
-          <t>4Б
-Асаева</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="30" customHeight="1">
-      <c r="A26" s="26" t="inlineStr">
-        <is>
-          <t>Спортивный зал (№01)</t>
-        </is>
-      </c>
-      <c r="B26" s="22" t="inlineStr">
-        <is>
-          <t>10А
-Мельников</t>
-        </is>
-      </c>
-      <c r="C26" s="22" t="inlineStr">
-        <is>
-          <t>9Б
-Мельников</t>
-        </is>
-      </c>
-      <c r="D26" s="22" t="inlineStr">
+      <c r="T26" s="22" t="inlineStr">
         <is>
           <t>4Б
 Чифин</t>
         </is>
       </c>
-      <c r="E26" s="22" t="inlineStr">
-        <is>
-          <t>2Б
-Ольков</t>
-        </is>
-      </c>
-      <c r="F26" s="22" t="inlineStr">
-        <is>
-          <t>3А
-Чифин</t>
-        </is>
-      </c>
-      <c r="G26" s="22" t="inlineStr">
+      <c r="U26" s="22" t="inlineStr">
         <is>
           <t>7А
 Ольков</t>
-        </is>
-      </c>
-      <c r="H26" s="22" t="inlineStr">
-        <is>
-          <t>8А
-Ольков</t>
-        </is>
-      </c>
-      <c r="K26" s="22" t="inlineStr">
-        <is>
-          <t>9Б
-Мельников</t>
-        </is>
-      </c>
-      <c r="M26" s="22" t="inlineStr">
-        <is>
-          <t>6Б,6В
-Ольков</t>
-        </is>
-      </c>
-      <c r="O26" s="22" t="inlineStr">
-        <is>
-          <t>8А
-Ольков</t>
-        </is>
-      </c>
-      <c r="P26" s="22" t="inlineStr">
-        <is>
-          <t>8Б
-Ольков</t>
-        </is>
-      </c>
-      <c r="R26" s="22" t="inlineStr">
-        <is>
-          <t>6Б,6В
-Ольков</t>
-        </is>
-      </c>
-      <c r="S26" s="22" t="inlineStr">
-        <is>
-          <t>1Б
-Чифин</t>
-        </is>
-      </c>
-      <c r="T26" s="22" t="inlineStr">
-        <is>
-          <t>4Б
-Чифин</t>
         </is>
       </c>
       <c r="V26" s="22" t="inlineStr">
@@ -16769,7 +16796,7 @@
     <row r="34" ht="28" customHeight="1">
       <c r="A34" s="30" t="inlineStr">
         <is>
-          <t>1 урок 10:30–11:15, 2 урок 11:25–12:10, 3 урок 12:20–13:05 (сдвинуто относительно школьных звонков)</t>
+          <t>Пн–Ср: 1 урок 10:30–11:15, 2 урок 11:25–12:10, 3 урок 12:20–13:05. Чт: 10:05–10:50, 11:05–11:50 (по звонкам 3–4 уроков школы, чтобы Жукова успевала к 5 уроку в 5Б)  Свап Ср и Чт: Жукова перенесена со среды на четверг (10:05–11:50), Дукач с четверга на среду (10:30–13:05).</t>
         </is>
       </c>
     </row>
@@ -16998,12 +17025,12 @@
       </c>
       <c r="E41" s="29" t="inlineStr">
         <is>
-          <t>Изобразительное искусство</t>
+          <t>Развитие речи и коммуникации</t>
         </is>
       </c>
       <c r="F41" s="29" t="inlineStr">
         <is>
-          <t>Жукова Ирина Михайловна</t>
+          <t>Дукач Татьяна Анатольевна</t>
         </is>
       </c>
       <c r="G41" s="29" t="inlineStr"/>
@@ -17031,12 +17058,12 @@
       </c>
       <c r="E42" s="29" t="inlineStr">
         <is>
-          <t>Хозяйственный труд</t>
+          <t>Счет</t>
         </is>
       </c>
       <c r="F42" s="29" t="inlineStr">
         <is>
-          <t>Жукова Ирина Михайловна</t>
+          <t>Дукач Татьяна Анатольевна</t>
         </is>
       </c>
       <c r="G42" s="29" t="inlineStr"/>
@@ -17044,27 +17071,27 @@
     <row r="43">
       <c r="A43" s="29" t="inlineStr">
         <is>
-          <t>Чт</t>
+          <t>Ср</t>
         </is>
       </c>
       <c r="B43" s="29" t="inlineStr">
         <is>
-          <t>3–4</t>
+          <t>5–6</t>
         </is>
       </c>
       <c r="C43" s="29" t="inlineStr">
         <is>
-          <t>3-й 10:05–10:50; 4-й 11:05–11:50</t>
+          <t>5-й 11:55–12:40; 6-й 12:45–13:30</t>
         </is>
       </c>
       <c r="D43" s="29" t="inlineStr">
         <is>
-          <t>10:30–11:15</t>
+          <t>12:20–13:05</t>
         </is>
       </c>
       <c r="E43" s="29" t="inlineStr">
         <is>
-          <t>Развитие речи и коммуникации</t>
+          <t>Человек и мир</t>
         </is>
       </c>
       <c r="F43" s="29" t="inlineStr">
@@ -17082,27 +17109,27 @@
       </c>
       <c r="B44" s="29" t="inlineStr">
         <is>
-          <t>4–5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C44" s="29" t="inlineStr">
         <is>
-          <t>4-й 11:05–11:50; 5-й 11:55–12:40</t>
+          <t>3-й 10:05–10:50</t>
         </is>
       </c>
       <c r="D44" s="29" t="inlineStr">
         <is>
-          <t>11:25–12:10</t>
+          <t>10:05–10:50</t>
         </is>
       </c>
       <c r="E44" s="29" t="inlineStr">
         <is>
-          <t>Счет</t>
+          <t>Изобразительное искусство</t>
         </is>
       </c>
       <c r="F44" s="29" t="inlineStr">
         <is>
-          <t>Дукач Татьяна Анатольевна</t>
+          <t>Жукова Ирина Михайловна</t>
         </is>
       </c>
       <c r="G44" s="29" t="inlineStr"/>
@@ -17115,27 +17142,27 @@
       </c>
       <c r="B45" s="29" t="inlineStr">
         <is>
-          <t>5–6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C45" s="29" t="inlineStr">
         <is>
-          <t>5-й 11:55–12:40; 6-й 12:45–13:30</t>
+          <t>4-й 11:05–11:50</t>
         </is>
       </c>
       <c r="D45" s="29" t="inlineStr">
         <is>
-          <t>12:20–13:05</t>
+          <t>11:05–11:50</t>
         </is>
       </c>
       <c r="E45" s="29" t="inlineStr">
         <is>
-          <t>Человек и мир</t>
+          <t>Хозяйственный труд</t>
         </is>
       </c>
       <c r="F45" s="29" t="inlineStr">
         <is>
-          <t>Дукач Татьяна Анатольевна</t>
+          <t>Жукова Ирина Михайловна</t>
         </is>
       </c>
       <c r="G45" s="29" t="inlineStr"/>
